--- a/results/01_pollution_assessment/artifacts/SumRel_01_updated_data.xlsx
+++ b/results/01_pollution_assessment/artifacts/SumRel_01_updated_data.xlsx
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4745969067577696</v>
+        <v>0.1461630171032758</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4345707915710142</v>
+        <v>-0.2830717709267092</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9243267853069075</v>
+        <v>2.763479807123514</v>
       </c>
       <c r="E5" t="n">
-        <v>0.299725861696791</v>
+        <v>-1.159931038013033</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5268705766987926</v>
+        <v>0.4481559725105925</v>
       </c>
       <c r="G5" t="n">
         <v>2.660090922031275</v>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2576733561841816</v>
+        <v>-2.61842307096378</v>
       </c>
       <c r="C6" t="n">
-        <v>0.169823909704873</v>
+        <v>-2.166129328688029</v>
       </c>
       <c r="D6" t="n">
-        <v>0.243230686560354</v>
+        <v>-1.182851566076757</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1687227330532292</v>
+        <v>-2.21295224057067</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4279270434436434</v>
+        <v>-0.2280902140263398</v>
       </c>
       <c r="G6" t="n">
         <v>1.267377728946281</v>
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3102001673525372</v>
+        <v>-1.94899418220281</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2036852936450419</v>
+        <v>-1.925284433762951</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8404195797588516</v>
+        <v>2.27731399542493</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3341451565085963</v>
+        <v>-0.8832640027353664</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4452304270117665</v>
+        <v>-0.1098273345114712</v>
       </c>
       <c r="G7" t="n">
         <v>2.133680624276793</v>
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7750641297161766</v>
+        <v>3.975472939029722</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6374992256631276</v>
+        <v>1.160291485359084</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9533573171392666</v>
+        <v>2.931685290551719</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3399803720694529</v>
+        <v>-0.8363597358625144</v>
       </c>
       <c r="F8" t="n">
-        <v>0.507481114790837</v>
+        <v>0.3156354404163368</v>
       </c>
       <c r="G8" t="n">
         <v>3.213382159378861</v>
@@ -641,19 +641,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3722274113127165</v>
+        <v>-1.158486857018305</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2610439504719472</v>
+        <v>-1.517311159518486</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9115225033341499</v>
+        <v>2.689290658553455</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2836523809716887</v>
+        <v>-1.289131891287967</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4907235992777867</v>
+        <v>0.2011033877524098</v>
       </c>
       <c r="G9" t="n">
         <v>2.319169845368289</v>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4621999715716549</v>
+        <v>-0.01182994612998662</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09693110212252241</v>
+        <v>-2.684591911729092</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7451698833102089</v>
+        <v>1.72542878264095</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5448837788263049</v>
+        <v>0.8106820869196382</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5671214563178748</v>
+        <v>0.7232573657160433</v>
       </c>
       <c r="G10" t="n">
         <v>2.416306192148566</v>
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4499061108660709</v>
+        <v>-0.1685092747940378</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4414701077396214</v>
+        <v>-0.2339992025810342</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3758780159873583</v>
+        <v>-0.414281141650042</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1629481177972793</v>
+        <v>-2.259369393840901</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3962373357977699</v>
+        <v>-0.4446788403161421</v>
       </c>
       <c r="G11" t="n">
         <v>1.8264396881881</v>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3965749952303471</v>
+        <v>-0.8481886362914927</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2347069923226546</v>
+        <v>-1.704637286806151</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1503501055302019</v>
+        <v>-1.721009913415572</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3417779386579365</v>
+        <v>-0.8219106478881908</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4645219119572452</v>
+        <v>0.02202355758647872</v>
       </c>
       <c r="G12" t="n">
         <v>1.587931943698385</v>
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4069106777432545</v>
+        <v>-0.7164653447894558</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2010066163984452</v>
+        <v>-1.944336984631359</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7891204243184647</v>
+        <v>1.980082126228146</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3631649401281153</v>
+        <v>-0.6499989825683068</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5163885549807952</v>
+        <v>0.3765148355833932</v>
       </c>
       <c r="G13" t="n">
         <v>2.276591213569075</v>
@@ -766,19 +766,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4910853206692494</v>
+        <v>0.3562999044695216</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2411055918769637</v>
+        <v>-1.659126151170106</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8219680459459473</v>
+        <v>2.170404167423368</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4111069107216775</v>
+        <v>-0.2646348156958178</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4635039014351687</v>
+        <v>0.0150657937917144</v>
       </c>
       <c r="G14" t="n">
         <v>2.428769770649007</v>
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5223875881519034</v>
+        <v>0.7552322148557221</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2473858190521788</v>
+        <v>-1.614456959361735</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7704970058097398</v>
+        <v>1.872176383011477</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5582545853357138</v>
+        <v>0.9181584723730878</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4553918696757022</v>
+        <v>-0.04037724894114841</v>
       </c>
       <c r="G15" t="n">
         <v>2.553916868025238</v>
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7503797124968525</v>
+        <v>3.660881940237104</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3056848830122292</v>
+        <v>-1.199794878257832</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3412240009438444</v>
+        <v>-0.6150695869593756</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8479939113629964</v>
+        <v>3.247123106123325</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2707757370958702</v>
+        <v>-1.30216719642931</v>
       </c>
       <c r="G16" t="n">
         <v>2.516058244911793</v>
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2775638842097486</v>
+        <v>-2.3649278791398</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04817454124821548</v>
+        <v>-3.031381304667946</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7549672201377287</v>
+        <v>1.782195423600141</v>
       </c>
       <c r="E17" t="n">
-        <v>0.360383495313425</v>
+        <v>-0.6723566193204957</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5049334762191146</v>
+        <v>0.298223176955328</v>
       </c>
       <c r="G17" t="n">
         <v>1.946022617128232</v>
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.528789930905223</v>
+        <v>0.8368269871156375</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3229634775952979</v>
+        <v>-1.076897913852441</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8498365014758507</v>
+        <v>2.331876477399435</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4044405536179535</v>
+        <v>-0.3182199128360695</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4691127912350977</v>
+        <v>0.05340069262867814</v>
       </c>
       <c r="G18" t="n">
         <v>2.575143254829423</v>
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6161232367109806</v>
+        <v>1.949847872202055</v>
       </c>
       <c r="C19" t="n">
-        <v>0.646864932675818</v>
+        <v>1.226906681163135</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4332112511405152</v>
+        <v>-0.0820872779230888</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-3.569168821793931</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2441918792679968</v>
+        <v>-1.483859035078137</v>
       </c>
       <c r="G19" t="n">
         <v>1.940391299795311</v>
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5217034781906107</v>
+        <v>0.7465135631616248</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4179429248166298</v>
+        <v>-0.4013403221579306</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2352989249225513</v>
+        <v>-1.228808898461442</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2964872509796734</v>
+        <v>-1.185963437294383</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4846999029831134</v>
+        <v>0.1599334242983557</v>
       </c>
       <c r="G20" t="n">
         <v>1.956132481892578</v>
@@ -941,19 +941,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2862966885051687</v>
+        <v>-2.253632497881782</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1833502747449902</v>
+        <v>-2.069920739796283</v>
       </c>
       <c r="D21" t="n">
-        <v>0.834081369310496</v>
+        <v>2.240589840363225</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3043283566275114</v>
+        <v>-1.122935549455663</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5366781636379333</v>
+        <v>0.5151875717321431</v>
       </c>
       <c r="G21" t="n">
         <v>2.1447348528261</v>
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6053124746914808</v>
+        <v>1.812069921391803</v>
       </c>
       <c r="C22" t="n">
-        <v>0.658404310883713</v>
+        <v>1.3089824857697</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8170967647078101</v>
+        <v>2.14217953067516</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1072469249865204</v>
+        <v>-2.707103258251648</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4253319264366726</v>
+        <v>-0.2458269768227078</v>
       </c>
       <c r="G22" t="n">
         <v>2.613392401706197</v>
@@ -991,19 +991,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.303713407547681</v>
+        <v>-2.031664809092879</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1454166540318269</v>
+        <v>-2.339730116487223</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8010756606369889</v>
+        <v>2.049351828762988</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3246814946586586</v>
+        <v>-0.9593342209431666</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5182275115842617</v>
+        <v>0.3890834931741244</v>
       </c>
       <c r="G23" t="n">
         <v>2.093114728459417</v>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6004826529035383</v>
+        <v>1.750516170830915</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5285696544488734</v>
+        <v>0.3855112466161313</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2934139273117647</v>
+        <v>-0.8920854058379685</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2394344442695688</v>
+        <v>-1.644561760504088</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4228031212575404</v>
+        <v>-0.263110520300714</v>
       </c>
       <c r="G24" t="n">
         <v>2.084703800191285</v>
@@ -1041,19 +1041,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5649295156080353</v>
+        <v>1.297408573733281</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3966010541986893</v>
+        <v>-0.5531380335439952</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3248699437408638</v>
+        <v>-0.7098264489323145</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2882519889919833</v>
+        <v>-1.252159608114467</v>
       </c>
       <c r="F25" t="n">
-        <v>0.372174747045673</v>
+        <v>-0.6091386422503443</v>
       </c>
       <c r="G25" t="n">
         <v>1.946827249585245</v>
@@ -1066,19 +1066,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4531853728385168</v>
+        <v>-0.1267166616629151</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4566228460312882</v>
+        <v>-0.1262227552824805</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3346665804585646</v>
+        <v>-0.6530638644716826</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08584679923892796</v>
+        <v>-2.879120418322136</v>
       </c>
       <c r="F26" t="n">
-        <v>0.390032708757735</v>
+        <v>-0.487085405320118</v>
       </c>
       <c r="G26" t="n">
         <v>1.720354307325032</v>
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4832393409085885</v>
+        <v>0.2563066744296122</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4340742515655355</v>
+        <v>-0.286603496790511</v>
       </c>
       <c r="D27" t="n">
-        <v>0.923814068391583</v>
+        <v>2.760509079714799</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2617015959812114</v>
+        <v>-1.465575326243233</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4892581013469989</v>
+        <v>0.191087196148281</v>
       </c>
       <c r="G27" t="n">
         <v>2.592087358193917</v>
@@ -1116,19 +1116,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6899527436386715</v>
+        <v>2.890769349844495</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4156458935863436</v>
+        <v>-0.4176783503458927</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1986776021663886</v>
+        <v>-1.440996099631296</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6342380490520829</v>
+        <v>1.528924025574536</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3792612820791274</v>
+        <v>-0.5607045290296652</v>
       </c>
       <c r="G28" t="n">
         <v>2.317775570522614</v>
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4863785448179797</v>
+        <v>0.2963143150595054</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>-3.374030983295713</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-2.592151797078886</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6178038292714395</v>
+        <v>1.396823502055015</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4338130364860903</v>
+        <v>-0.187861406564276</v>
       </c>
       <c r="G29" t="n">
         <v>1.53799541057551</v>
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6290487152645328</v>
+        <v>2.114576865878735</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4102349583556351</v>
+        <v>-0.4561645542585586</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7651163916690356</v>
+        <v>1.841000626125448</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6507656391242882</v>
+        <v>1.661775072365689</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5313358378699583</v>
+        <v>0.478674549516585</v>
       </c>
       <c r="G30" t="n">
         <v>2.98650154228345</v>
@@ -1191,19 +1191,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.467512626807579</v>
+        <v>0.05587728398447637</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3120268799952826</v>
+        <v>-1.154686338107861</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2387890972021096</v>
+        <v>-1.208586529855833</v>
       </c>
       <c r="E31" t="n">
-        <v>0.37828729538482</v>
+        <v>-0.528443406890065</v>
       </c>
       <c r="F31" t="n">
-        <v>0.368648571205086</v>
+        <v>-0.633238882931122</v>
       </c>
       <c r="G31" t="n">
         <v>1.765264470594877</v>
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6971039986763327</v>
+        <v>2.981908648169002</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2607423791116762</v>
+        <v>-1.519456137488236</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1735852374931125</v>
+        <v>-1.586383492277014</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7177302982953639</v>
+        <v>2.20004623168318</v>
       </c>
       <c r="F32" t="n">
-        <v>0.348672085344473</v>
+        <v>-0.7697715287667245</v>
       </c>
       <c r="G32" t="n">
         <v>2.197833998920958</v>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4217566576980298</v>
+        <v>-0.5272604864964361</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2272655911461887</v>
+        <v>-1.757565527648523</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2241878910343253</v>
+        <v>-1.293187217031307</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3096428152465129</v>
+        <v>-1.08021719865085</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5032146687493856</v>
+        <v>0.2864756987871691</v>
       </c>
       <c r="G33" t="n">
         <v>1.686067623874442</v>
@@ -1266,19 +1266,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.485442471801993</v>
+        <v>0.2843845156874721</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5011199261156756</v>
+        <v>0.1902703507386197</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3877937409012617</v>
+        <v>-0.3452403717077387</v>
       </c>
       <c r="E34" t="n">
-        <v>0.05611462191390484</v>
+        <v>-3.118111757274341</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3408898590173048</v>
+        <v>-0.8229604609119283</v>
       </c>
       <c r="G34" t="n">
         <v>1.77136061975014</v>
@@ -1291,19 +1291,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6992272657714028</v>
+        <v>3.008968663813961</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7172240308022388</v>
+        <v>1.72734782158501</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4288869981799265</v>
+        <v>-0.1071423841781833</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1978037680013341</v>
+        <v>-1.979194873782933</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4126764649667501</v>
+        <v>-0.3323228525645893</v>
       </c>
       <c r="G35" t="n">
         <v>2.455818527721652</v>
@@ -1316,19 +1316,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5491373407928409</v>
+        <v>1.096144918039989</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3320121169642645</v>
+        <v>-1.012537915989258</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1770635290443658</v>
+        <v>-1.566229961667883</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4177585262313399</v>
+        <v>-0.2111682135202834</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5503133858873539</v>
+        <v>0.6083797869825953</v>
       </c>
       <c r="G36" t="n">
         <v>2.026284898920165</v>
@@ -1341,19 +1341,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5722068049985606</v>
+        <v>1.390154119132507</v>
       </c>
       <c r="C37" t="n">
-        <v>0.521596067793572</v>
+        <v>0.3359104167086873</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3267968457626984</v>
+        <v>-0.6986618072380764</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1022555271573514</v>
+        <v>-2.747224801904364</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2962455184274666</v>
+        <v>-1.128089700601403</v>
       </c>
       <c r="G37" t="n">
         <v>1.819100764139649</v>
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4993353991022541</v>
+        <v>0.4614431773001467</v>
       </c>
       <c r="C38" t="n">
-        <v>0.295414890184875</v>
+        <v>-1.272841961854766</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8493559187984098</v>
+        <v>2.329091938623054</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4415410935980529</v>
+        <v>-0.02000065937321023</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4523743815057935</v>
+        <v>-0.06100077834916965</v>
       </c>
       <c r="G38" t="n">
         <v>2.538021683189385</v>
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7374807311980002</v>
+        <v>3.496490641299062</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5254172026942543</v>
+        <v>0.3630888933851129</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1566784321049476</v>
+        <v>-1.684343026396639</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2902658601411758</v>
+        <v>-1.235971834270616</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4695857531487154</v>
+        <v>0.05663323021793536</v>
       </c>
       <c r="G39" t="n">
         <v>2.179427979287093</v>
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5419112580770884</v>
+        <v>1.004051977027507</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4767344106716816</v>
+        <v>0.01682419404342771</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7518632452480585</v>
+        <v>1.764210717020153</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2452669558914615</v>
+        <v>-1.597679228265277</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5493570933233298</v>
+        <v>0.6018438449320197</v>
       </c>
       <c r="G40" t="n">
         <v>2.56513296321162</v>
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4651561557307316</v>
+        <v>0.02584519600344023</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2645302576111763</v>
+        <v>-1.492514202663214</v>
       </c>
       <c r="D41" t="n">
-        <v>0.903183418158147</v>
+        <v>2.640973257360858</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4652157972095634</v>
+        <v>0.1702998710440349</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5254360504073077</v>
+        <v>0.43835146177413</v>
       </c>
       <c r="G41" t="n">
         <v>2.623521679116926</v>
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7637891954072916</v>
+        <v>3.831779336136942</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4387465051753653</v>
+        <v>-0.2533712924685882</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4112886677523168</v>
+        <v>-0.209108675880971</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5185464654022424</v>
+        <v>0.5989791318749325</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4418790882069332</v>
+        <v>-0.1327326221235222</v>
       </c>
       <c r="G42" t="n">
         <v>2.574249921944149</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9775067813330917</v>
+        <v>6.555506950144018</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5489647996396479</v>
+        <v>0.5305752111939868</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2292939981407258</v>
+        <v>-1.263601978316839</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5960079132105945</v>
+        <v>1.22162492489978</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4982663735936817</v>
+        <v>0.2526557449325313</v>
       </c>
       <c r="G43" t="n">
         <v>2.850039865917742</v>
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7422970234339675</v>
+        <v>3.557871964241698</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5862510904287278</v>
+        <v>0.7957803428894118</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4435670784945845</v>
+        <v>-0.02208469318061384</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2362587945924242</v>
+        <v>-1.670088070269003</v>
       </c>
       <c r="F44" t="n">
-        <v>0.373645422442988</v>
+        <v>-0.5990870643821545</v>
       </c>
       <c r="G44" t="n">
         <v>2.382019409392692</v>
@@ -1541,19 +1541,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6901565077010502</v>
+        <v>2.893366224598804</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5896521459849051</v>
+        <v>0.8199709332536217</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6505968431677325</v>
+        <v>1.177464176677081</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5915488375369373</v>
+        <v>1.185782260096363</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>3.681838434817529</v>
       </c>
       <c r="G45" t="n">
         <v>3.521954334390625</v>
@@ -1566,19 +1566,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.56806693376109</v>
+        <v>1.337393455759457</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5493304327413789</v>
+        <v>0.5331758392759078</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3433996664261247</v>
+        <v>-0.6024635876501555</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1390985615588959</v>
+        <v>-2.451075413770698</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3676546923858368</v>
+        <v>-0.6400317145522038</v>
       </c>
       <c r="G46" t="n">
         <v>1.967550286873326</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3948931572335855</v>
+        <v>-0.8696228508612583</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3790456244188022</v>
+        <v>-0.6780040357184001</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3038393444941487</v>
+        <v>-0.8316796114408801</v>
       </c>
       <c r="E47" t="n">
-        <v>0.180807603128216</v>
+        <v>-2.11581238940162</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5227822636279221</v>
+        <v>0.4202137105699785</v>
       </c>
       <c r="G47" t="n">
         <v>1.781367992902675</v>
@@ -1616,19 +1616,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6920493137342756</v>
+        <v>2.917489125100054</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5167366398753422</v>
+        <v>0.3013469030487012</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9034678722125055</v>
+        <v>2.642621409451311</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3669850630495454</v>
+        <v>-0.619292308046149</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5580407047477031</v>
+        <v>0.661193444829144</v>
       </c>
       <c r="G48" t="n">
         <v>3.037279593619371</v>
@@ -1641,19 +1641,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4315652138063645</v>
+        <v>-0.4022551669291249</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2558394065719206</v>
+        <v>-1.554329369729555</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2750620886944001</v>
+        <v>-0.9984175910096292</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2546999455851121</v>
+        <v>-1.521855557076872</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3827372157944766</v>
+        <v>-0.536947676587389</v>
       </c>
       <c r="G49" t="n">
         <v>1.599903870452274</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5966073432996783</v>
+        <v>1.701127217951179</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4004767138085472</v>
+        <v>-0.5255717405315506</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3180995562332413</v>
+        <v>-0.7490546763134789</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2097426061261685</v>
+        <v>-1.883228847554964</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1707064253671641</v>
+        <v>-1.986107704915156</v>
       </c>
       <c r="G50" t="n">
         <v>1.6956326448348</v>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6478839196008841</v>
+        <v>2.354622465982963</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4438668111633718</v>
+        <v>-0.2169522388396917</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4221396901039073</v>
+        <v>-0.1462368872799416</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2137937757921553</v>
+        <v>-1.850664987457779</v>
       </c>
       <c r="F51" t="n">
-        <v>0.08674009433000712</v>
+        <v>-2.559989688843802</v>
       </c>
       <c r="G51" t="n">
         <v>1.814424290990326</v>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6009062358026265</v>
+        <v>1.755914530699477</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4190782663358482</v>
+        <v>-0.3932650110784013</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2254528375790418</v>
+        <v>-1.285858004246176</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2199252194626042</v>
+        <v>-1.801379598214613</v>
       </c>
       <c r="F52" t="n">
-        <v>0.17001395595225</v>
+        <v>-1.990840503368205</v>
       </c>
       <c r="G52" t="n">
         <v>1.635376515132371</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6853216505185022</v>
+        <v>2.831748300360889</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5544822451838949</v>
+        <v>0.5698189879606708</v>
       </c>
       <c r="D53" t="n">
-        <v>0.179995678408526</v>
+        <v>-1.549240827464957</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2738321348778583</v>
+        <v>-1.368068382791717</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4732552897440292</v>
+        <v>0.08171329404120221</v>
       </c>
       <c r="G53" t="n">
         <v>2.166886998732811</v>
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.482292423318319</v>
+        <v>0.2442386661857714</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2649679630121791</v>
+        <v>-1.489400948004193</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1967292976057901</v>
+        <v>-1.452284749538686</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3745087125490466</v>
+        <v>-0.5588161764787654</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4391820264878001</v>
+        <v>-0.1511661431674419</v>
       </c>
       <c r="G54" t="n">
         <v>1.757680422973135</v>
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7659301314080673</v>
+        <v>3.859064533468148</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5580091542753759</v>
+        <v>0.5949047331578832</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2316889462179526</v>
+        <v>-1.249725436149384</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2991499797727762</v>
+        <v>-1.164560056284858</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3126213670741366</v>
+        <v>-1.016166214201748</v>
       </c>
       <c r="G55" t="n">
         <v>2.167399578748308</v>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7008729885720086</v>
+        <v>3.029942607617384</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5454673892469203</v>
+        <v>0.5056992805458262</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1295883198535298</v>
+        <v>-1.841305546190881</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2749419923628517</v>
+        <v>-1.359147195369583</v>
       </c>
       <c r="F56" t="n">
-        <v>0.491167557163683</v>
+        <v>0.2041376924456348</v>
       </c>
       <c r="G56" t="n">
         <v>2.142038247198994</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4055838691399105</v>
+        <v>-0.7333748808754794</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2921848258132824</v>
+        <v>-1.29581634812179</v>
       </c>
       <c r="D57" t="n">
-        <v>0.326067140511287</v>
+        <v>-0.7028897843651414</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2259792010821368</v>
+        <v>-1.752716859612337</v>
       </c>
       <c r="F57" t="n">
-        <v>0.62441601970585</v>
+        <v>1.114846676565727</v>
       </c>
       <c r="G57" t="n">
         <v>1.874231056252467</v>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5601444483024109</v>
+        <v>1.236425197476465</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5478880536320156</v>
+        <v>0.5229166707300932</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2830885864783657</v>
+        <v>-0.9519113489681915</v>
       </c>
       <c r="E58" t="n">
-        <v>0.313326425410842</v>
+        <v>-1.050607832484112</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4621385447942732</v>
+        <v>0.005734034642913454</v>
       </c>
       <c r="G58" t="n">
         <v>2.166586058617908</v>
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3501744168311687</v>
+        <v>-1.439541641446721</v>
       </c>
       <c r="C59" t="n">
-        <v>0.128280739380908</v>
+        <v>-2.461612245429088</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2391456677742647</v>
+        <v>-1.206520528247183</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3755533823135112</v>
+        <v>-0.5504189769382474</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4996454746195236</v>
+        <v>0.2620814423873599</v>
       </c>
       <c r="G59" t="n">
         <v>1.592799680919376</v>
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7968850694695153</v>
+        <v>4.253570297804814</v>
       </c>
       <c r="C60" t="n">
-        <v>0.5421523702786668</v>
+        <v>0.4821206401543292</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2572093711171005</v>
+        <v>-1.101857824483052</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3371379368325406</v>
+        <v>-0.8592076220340685</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4523887122968113</v>
+        <v>-0.06090283215241446</v>
       </c>
       <c r="G60" t="n">
         <v>2.385773459994635</v>
@@ -1941,19 +1941,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5981282750573238</v>
+        <v>1.720510760065293</v>
       </c>
       <c r="C61" t="n">
-        <v>0.01272371312660734</v>
+        <v>-3.283531393661418</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4780562291284314</v>
+        <v>0.1777485130759779</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9779984231567342</v>
+        <v>4.292117288815221</v>
       </c>
       <c r="F61" t="n">
-        <v>0.25967052435327</v>
+        <v>-1.378067637022015</v>
       </c>
       <c r="G61" t="n">
         <v>2.326577164822367</v>
@@ -1966,19 +1966,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9905182490356108</v>
+        <v>6.721331834074801</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4409317767803643</v>
+        <v>-0.2378281737638503</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1914358341628288</v>
+        <v>-1.482955547530763</v>
       </c>
       <c r="E62" t="n">
-        <v>0.6441404726788168</v>
+        <v>1.608521071413265</v>
       </c>
       <c r="F62" t="n">
-        <v>0.500632134158017</v>
+        <v>0.2688249326222985</v>
       </c>
       <c r="G62" t="n">
         <v>2.767658466815638</v>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5482542637703984</v>
+        <v>1.084890527059936</v>
       </c>
       <c r="C63" t="n">
-        <v>0.102074325112397</v>
+        <v>-2.648009856997918</v>
       </c>
       <c r="D63" t="n">
-        <v>0.256785646701787</v>
+        <v>-1.104312921431662</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5899256148787306</v>
+        <v>1.172734572661247</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3582497483306528</v>
+        <v>-0.7043113833963557</v>
       </c>
       <c r="G63" t="n">
         <v>1.855289598793966</v>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.600526352422122</v>
+        <v>1.751073100130719</v>
       </c>
       <c r="C64" t="n">
-        <v>0.3228721536323513</v>
+        <v>-1.077547471185917</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3060897915444776</v>
+        <v>-0.8186403210752722</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3886448604674699</v>
+        <v>-0.4451878713022363</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3382401312290295</v>
+        <v>-0.8410704702600007</v>
       </c>
       <c r="G64" t="n">
         <v>1.95637328929545</v>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8684307388725729</v>
+        <v>5.165385367077522</v>
       </c>
       <c r="C65" t="n">
-        <v>0.3039062248706237</v>
+        <v>-1.21244588903694</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1542479649782257</v>
+        <v>-1.698425369095952</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6606785798268667</v>
+        <v>1.741456655909494</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4806623396861266</v>
+        <v>0.1323380202061264</v>
       </c>
       <c r="G65" t="n">
         <v>2.467925848234416</v>
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.77131020120551</v>
+        <v>3.927630929673222</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3571211818641831</v>
+        <v>-0.8339453898192339</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3092977945631336</v>
+        <v>-0.8000528662636212</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5895008724045661</v>
+        <v>1.169320434116975</v>
       </c>
       <c r="F66" t="n">
-        <v>0.301195121474578</v>
+        <v>-1.094260807743402</v>
       </c>
       <c r="G66" t="n">
         <v>2.328425171511971</v>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8077219833367963</v>
+        <v>4.391681541309022</v>
       </c>
       <c r="C67" t="n">
-        <v>0.557137509578421</v>
+        <v>0.588705010907279</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8693874790905177</v>
+        <v>2.44515658057355</v>
       </c>
       <c r="E67" t="n">
-        <v>0.409825783659344</v>
+        <v>-0.2749326915845541</v>
       </c>
       <c r="F67" t="n">
-        <v>0.5406116230626467</v>
+        <v>0.5420714604346089</v>
       </c>
       <c r="G67" t="n">
         <v>3.184684378727726</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5906354705437348</v>
+        <v>1.625018578307704</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5335337979683837</v>
+        <v>0.4208195679317051</v>
       </c>
       <c r="D68" t="n">
-        <v>0.9585577371642899</v>
+        <v>2.96181698670493</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2736473781046624</v>
+        <v>-1.369553483197379</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3414922613040446</v>
+        <v>-0.8188432413649119</v>
       </c>
       <c r="G68" t="n">
         <v>2.697866645085115</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5761045544230835</v>
+        <v>1.439829056709893</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3985708818656676</v>
+        <v>-0.5391272967615832</v>
       </c>
       <c r="D69" t="n">
-        <v>0.8822790391143867</v>
+        <v>2.519851425934307</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4155071296198924</v>
+        <v>-0.2292652497648993</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5474003966041896</v>
+        <v>0.5884704727570466</v>
       </c>
       <c r="G69" t="n">
         <v>2.81986200162722</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.767750909120121</v>
+        <v>3.882269467735987</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5286246123082792</v>
+        <v>0.3859021438073764</v>
       </c>
       <c r="D70" t="n">
-        <v>0.8696275423735416</v>
+        <v>2.446547528586752</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4124432349421072</v>
+        <v>-0.2538932574431716</v>
       </c>
       <c r="F70" t="n">
-        <v>0.5536770186328448</v>
+        <v>0.6313690995957126</v>
       </c>
       <c r="G70" t="n">
         <v>3.132123317376894</v>
@@ -2191,19 +2191,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6404354344293456</v>
+        <v>2.259695112876489</v>
       </c>
       <c r="C71" t="n">
-        <v>0.4163866480998409</v>
+        <v>-0.4124096069512407</v>
       </c>
       <c r="D71" t="n">
-        <v>0.7927824614648837</v>
+        <v>2.001300295158102</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4566754061074625</v>
+        <v>0.1016510303501927</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6250951121173216</v>
+        <v>1.119488047643306</v>
       </c>
       <c r="G71" t="n">
         <v>2.931375062218854</v>
@@ -2216,19 +2216,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6931656668002454</v>
+        <v>2.93171650680845</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2990676569263301</v>
+        <v>-1.246861032558254</v>
       </c>
       <c r="D72" t="n">
-        <v>0.6227083559773076</v>
+        <v>1.015875801478323</v>
       </c>
       <c r="E72" t="n">
-        <v>0.5825888429329936</v>
+        <v>1.113760588626013</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9647952907770359</v>
+        <v>3.441225940226508</v>
       </c>
       <c r="G72" t="n">
         <v>3.162325813413912</v>
@@ -2241,19 +2241,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.9026038492070401</v>
+        <v>5.600905185773277</v>
       </c>
       <c r="C73" t="n">
-        <v>0.6606410202699555</v>
+        <v>1.324891464506641</v>
       </c>
       <c r="D73" t="n">
-        <v>0.1805467660584461</v>
+        <v>-1.54604777660728</v>
       </c>
       <c r="E73" t="n">
-        <v>0.3968153077834334</v>
+        <v>-0.3795126897460858</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9521524407998946</v>
+        <v>3.354816259848985</v>
       </c>
       <c r="G73" t="n">
         <v>3.09275938411877</v>
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8272948146135937</v>
+        <v>4.641127841209785</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5643948660819573</v>
+        <v>0.6403242024800895</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9215996131933117</v>
+        <v>2.747678329341149</v>
       </c>
       <c r="E74" t="n">
-        <v>0.3836020379793783</v>
+        <v>-0.4857227734505894</v>
       </c>
       <c r="F74" t="n">
-        <v>0.5217321299187581</v>
+        <v>0.413036395460917</v>
       </c>
       <c r="G74" t="n">
         <v>3.218623461786999</v>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.653243814211362</v>
+        <v>2.422931739155248</v>
       </c>
       <c r="C75" t="n">
-        <v>0.5720262185815462</v>
+        <v>0.694603504653542</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9423048753384816</v>
+        <v>2.867646459747699</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3226531650684367</v>
+        <v>-0.9756382137286365</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5199526243081898</v>
+        <v>0.4008740656604979</v>
       </c>
       <c r="G75" t="n">
         <v>3.010180697508016</v>
@@ -2316,19 +2316,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6630217047970338</v>
+        <v>2.54754624141797</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4543948495336061</v>
+        <v>-0.1420697621067095</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>3.201937143472751</v>
       </c>
       <c r="E76" t="n">
-        <v>0.3312316714531551</v>
+        <v>-0.9066829971401626</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2589996673626849</v>
+        <v>-1.38265272173316</v>
       </c>
       <c r="G76" t="n">
         <v>2.70764789314648</v>
@@ -2341,19 +2341,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5896768109398065</v>
+        <v>1.612800923759805</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4183652326042007</v>
+        <v>-0.3983365856625974</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8253991727079085</v>
+        <v>2.190284421048478</v>
       </c>
       <c r="E77" t="n">
-        <v>0.3842529661327017</v>
+        <v>-0.4804905232448999</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5890848816868328</v>
+        <v>0.8733700831459458</v>
       </c>
       <c r="G77" t="n">
         <v>2.80677906407145</v>
@@ -2366,19 +2366,19 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6788299238102649</v>
+        <v>2.74901437268143</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4591210603268674</v>
+        <v>-0.1084537780728595</v>
       </c>
       <c r="D78" t="n">
-        <v>0.8371829803608046</v>
+        <v>2.258560850647712</v>
       </c>
       <c r="E78" t="n">
-        <v>0.4304491060119401</v>
+        <v>-0.10915958426013</v>
       </c>
       <c r="F78" t="n">
-        <v>0.5693910840946644</v>
+        <v>0.7387695177326324</v>
       </c>
       <c r="G78" t="n">
         <v>2.974974154604542</v>
@@ -2391,19 +2391,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4259794438384148</v>
+        <v>-0.4734431126533395</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3834620938389542</v>
+        <v>-0.6465911402704233</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3545678357266164</v>
+        <v>-0.5377542214199683</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2001048401158247</v>
+        <v>-1.960698538998704</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5601275943142237</v>
+        <v>0.675456641873503</v>
       </c>
       <c r="G79" t="n">
         <v>1.924241807834034</v>
@@ -2416,19 +2416,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5656222560816909</v>
+        <v>1.306237217147264</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2789579233832101</v>
+        <v>-1.389894957891074</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8330840616624919</v>
+        <v>2.234811351149597</v>
       </c>
       <c r="E80" t="n">
-        <v>0.4774011507380781</v>
+        <v>0.2682474220609176</v>
       </c>
       <c r="F80" t="n">
-        <v>0.551178106226357</v>
+        <v>0.6142898632900973</v>
       </c>
       <c r="G80" t="n">
         <v>2.706243498091828</v>
@@ -2441,19 +2441,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7517256389471527</v>
+        <v>3.67803512406718</v>
       </c>
       <c r="C81" t="n">
-        <v>0.5574578266461276</v>
+        <v>0.5909833209329661</v>
       </c>
       <c r="D81" t="n">
-        <v>0.9558323625751309</v>
+        <v>2.946025923939023</v>
       </c>
       <c r="E81" t="n">
-        <v>0.3527548908727252</v>
+        <v>-0.733676393169858</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3902072686544777</v>
+        <v>-0.4858923464044823</v>
       </c>
       <c r="G81" t="n">
         <v>3.007977987695615</v>
@@ -2466,19 +2466,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6280847762652918</v>
+        <v>2.102291927982409</v>
       </c>
       <c r="C82" t="n">
-        <v>0.5480465901700677</v>
+        <v>0.5240442890198951</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4694451086788476</v>
+        <v>0.1278549153132864</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2078288704260417</v>
+        <v>-1.898611718858809</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0692507035517556</v>
+        <v>-2.679523865859168</v>
       </c>
       <c r="G82" t="n">
         <v>1.922656049092005</v>
@@ -2491,19 +2491,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5710751553023293</v>
+        <v>1.375731789244887</v>
       </c>
       <c r="C83" t="n">
-        <v>0.434418799943063</v>
+        <v>-0.2841528374220448</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2763152562009253</v>
+        <v>-0.9911566270194123</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1799089358149479</v>
+        <v>-2.123036001117732</v>
       </c>
       <c r="F83" t="n">
-        <v>0.3733741822002739</v>
+        <v>-0.6009409013509414</v>
       </c>
       <c r="G83" t="n">
         <v>1.83509232946154</v>
@@ -2516,19 +2516,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7496020609057499</v>
+        <v>3.650971145561097</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3240467202455277</v>
+        <v>-1.069193164904969</v>
       </c>
       <c r="D84" t="n">
-        <v>0.7693003371589151</v>
+        <v>1.86524277841623</v>
       </c>
       <c r="E84" t="n">
-        <v>0.5654667053157075</v>
+        <v>0.9761304867284574</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5547624573965821</v>
+        <v>0.6387877130265049</v>
       </c>
       <c r="G84" t="n">
         <v>2.963178281022482</v>
@@ -2541,19 +2541,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6980453403721991</v>
+        <v>2.993905594326431</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3934672094101456</v>
+        <v>-0.5754280415407723</v>
       </c>
       <c r="D85" t="n">
-        <v>0.8402115464951354</v>
+        <v>2.276108632192367</v>
       </c>
       <c r="E85" t="n">
-        <v>0.4736945240032803</v>
+        <v>0.2384530455286678</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5613230147974027</v>
+        <v>0.6836269438271769</v>
       </c>
       <c r="G85" t="n">
         <v>2.966741635078163</v>
@@ -2566,19 +2566,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.9334990011324412</v>
+        <v>5.994649004624828</v>
       </c>
       <c r="C86" t="n">
-        <v>0.4875560503796529</v>
+        <v>0.09379496059533921</v>
       </c>
       <c r="D86" t="n">
-        <v>0.8299939483255052</v>
+        <v>2.216906959638711</v>
       </c>
       <c r="E86" t="n">
-        <v>0.6054491999434468</v>
+        <v>1.297515288832765</v>
       </c>
       <c r="F86" t="n">
-        <v>0.5932983421235098</v>
+        <v>0.9021676857652036</v>
       </c>
       <c r="G86" t="n">
         <v>3.449796541904556</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4575036264652018</v>
+        <v>-0.0716826007252645</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1567339386040638</v>
+        <v>-2.259233990916757</v>
       </c>
       <c r="D87" t="n">
-        <v>0.8068000919688815</v>
+        <v>2.082519693034055</v>
       </c>
       <c r="E87" t="n">
-        <v>0.4938468948100888</v>
+        <v>0.400440579422697</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3718763133026134</v>
+        <v>-0.6111783377618998</v>
       </c>
       <c r="G87" t="n">
         <v>2.286760865150849</v>
@@ -2616,19 +2616,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5773490495760649</v>
+        <v>1.455689547548723</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2265280193507119</v>
+        <v>-1.762811633415942</v>
       </c>
       <c r="D88" t="n">
-        <v>0.7358294520311127</v>
+        <v>1.671309493066756</v>
       </c>
       <c r="E88" t="n">
-        <v>0.5710227885575041</v>
+        <v>1.020791049551393</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5109444960658476</v>
+        <v>0.3393065010980859</v>
       </c>
       <c r="G88" t="n">
         <v>2.621673805581241</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4136907663221907</v>
+        <v>-0.6300563840674588</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3251551589899228</v>
+        <v>-1.061309204420766</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3426208122274422</v>
+        <v>-0.6069763381490443</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2813038664852284</v>
+        <v>-1.308009574396477</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6335293202176466</v>
+        <v>1.177133058657776</v>
       </c>
       <c r="G89" t="n">
         <v>1.996299924242431</v>
@@ -2666,19 +2666,19 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7065930542623292</v>
+        <v>3.102842087588441</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5581928045062601</v>
+        <v>0.5962109768908158</v>
       </c>
       <c r="D90" t="n">
-        <v>0.2468384184423064</v>
+        <v>-1.161948046679061</v>
       </c>
       <c r="E90" t="n">
-        <v>0.2846950722997512</v>
+        <v>-1.280750594691914</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4883980958663969</v>
+        <v>0.1852093443319505</v>
       </c>
       <c r="G90" t="n">
         <v>2.284717445377044</v>
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5696114516611309</v>
+        <v>1.357077591889135</v>
       </c>
       <c r="C91" t="n">
-        <v>0.5218601132835684</v>
+        <v>0.3377884854966019</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9521888956593905</v>
+        <v>2.924915352577265</v>
       </c>
       <c r="E91" t="n">
-        <v>0.2092732550554273</v>
+        <v>-1.887001556146362</v>
       </c>
       <c r="F91" t="n">
-        <v>0.4465813466383316</v>
+        <v>-0.1005942475604853</v>
       </c>
       <c r="G91" t="n">
         <v>2.699515062297849</v>
@@ -2716,19 +2716,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7270061444809685</v>
+        <v>3.362997082671668</v>
       </c>
       <c r="C92" t="n">
-        <v>0.5603338262186831</v>
+        <v>0.6114393606530381</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2228236188309405</v>
+        <v>-1.30109193151684</v>
       </c>
       <c r="E92" t="n">
-        <v>0.3354149594369414</v>
+        <v>-0.8730571517962926</v>
       </c>
       <c r="F92" t="n">
-        <v>0.5167251142510223</v>
+        <v>0.3788151064100657</v>
       </c>
       <c r="G92" t="n">
         <v>2.362303663218555</v>
@@ -2741,19 +2741,19 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8016283830315825</v>
+        <v>4.314021542726616</v>
       </c>
       <c r="C93" t="n">
-        <v>0.708743031993889</v>
+        <v>1.667025264466083</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1544654020923366</v>
+        <v>-1.697165519117817</v>
       </c>
       <c r="E93" t="n">
-        <v>0.2737739457186368</v>
+        <v>-1.368536115273023</v>
       </c>
       <c r="F93" t="n">
-        <v>0.5732339182666498</v>
+        <v>0.7650340129331171</v>
       </c>
       <c r="G93" t="n">
         <v>2.511844681103095</v>
@@ -2766,19 +2766,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.3470079192525538</v>
+        <v>-1.479897126734461</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2589294537402781</v>
+        <v>-1.53235087981043</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2756713673188497</v>
+        <v>-0.9948873764699908</v>
       </c>
       <c r="E94" t="n">
-        <v>0.275689602488943</v>
+        <v>-1.353137802142319</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5024228727994454</v>
+        <v>0.28106403645769</v>
       </c>
       <c r="G94" t="n">
         <v>1.65972121560007</v>
@@ -2791,19 +2791,19 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5001062400358601</v>
+        <v>0.4712671734293135</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2834521811534184</v>
+        <v>-1.357928779475431</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2681665759142246</v>
+        <v>-1.038370805348676</v>
       </c>
       <c r="E95" t="n">
-        <v>0.339996218058326</v>
+        <v>-0.8362323636200973</v>
       </c>
       <c r="F95" t="n">
-        <v>0.464859376559414</v>
+        <v>0.02433001605627384</v>
       </c>
       <c r="G95" t="n">
         <v>1.856580591721243</v>
@@ -2816,19 +2816,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7314660529615133</v>
+        <v>3.419836466439655</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3752956348338404</v>
+        <v>-0.7046764791470588</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2344601410163482</v>
+        <v>-1.233668887015886</v>
       </c>
       <c r="E96" t="n">
-        <v>0.5164803198786569</v>
+        <v>0.5823711694053896</v>
       </c>
       <c r="F96" t="n">
-        <v>0.5075796518735924</v>
+        <v>0.316308908648707</v>
       </c>
       <c r="G96" t="n">
         <v>2.365281800563952</v>
@@ -2841,19 +2841,19 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6590007243578806</v>
+        <v>2.496300783960359</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2251894848989133</v>
+        <v>-1.772332189042571</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1571983689173588</v>
+        <v>-1.681330466262061</v>
       </c>
       <c r="E97" t="n">
-        <v>0.5549139867951354</v>
+        <v>0.8913062809110552</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3694963444295517</v>
+        <v>-0.6274446345226417</v>
       </c>
       <c r="G97" t="n">
         <v>1.96579890939884</v>
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.625912350805265</v>
+        <v>2.07460541267196</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3267573149988645</v>
+        <v>-1.049913595301275</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1677452372555188</v>
+        <v>-1.620220973066474</v>
       </c>
       <c r="E98" t="n">
-        <v>0.4098780507059315</v>
+        <v>-0.2745125618607719</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5136415573680004</v>
+        <v>0.3577400192920832</v>
       </c>
       <c r="G98" t="n">
         <v>2.04393451113358</v>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6200213455377179</v>
+        <v>1.999527390187418</v>
       </c>
       <c r="C99" t="n">
-        <v>0.3117466483488708</v>
+        <v>-1.156679533706541</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3303982437454727</v>
+        <v>-0.6777949870155584</v>
       </c>
       <c r="E99" t="n">
-        <v>0.4934705022549241</v>
+        <v>0.3974150841908107</v>
       </c>
       <c r="F99" t="n">
-        <v>0.3693055093072765</v>
+        <v>-0.6287489291991131</v>
       </c>
       <c r="G99" t="n">
         <v>2.124942249194262</v>
@@ -2916,19 +2916,19 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5871527405550957</v>
+        <v>1.580632863388202</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1720226807715412</v>
+        <v>-2.150490192749234</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2868976844908349</v>
+        <v>-0.9298410963006669</v>
       </c>
       <c r="E100" t="n">
-        <v>0.5082000497652057</v>
+        <v>0.5158132170675322</v>
       </c>
       <c r="F100" t="n">
-        <v>0.3875742922918902</v>
+        <v>-0.5038878653218247</v>
       </c>
       <c r="G100" t="n">
         <v>1.941847447874568</v>
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5901586072573175</v>
+        <v>1.618941185585461</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2577395573413812</v>
+        <v>-1.54081422181885</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1617699043718861</v>
+        <v>-1.654842583243645</v>
       </c>
       <c r="E101" t="n">
-        <v>0.5073718467382425</v>
+        <v>0.5091560069959498</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8256982409959298</v>
+        <v>2.490543804887305</v>
       </c>
       <c r="G101" t="n">
         <v>2.342738156704757</v>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5336298602500342</v>
+        <v>0.8985095536166571</v>
       </c>
       <c r="C102" t="n">
-        <v>0.1911587334199734</v>
+        <v>-2.014381739605798</v>
       </c>
       <c r="D102" t="n">
-        <v>0.08426375148876122</v>
+        <v>-2.103920126488463</v>
       </c>
       <c r="E102" t="n">
-        <v>0.3690860370812686</v>
+        <v>-0.6024043892282173</v>
       </c>
       <c r="F102" t="n">
-        <v>0.7918350375648093</v>
+        <v>2.259100056813676</v>
       </c>
       <c r="G102" t="n">
         <v>1.969973419804847</v>
@@ -2991,19 +2991,19 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5234719288435601</v>
+        <v>0.7690516142844713</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3647928069575589</v>
+        <v>-0.7793796419223545</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2347014517085289</v>
+        <v>-1.232270711403085</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2519020298027501</v>
+        <v>-1.544345589737193</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3652504508882173</v>
+        <v>-0.6564639066398494</v>
       </c>
       <c r="G103" t="n">
         <v>1.740118668200615</v>
@@ -3016,19 +3016,19 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.2515267714279202</v>
+        <v>-2.696758330834611</v>
       </c>
       <c r="C104" t="n">
-        <v>0.171213018257092</v>
+        <v>-2.15624905610703</v>
       </c>
       <c r="D104" t="n">
-        <v>0.358547988081802</v>
+        <v>-0.5146928646770766</v>
       </c>
       <c r="E104" t="n">
-        <v>0.2004305366469868</v>
+        <v>-1.958080545394549</v>
       </c>
       <c r="F104" t="n">
-        <v>0.4986068132440482</v>
+        <v>0.2549825368686213</v>
       </c>
       <c r="G104" t="n">
         <v>1.480325127657849</v>
@@ -3041,19 +3041,19 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7419293129378134</v>
+        <v>3.55318567121627</v>
       </c>
       <c r="C105" t="n">
-        <v>0.6153764571481274</v>
+        <v>1.002939503884801</v>
       </c>
       <c r="D105" t="n">
-        <v>0.2529987722399505</v>
+        <v>-1.126254408870247</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2667896306988077</v>
+        <v>-1.424677001963086</v>
       </c>
       <c r="F105" t="n">
-        <v>0.4705350632582483</v>
+        <v>0.06312144951122764</v>
       </c>
       <c r="G105" t="n">
         <v>2.347629236282947</v>
@@ -3066,19 +3066,19 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7478199928277829</v>
+        <v>3.628259546920428</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6026150042789103</v>
+        <v>0.9121714838650443</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3104507630442387</v>
+        <v>-0.7933724643384455</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2755852777374428</v>
+        <v>-1.353976378872652</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4919185703677594</v>
+        <v>0.2092706182527805</v>
       </c>
       <c r="G106" t="n">
         <v>2.428389608256134</v>
@@ -3091,19 +3091,19 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.3563718128130419</v>
+        <v>-1.360558816998082</v>
       </c>
       <c r="C107" t="n">
-        <v>0.3463527287197254</v>
+        <v>-0.910537857825419</v>
       </c>
       <c r="D107" t="n">
-        <v>0.2841766635638849</v>
+        <v>-0.9456069335605172</v>
       </c>
       <c r="E107" t="n">
-        <v>0.2479091528859042</v>
+        <v>-1.576440884683023</v>
       </c>
       <c r="F107" t="n">
-        <v>0.4643361686496821</v>
+        <v>0.02075406377236158</v>
       </c>
       <c r="G107" t="n">
         <v>1.699146526632239</v>
@@ -3116,19 +3116,19 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7155209006446386</v>
+        <v>3.216623186227426</v>
       </c>
       <c r="C108" t="n">
-        <v>0.4137512079913956</v>
+        <v>-0.4311546262664994</v>
       </c>
       <c r="D108" t="n">
-        <v>0.1759645421401741</v>
+        <v>-1.572597589535271</v>
       </c>
       <c r="E108" t="n">
-        <v>0.4654397507719003</v>
+        <v>0.1721000406428136</v>
       </c>
       <c r="F108" t="n">
-        <v>0.5847611166626696</v>
+        <v>0.8438185853079608</v>
       </c>
       <c r="G108" t="n">
         <v>2.355437518210778</v>
@@ -3141,19 +3141,19 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5744726564412542</v>
+        <v>1.419031303557776</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3501485248877357</v>
+        <v>-0.8835396072265423</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2256883819980622</v>
+        <v>-1.284493238932921</v>
       </c>
       <c r="E109" t="n">
-        <v>0.3534649135491815</v>
+        <v>-0.727969133042968</v>
       </c>
       <c r="F109" t="n">
-        <v>0.547381950376567</v>
+        <v>0.5883443989180057</v>
       </c>
       <c r="G109" t="n">
         <v>2.0511564272528</v>
@@ -3166,19 +3166,19 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5839016940452877</v>
+        <v>1.539199842727658</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3379666080710051</v>
+        <v>-0.9701855777780007</v>
       </c>
       <c r="D110" t="n">
-        <v>0.8377669859084637</v>
+        <v>2.261944630732623</v>
       </c>
       <c r="E110" t="n">
-        <v>0.4215550513523665</v>
+        <v>-0.1806512213699573</v>
       </c>
       <c r="F110" t="n">
-        <v>0.5500758731296302</v>
+        <v>0.6067564661714181</v>
       </c>
       <c r="G110" t="n">
         <v>2.731266212506753</v>
@@ -3191,19 +3191,19 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4891807436025299</v>
+        <v>0.3320269878203992</v>
       </c>
       <c r="C111" t="n">
-        <v>0.2318739731466595</v>
+        <v>-1.724787621091628</v>
       </c>
       <c r="D111" t="n">
-        <v>0.8697147900844762</v>
+        <v>2.447053049583766</v>
       </c>
       <c r="E111" t="n">
-        <v>0.4179826210464498</v>
+        <v>-0.2093669085122475</v>
       </c>
       <c r="F111" t="n">
-        <v>0.3628574459917824</v>
+        <v>-0.6728193002905415</v>
       </c>
       <c r="G111" t="n">
         <v>2.371609573871898</v>
@@ -3216,19 +3216,19 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6969720372659843</v>
+        <v>2.980226863603674</v>
       </c>
       <c r="C112" t="n">
-        <v>0.5971616891982594</v>
+        <v>0.8733838460084996</v>
       </c>
       <c r="D112" t="n">
-        <v>0.1406066536294704</v>
+        <v>-1.777464340316397</v>
       </c>
       <c r="E112" t="n">
-        <v>0.2569317939229557</v>
+        <v>-1.503915652549578</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4980453040658325</v>
+        <v>0.2511448081360659</v>
       </c>
       <c r="G112" t="n">
         <v>2.189717478082502</v>
@@ -3241,19 +3241,19 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6956384936740742</v>
+        <v>2.963231493334849</v>
       </c>
       <c r="C113" t="n">
-        <v>0.5840147588560505</v>
+        <v>0.7798740514161859</v>
       </c>
       <c r="D113" t="n">
-        <v>0.3056464189352709</v>
+        <v>-0.8212092614068203</v>
       </c>
       <c r="E113" t="n">
-        <v>0.300554034197845</v>
+        <v>-1.153274073312916</v>
       </c>
       <c r="F113" t="n">
-        <v>0.5600968456065467</v>
+        <v>0.675246484669455</v>
       </c>
       <c r="G113" t="n">
         <v>2.445950551269787</v>
@@ -3266,19 +3266,19 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.2854478843478387</v>
+        <v>-2.264450097716577</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1243806599717083</v>
+        <v>-2.489352228448325</v>
       </c>
       <c r="D114" t="n">
-        <v>0.8095796148110737</v>
+        <v>2.098624495594011</v>
       </c>
       <c r="E114" t="n">
-        <v>0.4304213574156738</v>
+        <v>-0.10938263130116</v>
       </c>
       <c r="F114" t="n">
-        <v>0.455599499226133</v>
+        <v>-0.03895816992636211</v>
       </c>
       <c r="G114" t="n">
         <v>2.105429015772428</v>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.3993729810191778</v>
+        <v>-0.8125296561302462</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2674033135749317</v>
+        <v>-1.472079099865078</v>
       </c>
       <c r="D115" t="n">
-        <v>0.2295492820007124</v>
+        <v>-1.26212284092699</v>
       </c>
       <c r="E115" t="n">
-        <v>0.3059264883287745</v>
+        <v>-1.110089546590431</v>
       </c>
       <c r="F115" t="n">
-        <v>0.5104225059758862</v>
+        <v>0.3357388722078157</v>
       </c>
       <c r="G115" t="n">
         <v>1.712674570899483</v>
@@ -3316,19 +3316,19 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4765965222968032</v>
+        <v>0.1716471532704986</v>
       </c>
       <c r="C116" t="n">
-        <v>0.2562881308230359</v>
+        <v>-1.55113774161119</v>
       </c>
       <c r="D116" t="n">
-        <v>0.8723671399685544</v>
+        <v>2.462421000713577</v>
       </c>
       <c r="E116" t="n">
-        <v>0.5020770720289359</v>
+        <v>0.4665958781700509</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4289731823171606</v>
+        <v>-0.2209402022920736</v>
       </c>
       <c r="G116" t="n">
         <v>2.53630204743449</v>
@@ -3341,19 +3341,19 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6964607095991011</v>
+        <v>2.97371023896531</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1441042804406857</v>
+        <v>-2.349064598510147</v>
       </c>
       <c r="D117" t="n">
-        <v>0.04160603370047374</v>
+        <v>-2.351082737354753</v>
       </c>
       <c r="E117" t="n">
-        <v>0.635051376724824</v>
+        <v>1.535461665498797</v>
       </c>
       <c r="F117" t="n">
-        <v>0.9444986096343727</v>
+        <v>3.302504865988261</v>
       </c>
       <c r="G117" t="n">
         <v>2.461721010099457</v>
@@ -3366,19 +3366,19 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5334138276350805</v>
+        <v>0.8957563220736062</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1965259812455559</v>
+        <v>-1.976206269847286</v>
       </c>
       <c r="D118" t="n">
-        <v>0.8117628853166764</v>
+        <v>2.111274559084756</v>
       </c>
       <c r="E118" t="n">
-        <v>0.5573093194247272</v>
+        <v>0.9105602947064138</v>
       </c>
       <c r="F118" t="n">
-        <v>0.4682578813161113</v>
+        <v>0.04755766728354271</v>
       </c>
       <c r="G118" t="n">
         <v>2.567269894938152</v>
@@ -3391,19 +3391,19 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4043580809091811</v>
+        <v>-0.7489969610075358</v>
       </c>
       <c r="C119" t="n">
-        <v>0.05773011068954566</v>
+        <v>-2.963415679810057</v>
       </c>
       <c r="D119" t="n">
-        <v>0.7887574063130198</v>
+        <v>1.977978767617577</v>
       </c>
       <c r="E119" t="n">
-        <v>0.5722130561270371</v>
+        <v>1.030358584314974</v>
       </c>
       <c r="F119" t="n">
-        <v>0.380130985878913</v>
+        <v>-0.5547603924229295</v>
       </c>
       <c r="G119" t="n">
         <v>2.203189639917697</v>
@@ -3416,19 +3416,19 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.819192150054835</v>
+        <v>4.537863287148288</v>
       </c>
       <c r="C120" t="n">
-        <v>0.425569284939153</v>
+        <v>-0.3470965291217281</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2695155386315724</v>
+        <v>-1.030554795386875</v>
       </c>
       <c r="E120" t="n">
-        <v>0.6126507337388672</v>
+        <v>1.355402209977573</v>
       </c>
       <c r="F120" t="n">
-        <v>0.3561952360685213</v>
+        <v>-0.7183532923190646</v>
       </c>
       <c r="G120" t="n">
         <v>2.483122943432949</v>
@@ -3441,19 +3441,19 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4717255147443736</v>
+        <v>0.1095685099940603</v>
       </c>
       <c r="C121" t="n">
-        <v>0.05427899458633971</v>
+        <v>-2.987962334392148</v>
       </c>
       <c r="D121" t="n">
-        <v>0.04608331001076411</v>
+        <v>-2.325141000201505</v>
       </c>
       <c r="E121" t="n">
-        <v>0.4816008485980839</v>
+        <v>0.3020051722514078</v>
       </c>
       <c r="F121" t="n">
-        <v>0.3659027748235287</v>
+        <v>-0.6520054892059023</v>
       </c>
       <c r="G121" t="n">
         <v>1.41959144276309</v>
@@ -3466,19 +3466,19 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7953765230546896</v>
+        <v>4.234344600914814</v>
       </c>
       <c r="C122" t="n">
-        <v>0.4793204333014424</v>
+        <v>0.03521772307458364</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3420129237483332</v>
+        <v>-0.6104984980629383</v>
       </c>
       <c r="E122" t="n">
-        <v>0.5650726691106428</v>
+        <v>0.9729631694070708</v>
       </c>
       <c r="F122" t="n">
-        <v>0.3827377467330399</v>
+        <v>-0.5369440477986557</v>
       </c>
       <c r="G122" t="n">
         <v>2.564520295948148</v>
@@ -3491,19 +3491,19 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5814791967287359</v>
+        <v>1.50832628214832</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1612369147423414</v>
+        <v>-2.227205801614457</v>
       </c>
       <c r="D123" t="n">
-        <v>0.2144909309848214</v>
+        <v>-1.349372266011108</v>
       </c>
       <c r="E123" t="n">
-        <v>0.5490185233303936</v>
+        <v>0.8439177330835586</v>
       </c>
       <c r="F123" t="n">
-        <v>0.3762649263005941</v>
+        <v>-0.5811836255615815</v>
       </c>
       <c r="G123" t="n">
         <v>1.882490492086886</v>
@@ -3516,19 +3516,19 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6503937151874452</v>
+        <v>2.386608600933051</v>
       </c>
       <c r="C124" t="n">
-        <v>0.2999013011128034</v>
+        <v>-1.24093159544928</v>
       </c>
       <c r="D124" t="n">
-        <v>0.264758514944662</v>
+        <v>-1.058117413721145</v>
       </c>
       <c r="E124" t="n">
-        <v>0.4244477245862459</v>
+        <v>-0.1573995152551072</v>
       </c>
       <c r="F124" t="n">
-        <v>0.4115933424348047</v>
+        <v>-0.3397256353204008</v>
       </c>
       <c r="G124" t="n">
         <v>2.051094598265961</v>
@@ -3541,19 +3541,19 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5803593991080923</v>
+        <v>1.494055001250989</v>
       </c>
       <c r="C125" t="n">
-        <v>0.2020676724513447</v>
+        <v>-1.936790041658746</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1061010730730266</v>
+        <v>-1.977392743005802</v>
       </c>
       <c r="E125" t="n">
-        <v>0.5732369081796355</v>
+        <v>1.038588448218466</v>
       </c>
       <c r="F125" t="n">
-        <v>0.5689593944946789</v>
+        <v>0.7358190626987998</v>
       </c>
       <c r="G125" t="n">
         <v>2.030724447306778</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6469323701477642</v>
+        <v>2.342495426879799</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1231607992836273</v>
+        <v>-2.498028696597507</v>
       </c>
       <c r="D126" t="n">
-        <v>0.2219751424494691</v>
+        <v>-1.306008079135043</v>
       </c>
       <c r="E126" t="n">
-        <v>0.6340885310255909</v>
+        <v>1.527722179071396</v>
       </c>
       <c r="F126" t="n">
-        <v>0.3865678364895844</v>
+        <v>-0.5107666564447587</v>
       </c>
       <c r="G126" t="n">
         <v>2.012724679396036</v>
@@ -3591,19 +3591,19 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5441807557267831</v>
+        <v>1.032975630603418</v>
       </c>
       <c r="C127" t="n">
-        <v>0.06542277634092684</v>
+        <v>-2.908700277339375</v>
       </c>
       <c r="D127" t="n">
-        <v>0.7332544448199504</v>
+        <v>1.65638967226272</v>
       </c>
       <c r="E127" t="n">
-        <v>0.6475927864229288</v>
+        <v>1.636271245077607</v>
       </c>
       <c r="F127" t="n">
-        <v>0.4355170051382401</v>
+        <v>-0.176215346785682</v>
       </c>
       <c r="G127" t="n">
         <v>2.425967768448829</v>
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6409648891583338</v>
+        <v>2.266442758183566</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1896684850552454</v>
+        <v>-2.024981386432087</v>
       </c>
       <c r="D128" t="n">
-        <v>0.1299797974111829</v>
+        <v>-1.839037290403609</v>
       </c>
       <c r="E128" t="n">
-        <v>0.6162623351079122</v>
+        <v>1.384432759523746</v>
       </c>
       <c r="F128" t="n">
-        <v>0.38141107666838</v>
+        <v>-0.5460113970483075</v>
       </c>
       <c r="G128" t="n">
         <v>1.958286583401054</v>
@@ -3641,19 +3641,19 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>6.842172179612913</v>
       </c>
       <c r="C129" t="n">
-        <v>0.366168264723647</v>
+        <v>-0.7695964628965734</v>
       </c>
       <c r="D129" t="n">
-        <v>0.135528424889126</v>
+        <v>-1.806888049298418</v>
       </c>
       <c r="E129" t="n">
-        <v>0.720135279598009</v>
+        <v>2.219377802842296</v>
       </c>
       <c r="F129" t="n">
-        <v>0.3142494979944565</v>
+        <v>-1.005038480131347</v>
       </c>
       <c r="G129" t="n">
         <v>2.536081467205239</v>
@@ -3666,19 +3666,19 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6129199325717485</v>
+        <v>1.909023305041172</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2827375665096362</v>
+        <v>-1.363011598568051</v>
       </c>
       <c r="D130" t="n">
-        <v>0.3011023939117666</v>
+        <v>-0.8475377465410968</v>
       </c>
       <c r="E130" t="n">
-        <v>0.54371601662123</v>
+        <v>0.8012954533772055</v>
       </c>
       <c r="F130" t="n">
-        <v>0.3557975193424806</v>
+        <v>-0.7210715540432888</v>
       </c>
       <c r="G130" t="n">
         <v>2.096273428956862</v>
@@ -3691,19 +3691,19 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6066125644216813</v>
+        <v>1.828638938318954</v>
       </c>
       <c r="C131" t="n">
-        <v>0.4144332042102474</v>
+        <v>-0.4263038113098841</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2410311398037424</v>
+        <v>-1.195595935613467</v>
       </c>
       <c r="E131" t="n">
-        <v>0.2956770362485693</v>
+        <v>-1.192476054964748</v>
       </c>
       <c r="F131" t="n">
-        <v>0.4288370086037299</v>
+        <v>-0.2218709043944195</v>
       </c>
       <c r="G131" t="n">
         <v>1.98659095328797</v>
@@ -3716,19 +3716,19 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.6276808832828212</v>
+        <v>2.097144506609979</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1908195161578669</v>
+        <v>-2.016794480502424</v>
       </c>
       <c r="D132" t="n">
-        <v>0.07253916680002473</v>
+        <v>-2.171853412966033</v>
       </c>
       <c r="E132" t="n">
-        <v>0.5858995751382194</v>
+        <v>1.140372710368378</v>
       </c>
       <c r="F132" t="n">
-        <v>0.3734411824253433</v>
+        <v>-0.6004829770661529</v>
       </c>
       <c r="G132" t="n">
         <v>1.850380323804276</v>
@@ -3741,19 +3741,19 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.2544203614970008</v>
+        <v>-2.659880920205858</v>
       </c>
       <c r="C133" t="n">
-        <v>0.5561563520250102</v>
+        <v>0.5817263597017146</v>
       </c>
       <c r="D133" t="n">
-        <v>0.4864025328400706</v>
+        <v>0.2261077391060719</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5233052694389956</v>
+        <v>0.6372310545687212</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4171668114818138</v>
+        <v>-0.3016328255649398</v>
       </c>
       <c r="G133" t="n">
         <v>2.237451327282891</v>
@@ -3766,19 +3766,19 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.3412524375397968</v>
+        <v>-1.55324796683983</v>
       </c>
       <c r="C134" t="n">
-        <v>0.6374505489593454</v>
+        <v>1.159945263963395</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4587871736149449</v>
+        <v>0.0661018916304101</v>
       </c>
       <c r="E134" t="n">
-        <v>0.4983672271045696</v>
+        <v>0.436775633386527</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3862674890056118</v>
+        <v>-0.5128194317398215</v>
       </c>
       <c r="G134" t="n">
         <v>2.322124876224269</v>
@@ -3791,19 +3791,19 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4671316883107817</v>
+        <v>0.05102240646716513</v>
       </c>
       <c r="C135" t="n">
-        <v>0.8462082812769164</v>
+        <v>2.644770402642359</v>
       </c>
       <c r="D135" t="n">
-        <v>0.389260829541223</v>
+        <v>-0.3367399296441296</v>
       </c>
       <c r="E135" t="n">
-        <v>0.4642886994541112</v>
+        <v>0.1628477315154365</v>
       </c>
       <c r="F135" t="n">
-        <v>0.3545958855777686</v>
+        <v>-0.7292843217125511</v>
       </c>
       <c r="G135" t="n">
         <v>2.521485384160801</v>
@@ -3816,19 +3816,19 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4308467308940567</v>
+        <v>-0.4114118853150632</v>
       </c>
       <c r="C136" t="n">
-        <v>0.7973251537487782</v>
+        <v>2.297080782692796</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3919894735823928</v>
+        <v>-0.3209299233824855</v>
       </c>
       <c r="E136" t="n">
-        <v>0.4592818709797844</v>
+        <v>0.1226021542103289</v>
       </c>
       <c r="F136" t="n">
-        <v>0.2865886251252523</v>
+        <v>-1.194091358866186</v>
       </c>
       <c r="G136" t="n">
         <v>2.366031854330265</v>
@@ -3841,19 +3841,19 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5866444800740396</v>
+        <v>1.574155328554725</v>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>3.738640352011697</v>
       </c>
       <c r="D137" t="n">
-        <v>0.389433082366882</v>
+        <v>-0.3357418814520001</v>
       </c>
       <c r="E137" t="n">
-        <v>0.496846883944973</v>
+        <v>0.4245549055398301</v>
       </c>
       <c r="F137" t="n">
-        <v>0.3058491041119691</v>
+        <v>-1.062452382198005</v>
       </c>
       <c r="G137" t="n">
         <v>2.778773550497863</v>
@@ -3866,19 +3866,19 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.2381751941025895</v>
+        <v>-2.86691774796456</v>
       </c>
       <c r="C138" t="n">
-        <v>0.5579190477234698</v>
+        <v>0.5942638348690173</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4606774770798889</v>
+        <v>0.07705447803092877</v>
       </c>
       <c r="E138" t="n">
-        <v>0.4434452651463867</v>
+        <v>-0.004694666039584187</v>
       </c>
       <c r="F138" t="n">
-        <v>0.5231708020045504</v>
+        <v>0.4228692413244797</v>
       </c>
       <c r="G138" t="n">
         <v>2.223387786056885</v>
@@ -3891,19 +3891,19 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.3356494109262725</v>
+        <v>-1.624655840193646</v>
       </c>
       <c r="C139" t="n">
-        <v>0.7300656900907722</v>
+        <v>1.818686323504345</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4309644998360873</v>
+        <v>-0.09510515480824508</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4263411003965865</v>
+        <v>-0.1421802995513126</v>
       </c>
       <c r="F139" t="n">
-        <v>0.4047800563901776</v>
+        <v>-0.3862921824597976</v>
       </c>
       <c r="G139" t="n">
         <v>2.327800757639896</v>
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.470208063593527</v>
+        <v>0.09022932653583574</v>
       </c>
       <c r="C140" t="n">
-        <v>0.8719927416615398</v>
+        <v>2.828166794916441</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4680082306397742</v>
+        <v>0.1195295161581694</v>
       </c>
       <c r="E140" t="n">
-        <v>0.5077256001912253</v>
+        <v>0.5119995260044338</v>
       </c>
       <c r="F140" t="n">
-        <v>0.4936646946103053</v>
+        <v>0.2212047974901072</v>
       </c>
       <c r="G140" t="n">
         <v>2.811599330696371</v>
@@ -3941,19 +3941,19 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4933865970793254</v>
+        <v>0.3856285630281259</v>
       </c>
       <c r="C141" t="n">
-        <v>0.8810332524590305</v>
+        <v>2.89246897692229</v>
       </c>
       <c r="D141" t="n">
-        <v>0.5397169527797219</v>
+        <v>0.5350162300503305</v>
       </c>
       <c r="E141" t="n">
-        <v>0.4956365951492913</v>
+        <v>0.4148264374011926</v>
       </c>
       <c r="F141" t="n">
-        <v>0.285636884225848</v>
+        <v>-1.200596191800883</v>
       </c>
       <c r="G141" t="n">
         <v>2.695410281693217</v>
@@ -3966,19 +3966,19 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.3067491798423038</v>
+        <v>-1.992975354535908</v>
       </c>
       <c r="C142" t="n">
-        <v>0.6176346785065769</v>
+        <v>1.019001490209825</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4324828272045291</v>
+        <v>-0.08630783099461956</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4774960096057458</v>
+        <v>0.2690099107124406</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3023737845981285</v>
+        <v>-1.086205036776972</v>
       </c>
       <c r="G142" t="n">
         <v>2.136736479757284</v>
@@ -3991,19 +3991,19 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4273731240932176</v>
+        <v>-0.4556813296037188</v>
       </c>
       <c r="C143" t="n">
-        <v>0.7951204776476718</v>
+        <v>2.281399646184818</v>
       </c>
       <c r="D143" t="n">
-        <v>0.388542554485775</v>
+        <v>-0.3409016791991754</v>
       </c>
       <c r="E143" t="n">
-        <v>0.5275536660901464</v>
+        <v>0.6713802523539808</v>
       </c>
       <c r="F143" t="n">
-        <v>0.8162924654769743</v>
+        <v>2.426258453264439</v>
       </c>
       <c r="G143" t="n">
         <v>2.954882287793785</v>
@@ -4016,19 +4016,19 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.3170710232588159</v>
+        <v>-1.861428435646548</v>
       </c>
       <c r="C144" t="n">
-        <v>0.5724960596840994</v>
+        <v>0.6979453299958206</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3428406995291626</v>
+        <v>-0.6057022915659784</v>
       </c>
       <c r="E144" t="n">
-        <v>0.5579741394822614</v>
+        <v>0.9159042099526967</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2015297404169004</v>
+        <v>-1.775440584254941</v>
       </c>
       <c r="G144" t="n">
         <v>1.991911662371239</v>
@@ -4041,19 +4041,19 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5636516603651477</v>
+        <v>1.28112292462921</v>
       </c>
       <c r="C145" t="n">
-        <v>0.9684163502568556</v>
+        <v>3.513996231819244</v>
       </c>
       <c r="D145" t="n">
-        <v>0.3724129698716405</v>
+        <v>-0.434357927027624</v>
       </c>
       <c r="E145" t="n">
-        <v>0.4952420431931891</v>
+        <v>0.4116549744018875</v>
       </c>
       <c r="F145" t="n">
-        <v>0.4247052308547814</v>
+        <v>-0.2501102329732696</v>
       </c>
       <c r="G145" t="n">
         <v>2.824428254541614</v>
@@ -4066,19 +4066,19 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4001025986666719</v>
+        <v>-0.8032310309116535</v>
       </c>
       <c r="C146" t="n">
-        <v>0.7679841163510293</v>
+        <v>2.088387627045643</v>
       </c>
       <c r="D146" t="n">
-        <v>0.3227979021794732</v>
+        <v>-0.7218320420275312</v>
       </c>
       <c r="E146" t="n">
-        <v>0.5321674440284923</v>
+        <v>0.7084664352816403</v>
       </c>
       <c r="F146" t="n">
-        <v>0.9692453361367768</v>
+        <v>3.471640522215216</v>
       </c>
       <c r="G146" t="n">
         <v>2.992297397362443</v>
@@ -4091,19 +4091,19 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.1381793102341842</v>
+        <v>-4.141317086697408</v>
       </c>
       <c r="C147" t="n">
-        <v>0.4484389135806176</v>
+        <v>-0.1844323770344575</v>
       </c>
       <c r="D147" t="n">
-        <v>0.3644770344831516</v>
+        <v>-0.4803394424950003</v>
       </c>
       <c r="E147" t="n">
-        <v>0.4425531900013611</v>
+        <v>-0.01186528899884616</v>
       </c>
       <c r="F147" t="n">
-        <v>0.4696021838684143</v>
+        <v>0.05674552872975166</v>
       </c>
       <c r="G147" t="n">
         <v>1.863250632167729</v>
@@ -4116,19 +4116,19 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4630562696194199</v>
+        <v>-0.0009168402738896204</v>
       </c>
       <c r="C148" t="n">
-        <v>0.836022752643399</v>
+        <v>2.572324085095787</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4045274592150128</v>
+        <v>-0.2482837194917268</v>
       </c>
       <c r="E148" t="n">
-        <v>0.5274960891575111</v>
+        <v>0.6709174410343501</v>
       </c>
       <c r="F148" t="n">
-        <v>0.8212827687821422</v>
+        <v>2.460365518868009</v>
       </c>
       <c r="G148" t="n">
         <v>3.052385339417484</v>
@@ -4141,19 +4141,19 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.1089880224808929</v>
+        <v>-4.513345977991692</v>
       </c>
       <c r="C149" t="n">
-        <v>0.4423351006893577</v>
+        <v>-0.2278467920222016</v>
       </c>
       <c r="D149" t="n">
-        <v>0.5100504640388254</v>
+        <v>0.3631259557317028</v>
       </c>
       <c r="E149" t="n">
-        <v>0.381257393834241</v>
+        <v>-0.5045693462221438</v>
       </c>
       <c r="F149" t="n">
-        <v>0.6795732758109243</v>
+        <v>1.491828202025415</v>
       </c>
       <c r="G149" t="n">
         <v>2.122204256854241</v>
@@ -4166,19 +4166,19 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.208742307656846</v>
+        <v>-3.242025698135956</v>
       </c>
       <c r="C150" t="n">
-        <v>0.3716774863633721</v>
+        <v>-0.7304111800598454</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4410036804921725</v>
+        <v>-0.03693724919662139</v>
       </c>
       <c r="E150" t="n">
-        <v>0.5640676320858971</v>
+        <v>0.9648845432904982</v>
       </c>
       <c r="F150" t="n">
-        <v>0.4524193407814736</v>
+        <v>-0.060693496632741</v>
       </c>
       <c r="G150" t="n">
         <v>2.037910447379761</v>
@@ -4191,19 +4191,19 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.3728010279715752</v>
+        <v>-1.151176389202471</v>
       </c>
       <c r="C151" t="n">
-        <v>0.5094848195288758</v>
+        <v>0.2497670883415908</v>
       </c>
       <c r="D151" t="n">
-        <v>0.3759499706963677</v>
+        <v>-0.4138642296663495</v>
       </c>
       <c r="E151" t="n">
-        <v>0.7357783871585788</v>
+        <v>2.345119257307775</v>
       </c>
       <c r="F151" t="n">
-        <v>0.3599440014579943</v>
+        <v>-0.6927317260028962</v>
       </c>
       <c r="G151" t="n">
         <v>2.353958206813392</v>
@@ -4216,19 +4216,19 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.271696815698637</v>
+        <v>-2.439700839201843</v>
       </c>
       <c r="C152" t="n">
-        <v>0.4944110004536251</v>
+        <v>0.1425519674914449</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4418523875329522</v>
+        <v>-0.03201976511787162</v>
       </c>
       <c r="E152" t="n">
-        <v>0.5513697836534377</v>
+        <v>0.8628174876049537</v>
       </c>
       <c r="F152" t="n">
-        <v>0.4544936593220696</v>
+        <v>-0.04651621837521624</v>
       </c>
       <c r="G152" t="n">
         <v>2.213823646660722</v>
@@ -4241,19 +4241,19 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.2607747623033463</v>
+        <v>-2.578897144950596</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5926706541324308</v>
+        <v>0.8414405896299196</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4212841293235138</v>
+        <v>-0.1511940825355887</v>
       </c>
       <c r="E153" t="n">
-        <v>0.4200903835591986</v>
+        <v>-0.1924244229482608</v>
       </c>
       <c r="F153" t="n">
-        <v>0.4201568025142052</v>
+        <v>-0.2811972299589065</v>
       </c>
       <c r="G153" t="n">
         <v>2.114976731832695</v>
@@ -4266,19 +4266,19 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.1935015870237865</v>
+        <v>-3.43626133609625</v>
       </c>
       <c r="C154" t="n">
-        <v>0.4399687942354072</v>
+        <v>-0.2446775521077678</v>
       </c>
       <c r="D154" t="n">
-        <v>0.5576156513591051</v>
+        <v>0.6387228815394025</v>
       </c>
       <c r="E154" t="n">
-        <v>0.5126825549159777</v>
+        <v>0.551844211236988</v>
       </c>
       <c r="F154" t="n">
-        <v>0.5207094493962823</v>
+        <v>0.406046713764525</v>
       </c>
       <c r="G154" t="n">
         <v>2.224478036930559</v>
@@ -4291,19 +4291,19 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.2465351855808285</v>
+        <v>-2.760373686353978</v>
       </c>
       <c r="C155" t="n">
-        <v>0.6083277810930987</v>
+        <v>0.9528045877563314</v>
       </c>
       <c r="D155" t="n">
-        <v>0.3449573468191118</v>
+        <v>-0.5934382489122353</v>
       </c>
       <c r="E155" t="n">
-        <v>0.4786081606726637</v>
+        <v>0.2779495342621806</v>
       </c>
       <c r="F155" t="n">
-        <v>0.6822249116624723</v>
+        <v>1.50995125235221</v>
       </c>
       <c r="G155" t="n">
         <v>2.360653385828175</v>
@@ -4316,19 +4316,19 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.3523957575541509</v>
+        <v>-1.411231724688604</v>
       </c>
       <c r="C156" t="n">
-        <v>0.6076986464554137</v>
+        <v>0.9483297598528198</v>
       </c>
       <c r="D156" t="n">
-        <v>0.3511652277875954</v>
+        <v>-0.5574692344484831</v>
       </c>
       <c r="E156" t="n">
-        <v>0.4821255628408479</v>
+        <v>0.3062228976495382</v>
       </c>
       <c r="F156" t="n">
-        <v>0.532639436762946</v>
+        <v>0.4875842149707524</v>
       </c>
       <c r="G156" t="n">
         <v>2.326024631400954</v>
@@ -4341,19 +4341,19 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.2605961286726086</v>
+        <v>-2.581173744467304</v>
       </c>
       <c r="C157" t="n">
-        <v>0.6504124138009956</v>
+        <v>1.25213874847473</v>
       </c>
       <c r="D157" t="n">
-        <v>0.357355481720337</v>
+        <v>-0.5216023525975783</v>
       </c>
       <c r="E157" t="n">
-        <v>0.4344043266380442</v>
+        <v>-0.07736697576897676</v>
       </c>
       <c r="F157" t="n">
-        <v>0.4578061531152816</v>
+        <v>-0.02387642351555256</v>
       </c>
       <c r="G157" t="n">
         <v>2.160574503947267</v>
@@ -4366,19 +4366,19 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.3553918595208428</v>
+        <v>-1.373047849338763</v>
       </c>
       <c r="C158" t="n">
-        <v>0.6705968300910684</v>
+        <v>1.395703867641043</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4897926461495559</v>
+        <v>0.2457503571397776</v>
       </c>
       <c r="E158" t="n">
-        <v>0.4783614763139313</v>
+        <v>0.2759666513892742</v>
       </c>
       <c r="F158" t="n">
-        <v>0.402148571874845</v>
+        <v>-0.4042775050966564</v>
       </c>
       <c r="G158" t="n">
         <v>2.396291383950244</v>
@@ -4391,19 +4391,19 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.3763106900196464</v>
+        <v>-1.106447438167609</v>
       </c>
       <c r="C159" t="n">
-        <v>0.6373599866468866</v>
+        <v>1.159301123999511</v>
       </c>
       <c r="D159" t="n">
-        <v>0.473374189921472</v>
+        <v>0.1506203614877049</v>
       </c>
       <c r="E159" t="n">
-        <v>0.5130976889249589</v>
+        <v>0.5551811156139007</v>
       </c>
       <c r="F159" t="n">
-        <v>0.4353044170404594</v>
+        <v>-0.1776683158246657</v>
       </c>
       <c r="G159" t="n">
         <v>2.435446972553423</v>
@@ -4416,19 +4416,19 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.2123779860428469</v>
+        <v>-3.195690729618029</v>
       </c>
       <c r="C160" t="n">
-        <v>0.5422080833277145</v>
+        <v>0.4825169087612939</v>
       </c>
       <c r="D160" t="n">
-        <v>0.5120110889706962</v>
+        <v>0.3744859909660251</v>
       </c>
       <c r="E160" t="n">
-        <v>0.4509436596858644</v>
+        <v>0.0555784626785556</v>
       </c>
       <c r="F160" t="n">
-        <v>0.5094324518779902</v>
+        <v>0.3289721812868349</v>
       </c>
       <c r="G160" t="n">
         <v>2.226973269905113</v>
@@ -4441,19 +4441,19 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.1877017000476571</v>
+        <v>-3.510178099878564</v>
       </c>
       <c r="C161" t="n">
-        <v>0.4655041575168747</v>
+        <v>-0.06305290565901274</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4817703950445548</v>
+        <v>0.1992687207339622</v>
       </c>
       <c r="E161" t="n">
-        <v>0.4814775628893654</v>
+        <v>0.3010141847338035</v>
       </c>
       <c r="F161" t="n">
-        <v>0.4577168136068571</v>
+        <v>-0.02448702938226801</v>
       </c>
       <c r="G161" t="n">
         <v>2.074170629105309</v>
@@ -4466,19 +4466,19 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.2432389548156956</v>
+        <v>-2.802382558568401</v>
       </c>
       <c r="C162" t="n">
-        <v>0.5475103983506402</v>
+        <v>0.5202305328356266</v>
       </c>
       <c r="D162" t="n">
-        <v>0.5054394726994904</v>
+        <v>0.3364094618074827</v>
       </c>
       <c r="E162" t="n">
-        <v>0.4961326308460055</v>
+        <v>0.4188136406937694</v>
       </c>
       <c r="F162" t="n">
-        <v>0.4243516535610464</v>
+        <v>-0.2525268163382256</v>
       </c>
       <c r="G162" t="n">
         <v>2.216673110272878</v>
@@ -4491,19 +4491,19 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.3072129890873857</v>
+        <v>-1.987064329278024</v>
       </c>
       <c r="C163" t="n">
-        <v>0.7037647680193277</v>
+        <v>1.631616508994628</v>
       </c>
       <c r="D163" t="n">
-        <v>0.2628840749636071</v>
+        <v>-1.068978085685103</v>
       </c>
       <c r="E163" t="n">
-        <v>0.4097468488637814</v>
+        <v>-0.2755671803498808</v>
       </c>
       <c r="F163" t="n">
-        <v>0.3512333013197996</v>
+        <v>-0.7522664682617017</v>
       </c>
       <c r="G163" t="n">
         <v>2.034841982253901</v>
@@ -4516,19 +4516,19 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.1682082824285766</v>
+        <v>-3.758612310991614</v>
       </c>
       <c r="C164" t="n">
-        <v>0.4883376607465896</v>
+        <v>0.09935429824762962</v>
       </c>
       <c r="D164" t="n">
-        <v>0.3655090408931761</v>
+        <v>-0.4743599055680986</v>
       </c>
       <c r="E164" t="n">
-        <v>0.4484778247187972</v>
+        <v>0.03575774137811578</v>
       </c>
       <c r="F164" t="n">
-        <v>0.4917373475281424</v>
+        <v>0.2080320203356396</v>
       </c>
       <c r="G164" t="n">
         <v>1.962270156315282</v>
@@ -4541,19 +4541,19 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.2218652722189683</v>
+        <v>-3.074779840474537</v>
       </c>
       <c r="C165" t="n">
-        <v>0.565108462632697</v>
+        <v>0.6453997802115087</v>
       </c>
       <c r="D165" t="n">
-        <v>0.3018137179550667</v>
+        <v>-0.8434162717686631</v>
       </c>
       <c r="E165" t="n">
-        <v>0.4893026795479938</v>
+        <v>0.3639135508736945</v>
       </c>
       <c r="F165" t="n">
-        <v>0.6213889412428641</v>
+        <v>1.094157600689859</v>
       </c>
       <c r="G165" t="n">
         <v>2.19947907359759</v>
@@ -4566,19 +4566,19 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.09521620160643515</v>
+        <v>-4.68886119658462</v>
       </c>
       <c r="C166" t="n">
-        <v>0.360838579694665</v>
+        <v>-0.8075047608284311</v>
       </c>
       <c r="D166" t="n">
-        <v>0.3344429215243607</v>
+        <v>-0.6543597642288085</v>
       </c>
       <c r="E166" t="n">
-        <v>0.4777134687342678</v>
+        <v>0.2707578771571686</v>
       </c>
       <c r="F166" t="n">
-        <v>0.7118508234353724</v>
+        <v>1.712434519322673</v>
       </c>
       <c r="G166" t="n">
         <v>1.980061994995101</v>
@@ -4591,19 +4591,19 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.1346860015721782</v>
+        <v>-4.185837621709718</v>
       </c>
       <c r="C167" t="n">
-        <v>0.3585778262707434</v>
+        <v>-0.8235847569029561</v>
       </c>
       <c r="D167" t="n">
-        <v>0.3293875031947677</v>
+        <v>-0.6836513076621652</v>
       </c>
       <c r="E167" t="n">
-        <v>0.484952423083475</v>
+        <v>0.3289455898705217</v>
       </c>
       <c r="F167" t="n">
-        <v>0.4414015686806901</v>
+        <v>-0.1359963094813013</v>
       </c>
       <c r="G167" t="n">
         <v>1.749005322801854</v>
@@ -4616,19 +4616,19 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.2128048173086937</v>
+        <v>-3.190250970880944</v>
       </c>
       <c r="C168" t="n">
-        <v>0.5772518883305402</v>
+        <v>0.7317719760849947</v>
       </c>
       <c r="D168" t="n">
-        <v>0.336264435840338</v>
+        <v>-0.6438057482755478</v>
       </c>
       <c r="E168" t="n">
-        <v>0.427663818640653</v>
+        <v>-0.1315481080118148</v>
       </c>
       <c r="F168" t="n">
-        <v>0.5356494830172995</v>
+        <v>0.5081568813577235</v>
       </c>
       <c r="G168" t="n">
         <v>2.089634443137524</v>
@@ -4641,19 +4641,19 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.08567860057850921</v>
+        <v>-4.810413324261017</v>
       </c>
       <c r="C169" t="n">
-        <v>0.4065899360207095</v>
+        <v>-0.4820904001367389</v>
       </c>
       <c r="D169" t="n">
-        <v>0.3401720405270007</v>
+        <v>-0.6211647391765079</v>
       </c>
       <c r="E169" t="n">
-        <v>0.4224357515237662</v>
+        <v>-0.1735720320163709</v>
       </c>
       <c r="F169" t="n">
-        <v>0.5856717489409903</v>
+        <v>0.850042454471434</v>
       </c>
       <c r="G169" t="n">
         <v>1.840548077590976</v>
@@ -4666,19 +4666,19 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.4262559701409802</v>
+        <v>-0.469918918221544</v>
       </c>
       <c r="C170" t="n">
-        <v>0.8123680146659075</v>
+        <v>2.404075708339076</v>
       </c>
       <c r="D170" t="n">
-        <v>0.3662247092409417</v>
+        <v>-0.470213259509207</v>
       </c>
       <c r="E170" t="n">
-        <v>0.4985875038250041</v>
+        <v>0.4385462480233608</v>
       </c>
       <c r="F170" t="n">
-        <v>0.2898708399800031</v>
+        <v>-1.17165851049401</v>
       </c>
       <c r="G170" t="n">
         <v>2.393307037852836</v>
@@ -4691,19 +4691,19 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.5073771297041378</v>
+        <v>0.5639311574533636</v>
       </c>
       <c r="C171" t="n">
-        <v>0.9165246489772899</v>
+        <v>3.144907615587742</v>
       </c>
       <c r="D171" t="n">
-        <v>0.3671166097429411</v>
+        <v>-0.4650455086744995</v>
       </c>
       <c r="E171" t="n">
-        <v>0.5307838197517414</v>
+        <v>0.697344672657509</v>
       </c>
       <c r="F171" t="n">
-        <v>0.9109474257459375</v>
+        <v>3.07319366785422</v>
       </c>
       <c r="G171" t="n">
         <v>3.232749633922047</v>
@@ -4716,19 +4716,19 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.1868758580787397</v>
+        <v>-3.520703057690538</v>
       </c>
       <c r="C172" t="n">
-        <v>0.5184533233839834</v>
+        <v>0.3135571086324083</v>
       </c>
       <c r="D172" t="n">
-        <v>0.2350835012416746</v>
+        <v>-1.230057082428342</v>
       </c>
       <c r="E172" t="n">
-        <v>0.3746999595870045</v>
+        <v>-0.5572789064304755</v>
       </c>
       <c r="F172" t="n">
-        <v>0.4989023702609824</v>
+        <v>0.2570025709125904</v>
       </c>
       <c r="G172" t="n">
         <v>1.814015012552385</v>
@@ -4741,19 +4741,19 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.2272012259688956</v>
+        <v>-3.00677568202972</v>
       </c>
       <c r="C173" t="n">
-        <v>0.5710865065096054</v>
+        <v>0.6879196415360052</v>
       </c>
       <c r="D173" t="n">
-        <v>0.2750601227041709</v>
+        <v>-0.9984289821318733</v>
       </c>
       <c r="E173" t="n">
-        <v>0.4346845044169773</v>
+        <v>-0.07511486816851831</v>
       </c>
       <c r="F173" t="n">
-        <v>0.5279123433652489</v>
+        <v>0.4552761016617888</v>
       </c>
       <c r="G173" t="n">
         <v>2.035944702964898</v>
@@ -4766,19 +4766,19 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.2658518123620932</v>
+        <v>-2.51419258925013</v>
       </c>
       <c r="C174" t="n">
-        <v>0.7163591403387138</v>
+        <v>1.721196139976914</v>
       </c>
       <c r="D174" t="n">
-        <v>0.2324282485395706</v>
+        <v>-1.245441852743973</v>
       </c>
       <c r="E174" t="n">
-        <v>0.416813884138678</v>
+        <v>-0.2187613768492899</v>
       </c>
       <c r="F174" t="n">
-        <v>0.9502781173816847</v>
+        <v>3.342005881826272</v>
       </c>
       <c r="G174" t="n">
         <v>2.58173120276074</v>
@@ -4791,19 +4791,19 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.1848056866515554</v>
+        <v>-3.54708639464208</v>
       </c>
       <c r="C175" t="n">
-        <v>0.4226389385447735</v>
+        <v>-0.3679391199235528</v>
       </c>
       <c r="D175" t="n">
-        <v>0.3499346013169683</v>
+        <v>-0.5645995936718938</v>
       </c>
       <c r="E175" t="n">
-        <v>0.5424472754850664</v>
+        <v>0.7910971372700197</v>
       </c>
       <c r="F175" t="n">
-        <v>0.4570106230391723</v>
+        <v>-0.02931360735713913</v>
       </c>
       <c r="G175" t="n">
         <v>1.956837125037536</v>
@@ -4816,19 +4816,19 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.1407896294823314</v>
+        <v>-4.108049826135982</v>
       </c>
       <c r="C176" t="n">
-        <v>0.475659701156313</v>
+        <v>0.009180138479683136</v>
       </c>
       <c r="D176" t="n">
-        <v>0.3524421125327902</v>
+        <v>-0.5500708506679908</v>
       </c>
       <c r="E176" t="n">
-        <v>0.4297881945961121</v>
+        <v>-0.1144720813057002</v>
       </c>
       <c r="F176" t="n">
-        <v>0.5228091805623424</v>
+        <v>0.4203976788765076</v>
       </c>
       <c r="G176" t="n">
         <v>1.921488818329889</v>
@@ -4841,19 +4841,19 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>-5.902345788846264</v>
       </c>
       <c r="C177" t="n">
-        <v>0.2605959723311836</v>
+        <v>-1.52049748079914</v>
       </c>
       <c r="D177" t="n">
-        <v>0.3915815243958138</v>
+        <v>-0.3232936172527501</v>
       </c>
       <c r="E177" t="n">
-        <v>0.4521156817091716</v>
+        <v>0.0649993372270171</v>
       </c>
       <c r="F177" t="n">
-        <v>0.5934093510114653</v>
+        <v>0.9029263946437102</v>
       </c>
       <c r="G177" t="n">
         <v>1.697702529447634</v>
@@ -4866,19 +4866,19 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.1523579861542184</v>
+        <v>-3.960616696665573</v>
       </c>
       <c r="C178" t="n">
-        <v>0.4785962151959065</v>
+        <v>0.03006659771482753</v>
       </c>
       <c r="D178" t="n">
-        <v>0.3660683219879844</v>
+        <v>-0.4711193811620099</v>
       </c>
       <c r="E178" t="n">
-        <v>0.4454430801764072</v>
+        <v>0.01136404650554766</v>
       </c>
       <c r="F178" t="n">
-        <v>0.4220676633913893</v>
+        <v>-0.2681371305397149</v>
       </c>
       <c r="G178" t="n">
         <v>1.864533266905906</v>
@@ -4891,19 +4891,19 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.2326825695404967</v>
+        <v>-2.936918600390152</v>
       </c>
       <c r="C179" t="n">
-        <v>0.4977908434553533</v>
+        <v>0.1665916799276767</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4873664076285927</v>
+        <v>0.2316925153583238</v>
       </c>
       <c r="E179" t="n">
-        <v>0.4498154128029679</v>
+        <v>0.04650945874169456</v>
       </c>
       <c r="F179" t="n">
-        <v>0.4889696012872223</v>
+        <v>0.1891153940625758</v>
       </c>
       <c r="G179" t="n">
         <v>2.156624834714633</v>
@@ -4916,19 +4916,19 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.2290101279497303</v>
+        <v>-2.983722098231791</v>
       </c>
       <c r="C180" t="n">
-        <v>0.5263857430900672</v>
+        <v>0.3699778028954989</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4196529322530281</v>
+        <v>-0.1606453834415504</v>
       </c>
       <c r="E180" t="n">
-        <v>0.4807027066273592</v>
+        <v>0.2947857833110621</v>
       </c>
       <c r="F180" t="n">
-        <v>0.6414509573146536</v>
+        <v>1.231274817110714</v>
       </c>
       <c r="G180" t="n">
         <v>2.297202467234839</v>
@@ -4941,19 +4941,19 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.265059381429541</v>
+        <v>-2.524291739508804</v>
       </c>
       <c r="C181" t="n">
-        <v>0.6084478435480961</v>
+        <v>0.9536585525384379</v>
       </c>
       <c r="D181" t="n">
-        <v>0.440806934619984</v>
+        <v>-0.03807721227876779</v>
       </c>
       <c r="E181" t="n">
-        <v>0.4549990148171163</v>
+        <v>0.08817596612237134</v>
       </c>
       <c r="F181" t="n">
-        <v>0.5376182232172589</v>
+        <v>0.5216125667239547</v>
       </c>
       <c r="G181" t="n">
         <v>2.306931397631996</v>
@@ -4966,19 +4966,19 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.3051765417845858</v>
+        <v>-2.013017868520377</v>
       </c>
       <c r="C182" t="n">
-        <v>0.6168109707877535</v>
+        <v>1.013142727929477</v>
       </c>
       <c r="D182" t="n">
-        <v>0.460095400298889</v>
+        <v>0.07368187339158484</v>
       </c>
       <c r="E182" t="n">
-        <v>0.5098221222185113</v>
+        <v>0.5288516589971349</v>
       </c>
       <c r="F182" t="n">
-        <v>0.3580485047696059</v>
+        <v>-0.7056868162947558</v>
       </c>
       <c r="G182" t="n">
         <v>2.249953539859346</v>
@@ -4991,19 +4991,19 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.2807177341978328</v>
+        <v>-2.324733581296837</v>
       </c>
       <c r="C183" t="n">
-        <v>0.6110652922305252</v>
+        <v>0.9722756047535895</v>
       </c>
       <c r="D183" t="n">
-        <v>0.459904603575957</v>
+        <v>0.0725763802093511</v>
       </c>
       <c r="E183" t="n">
-        <v>0.4853337074242649</v>
+        <v>0.3320104059494367</v>
       </c>
       <c r="F183" t="n">
-        <v>0.4466660097809278</v>
+        <v>-0.1000156031009907</v>
       </c>
       <c r="G183" t="n">
         <v>2.283687347209508</v>
@@ -5016,19 +5016,19 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.2914659890925675</v>
+        <v>-2.187752253661311</v>
       </c>
       <c r="C184" t="n">
-        <v>0.5775632142418805</v>
+        <v>0.7339863349705229</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4653767331401804</v>
+        <v>0.1042823855986838</v>
       </c>
       <c r="E184" t="n">
-        <v>0.5008355236333132</v>
+        <v>0.456616141058968</v>
       </c>
       <c r="F184" t="n">
-        <v>0.3958067885987502</v>
+        <v>-0.4476214874188126</v>
       </c>
       <c r="G184" t="n">
         <v>2.231048248706692</v>
@@ -5041,19 +5041,19 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.3587003693294156</v>
+        <v>-1.330882486634583</v>
       </c>
       <c r="C185" t="n">
-        <v>0.6512301012218443</v>
+        <v>1.257954690354242</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4606225018146716</v>
+        <v>0.07673594645472889</v>
       </c>
       <c r="E185" t="n">
-        <v>0.5192509194111519</v>
+        <v>0.6046416302846215</v>
       </c>
       <c r="F185" t="n">
-        <v>0.3648972434653446</v>
+        <v>-0.6588779620603112</v>
       </c>
       <c r="G185" t="n">
         <v>2.354701135242428</v>
@@ -5066,19 +5066,19 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.398642754755256</v>
+        <v>-0.8218360378718387</v>
       </c>
       <c r="C186" t="n">
-        <v>0.7381203637182031</v>
+        <v>1.875976569729429</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4984499985509311</v>
+        <v>0.2959118269430437</v>
       </c>
       <c r="E186" t="n">
-        <v>0.5104913571083995</v>
+        <v>0.5342310612743216</v>
       </c>
       <c r="F186" t="n">
-        <v>0.3677261921879342</v>
+        <v>-0.6395430371529254</v>
       </c>
       <c r="G186" t="n">
         <v>2.513430666320724</v>
@@ -5091,19 +5091,19 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.3058939786880471</v>
+        <v>-2.00387448101298</v>
       </c>
       <c r="C187" t="n">
-        <v>0.6354777360989823</v>
+        <v>1.145913294481564</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4840279216740929</v>
+        <v>0.2123490308111696</v>
       </c>
       <c r="E187" t="n">
-        <v>0.4952554742816276</v>
+        <v>0.4117629353417954</v>
       </c>
       <c r="F187" t="n">
-        <v>0.4122808100152912</v>
+        <v>-0.3350270227443484</v>
       </c>
       <c r="G187" t="n">
         <v>2.332935920758041</v>
@@ -5116,19 +5116,19 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.2704801807663645</v>
+        <v>-2.455206264957245</v>
       </c>
       <c r="C188" t="n">
-        <v>0.4990521957977148</v>
+        <v>0.1755632645769141</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4853134485411541</v>
+        <v>0.2197974878143911</v>
       </c>
       <c r="E188" t="n">
-        <v>0.5547159860535441</v>
+        <v>0.8897147236621819</v>
       </c>
       <c r="F188" t="n">
-        <v>0.6424842477783046</v>
+        <v>1.238337014231035</v>
       </c>
       <c r="G188" t="n">
         <v>2.452046058937082</v>
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.2794960448119774</v>
+        <v>-2.340303423626747</v>
       </c>
       <c r="C189" t="n">
-        <v>0.6365566232118295</v>
+        <v>1.153587063923145</v>
       </c>
       <c r="D189" t="n">
-        <v>0.5012080557356579</v>
+        <v>0.3118922555744778</v>
       </c>
       <c r="E189" t="n">
-        <v>0.4983230521849532</v>
+        <v>0.4364205492945742</v>
       </c>
       <c r="F189" t="n">
-        <v>0.3759866442311813</v>
+        <v>-0.5830855910769702</v>
       </c>
       <c r="G189" t="n">
         <v>2.291570420175599</v>
@@ -5166,19 +5166,19 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.4225491178900655</v>
+        <v>-0.5171609633397494</v>
       </c>
       <c r="C190" t="n">
-        <v>0.712579390219759</v>
+        <v>1.6943120196512</v>
       </c>
       <c r="D190" t="n">
-        <v>0.6201185503371184</v>
+        <v>1.000870237260326</v>
       </c>
       <c r="E190" t="n">
-        <v>0.5251790697726426</v>
+        <v>0.6522929198930111</v>
       </c>
       <c r="F190" t="n">
-        <v>0.3831595973532549</v>
+        <v>-0.5340608389236194</v>
       </c>
       <c r="G190" t="n">
         <v>2.66358572557284</v>
@@ -5191,19 +5191,19 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.2324285761957353</v>
+        <v>-2.940155623136333</v>
       </c>
       <c r="C191" t="n">
-        <v>0.4591711612737587</v>
+        <v>-0.1080974265040334</v>
       </c>
       <c r="D191" t="n">
-        <v>0.40915600235528</v>
+        <v>-0.2214655288718388</v>
       </c>
       <c r="E191" t="n">
-        <v>0.4920495726049761</v>
+        <v>0.3859934558355891</v>
       </c>
       <c r="F191" t="n">
-        <v>0.3727684725059258</v>
+        <v>-0.6050807259304319</v>
       </c>
       <c r="G191" t="n">
         <v>1.965573784935676</v>
@@ -5216,19 +5216,19 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.1409630775967931</v>
+        <v>-4.105839313524629</v>
       </c>
       <c r="C192" t="n">
-        <v>0.3522362163659798</v>
+        <v>-0.8686905438922697</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4143865641910386</v>
+        <v>-0.1911591883863978</v>
       </c>
       <c r="E192" t="n">
-        <v>0.4806992283263092</v>
+        <v>0.2947578242478518</v>
       </c>
       <c r="F192" t="n">
-        <v>0.4996803849859776</v>
+        <v>0.2623200431468876</v>
       </c>
       <c r="G192" t="n">
         <v>1.887965471466098</v>
@@ -5241,19 +5241,19 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.08989228701931627</v>
+        <v>-4.756711921702698</v>
       </c>
       <c r="C193" t="n">
-        <v>0.3088378220799602</v>
+        <v>-1.17736905892881</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4084468597966863</v>
+        <v>-0.2255743639278613</v>
       </c>
       <c r="E193" t="n">
-        <v>0.4452953699698398</v>
+        <v>0.01017673150811147</v>
       </c>
       <c r="F193" t="n">
-        <v>0.4300838115223777</v>
+        <v>-0.2133494205605597</v>
       </c>
       <c r="G193" t="n">
         <v>1.68255615038818</v>
@@ -5266,19 +5266,19 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.07212413227854479</v>
+        <v>-4.983158489062824</v>
       </c>
       <c r="C194" t="n">
-        <v>0.2650139389863997</v>
+        <v>-1.489073936010241</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4720543002247457</v>
+        <v>0.1429728031931556</v>
       </c>
       <c r="E194" t="n">
-        <v>0.4854230154784182</v>
+        <v>0.3327282763969321</v>
       </c>
       <c r="F194" t="n">
-        <v>0.4352238782656652</v>
+        <v>-0.1782187716001077</v>
       </c>
       <c r="G194" t="n">
         <v>1.729839265233774</v>
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.06656641423650279</v>
+        <v>-5.053988926513258</v>
       </c>
       <c r="C195" t="n">
-        <v>0.2685747563587534</v>
+        <v>-1.463747012355636</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4767018754778721</v>
+        <v>0.1699012675676762</v>
       </c>
       <c r="E195" t="n">
-        <v>0.4677475610056387</v>
+        <v>0.1906505373581875</v>
       </c>
       <c r="F195" t="n">
-        <v>0.3757644258559104</v>
+        <v>-0.5846043798639832</v>
       </c>
       <c r="G195" t="n">
         <v>1.655355032934677</v>
@@ -5316,19 +5316,19 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.268040109023083</v>
+        <v>-2.486303803133826</v>
       </c>
       <c r="C196" t="n">
-        <v>0.6146018592525765</v>
+        <v>0.9974300436367265</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4620218677661827</v>
+        <v>0.08484399723816416</v>
       </c>
       <c r="E196" t="n">
-        <v>0.421309954966668</v>
+        <v>-0.1826213398967675</v>
       </c>
       <c r="F196" t="n">
-        <v>0.3461110652924089</v>
+        <v>-0.7872752502013224</v>
       </c>
       <c r="G196" t="n">
         <v>2.112084856300919</v>
@@ -5341,19 +5341,19 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.3372087568856174</v>
+        <v>-1.604782727595732</v>
       </c>
       <c r="C197" t="n">
-        <v>0.7403528954991712</v>
+        <v>1.891855834533084</v>
       </c>
       <c r="D197" t="n">
-        <v>0.3802758251306891</v>
+        <v>-0.3887998443300119</v>
       </c>
       <c r="E197" t="n">
-        <v>0.3862424813193623</v>
+        <v>-0.4644985259845586</v>
       </c>
       <c r="F197" t="n">
-        <v>0.3549990841264211</v>
+        <v>-0.7265285935515164</v>
       </c>
       <c r="G197" t="n">
         <v>2.199079042961261</v>
@@ -5366,19 +5366,19 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.2426686628804868</v>
+        <v>-2.809650654383938</v>
       </c>
       <c r="C198" t="n">
-        <v>0.4935399726130457</v>
+        <v>0.1363566327375006</v>
       </c>
       <c r="D198" t="n">
-        <v>0.415783951907385</v>
+        <v>-0.1830625996734525</v>
       </c>
       <c r="E198" t="n">
-        <v>0.5005856599216519</v>
+        <v>0.4546077021090476</v>
       </c>
       <c r="F198" t="n">
-        <v>0.415487019873836</v>
+        <v>-0.3131136432768201</v>
       </c>
       <c r="G198" t="n">
         <v>2.068065267196406</v>
@@ -5391,19 +5391,19 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.2520134500369744</v>
+        <v>-2.690555846556655</v>
       </c>
       <c r="C199" t="n">
-        <v>0.5804986749188547</v>
+        <v>0.7548653019835587</v>
       </c>
       <c r="D199" t="n">
-        <v>0.3951970977094184</v>
+        <v>-0.3023446639026404</v>
       </c>
       <c r="E199" t="n">
-        <v>0.4617174914382964</v>
+        <v>0.1421800071269152</v>
       </c>
       <c r="F199" t="n">
-        <v>0.5738646882591513</v>
+        <v>0.769345116326919</v>
       </c>
       <c r="G199" t="n">
         <v>2.263291402362695</v>
@@ -5416,19 +5416,19 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.2566077735693703</v>
+        <v>-2.63200340774512</v>
       </c>
       <c r="C200" t="n">
-        <v>0.603074929859872</v>
+        <v>0.9154427833611247</v>
       </c>
       <c r="D200" t="n">
-        <v>0.3889613547643057</v>
+        <v>-0.3384751131370404</v>
       </c>
       <c r="E200" t="n">
-        <v>0.4295298150346844</v>
+        <v>-0.1165489718296747</v>
       </c>
       <c r="F200" t="n">
-        <v>0.5121516616374928</v>
+        <v>0.3475570768303943</v>
       </c>
       <c r="G200" t="n">
         <v>2.190325534865725</v>
@@ -5441,19 +5441,19 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.2726824197464834</v>
+        <v>-2.427139790704279</v>
       </c>
       <c r="C201" t="n">
-        <v>0.6337650931900197</v>
+        <v>1.133731828355369</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4174019447869897</v>
+        <v>-0.1736878050238442</v>
       </c>
       <c r="E201" t="n">
-        <v>0.4276418537562782</v>
+        <v>-0.1317246647795638</v>
       </c>
       <c r="F201" t="n">
-        <v>0.4597136362729676</v>
+        <v>-0.01083940968724928</v>
       </c>
       <c r="G201" t="n">
         <v>2.211204947752738</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.4245109017278926</v>
+        <v>-0.492158973968328</v>
       </c>
       <c r="C202" t="n">
-        <v>0.830568356786174</v>
+        <v>2.533528760030684</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4586528172403417</v>
+        <v>0.06532341884622925</v>
       </c>
       <c r="E202" t="n">
-        <v>0.4686040428727451</v>
+        <v>0.1975350566441591</v>
       </c>
       <c r="F202" t="n">
-        <v>0.3526873087041318</v>
+        <v>-0.7423288107261099</v>
       </c>
       <c r="G202" t="n">
         <v>2.535023427331285</v>
@@ -5491,19 +5491,19 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.3772331153593508</v>
+        <v>-1.094691571851184</v>
       </c>
       <c r="C203" t="n">
-        <v>0.791652672702895</v>
+        <v>2.256734289357667</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4448065066099691</v>
+        <v>-0.01490333644465504</v>
       </c>
       <c r="E203" t="n">
-        <v>0.4649500733529905</v>
+        <v>0.1681639460635104</v>
       </c>
       <c r="F203" t="n">
-        <v>0.4448149423657382</v>
+        <v>-0.1126670340673456</v>
       </c>
       <c r="G203" t="n">
         <v>2.523457310390944</v>
@@ -5516,19 +5516,19 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.3152621710244847</v>
+        <v>-1.884481385449269</v>
       </c>
       <c r="C204" t="n">
-        <v>0.6300470945975647</v>
+        <v>1.107286926342101</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4463123812793477</v>
+        <v>-0.006178164676951891</v>
       </c>
       <c r="E204" t="n">
-        <v>0.4728693297421642</v>
+        <v>0.2318200203316245</v>
       </c>
       <c r="F204" t="n">
-        <v>0.4422154239575018</v>
+        <v>-0.1304338789794753</v>
       </c>
       <c r="G204" t="n">
         <v>2.306706400601063</v>
@@ -5541,19 +5541,19 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.3135983895263618</v>
+        <v>-1.905685478647686</v>
       </c>
       <c r="C205" t="n">
-        <v>0.6185465476509819</v>
+        <v>1.025487315734785</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4771581834812556</v>
+        <v>0.172545156723566</v>
       </c>
       <c r="E205" t="n">
-        <v>0.4452708158142999</v>
+        <v>0.009979361821890246</v>
       </c>
       <c r="F205" t="n">
-        <v>0.502854131114961</v>
+        <v>0.2840115438054184</v>
       </c>
       <c r="G205" t="n">
         <v>2.35742806758786</v>
@@ -5566,19 +5566,19 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.06871854814852803</v>
+        <v>-5.026561017200922</v>
       </c>
       <c r="C206" t="n">
-        <v>0.1724858096868598</v>
+        <v>-2.147196108988696</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4366418250292004</v>
+        <v>-0.0622102276949129</v>
       </c>
       <c r="E206" t="n">
-        <v>0.5209571937133598</v>
+        <v>0.6183568982801889</v>
       </c>
       <c r="F206" t="n">
-        <v>0.2991811796695282</v>
+        <v>-1.108025431067092</v>
       </c>
       <c r="G206" t="n">
         <v>1.497984556247476</v>
@@ -5591,19 +5591,19 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.3483699510660835</v>
+        <v>-1.462538687813318</v>
       </c>
       <c r="C207" t="n">
-        <v>0.7001245106575487</v>
+        <v>1.60572455480436</v>
       </c>
       <c r="D207" t="n">
-        <v>0.3986302869257625</v>
+        <v>-0.2824524602333997</v>
       </c>
       <c r="E207" t="n">
-        <v>0.457608883717609</v>
+        <v>0.1091544520300793</v>
       </c>
       <c r="F207" t="n">
-        <v>0.376233090119818</v>
+        <v>-0.5814012152830668</v>
       </c>
       <c r="G207" t="n">
         <v>2.280966722486821</v>
@@ -5616,19 +5616,19 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.282007038554539</v>
+        <v>-2.308302018755982</v>
       </c>
       <c r="C208" t="n">
-        <v>0.6154034604025812</v>
+        <v>1.003131569158714</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4412563675427896</v>
+        <v>-0.0354731579512202</v>
       </c>
       <c r="E208" t="n">
-        <v>0.4832161081895049</v>
+        <v>0.3149888514582518</v>
       </c>
       <c r="F208" t="n">
-        <v>0.3488418834856404</v>
+        <v>-0.7686110148688693</v>
       </c>
       <c r="G208" t="n">
         <v>2.170724858175055</v>
@@ -5641,19 +5641,19 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.2524135962685387</v>
+        <v>-2.685456175718473</v>
       </c>
       <c r="C209" t="n">
-        <v>0.5254974249028412</v>
+        <v>0.3636594875885844</v>
       </c>
       <c r="D209" t="n">
-        <v>0.3832391393539261</v>
+        <v>-0.3716301381617754</v>
       </c>
       <c r="E209" t="n">
-        <v>0.4932008128328307</v>
+        <v>0.3952472834481091</v>
       </c>
       <c r="F209" t="n">
-        <v>0.4295216536481244</v>
+        <v>-0.2171915829150729</v>
       </c>
       <c r="G209" t="n">
         <v>2.083872627006261</v>
@@ -5666,19 +5666,19 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.2336334190291227</v>
+        <v>-2.924800481997058</v>
       </c>
       <c r="C210" t="n">
-        <v>0.5163819878358257</v>
+        <v>0.298824379653224</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4120434256491056</v>
+        <v>-0.2047355414983923</v>
       </c>
       <c r="E210" t="n">
-        <v>0.481384459508262</v>
+        <v>0.3002658069252208</v>
       </c>
       <c r="F210" t="n">
-        <v>0.3204697634741563</v>
+        <v>-0.962525031586438</v>
       </c>
       <c r="G210" t="n">
         <v>1.963913055496472</v>
@@ -5691,19 +5691,19 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.1508320697173837</v>
+        <v>-3.98006376611318</v>
       </c>
       <c r="C211" t="n">
-        <v>0.3401432117119216</v>
+        <v>-0.9547041114529285</v>
       </c>
       <c r="D211" t="n">
-        <v>0.4595089520625604</v>
+        <v>0.07028394015126727</v>
       </c>
       <c r="E211" t="n">
-        <v>0.4852841580118419</v>
+        <v>0.3316121209436056</v>
       </c>
       <c r="F211" t="n">
-        <v>0.3139230705622976</v>
+        <v>-1.007269503210028</v>
       </c>
       <c r="G211" t="n">
         <v>1.749691462066005</v>
@@ -5716,19 +5716,19 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.2016424749625816</v>
+        <v>-3.332509643481063</v>
       </c>
       <c r="C212" t="n">
-        <v>0.3888042133875201</v>
+        <v>-0.6085943996875534</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4564012075977475</v>
+        <v>0.05227739231763506</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5127327830639198</v>
+        <v>0.5522479520124634</v>
       </c>
       <c r="F212" t="n">
-        <v>0.2640718585320458</v>
+        <v>-1.347985979776195</v>
       </c>
       <c r="G212" t="n">
         <v>1.823652537543815</v>
@@ -5741,19 +5741,19 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.235112078278759</v>
+        <v>-2.905955682620839</v>
       </c>
       <c r="C213" t="n">
-        <v>0.4816737302232406</v>
+        <v>0.05195595063372497</v>
       </c>
       <c r="D213" t="n">
-        <v>0.437680251149061</v>
+        <v>-0.0561934943982489</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5186062015990544</v>
+        <v>0.599459299657599</v>
       </c>
       <c r="F213" t="n">
-        <v>0.3014644800703582</v>
+        <v>-1.092419831206434</v>
       </c>
       <c r="G213" t="n">
         <v>1.974536741320473</v>
@@ -5766,19 +5766,19 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.3778319621353156</v>
+        <v>-1.087059558354548</v>
       </c>
       <c r="C214" t="n">
-        <v>0.7052528390632292</v>
+        <v>1.642200669253487</v>
       </c>
       <c r="D214" t="n">
-        <v>0.4444717209958516</v>
+        <v>-0.01684311406886916</v>
       </c>
       <c r="E214" t="n">
-        <v>0.5179109324617324</v>
+        <v>0.5938706305115669</v>
       </c>
       <c r="F214" t="n">
-        <v>0.4078730691565153</v>
+        <v>-0.3651524675200444</v>
       </c>
       <c r="G214" t="n">
         <v>2.453340523812644</v>
@@ -5791,19 +5791,19 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.2146276827543537</v>
+        <v>-3.167019429454647</v>
       </c>
       <c r="C215" t="n">
-        <v>0.4905527966743298</v>
+        <v>0.1151098320646766</v>
       </c>
       <c r="D215" t="n">
-        <v>0.45678267211198</v>
+        <v>0.05448763164076208</v>
       </c>
       <c r="E215" t="n">
-        <v>0.5203593278017669</v>
+        <v>0.6135511696864331</v>
       </c>
       <c r="F215" t="n">
-        <v>0.3422804681982539</v>
+        <v>-0.813456109039279</v>
       </c>
       <c r="G215" t="n">
         <v>2.024602947540684</v>
@@ -5816,19 +5816,19 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.1868678074395999</v>
+        <v>-3.520805659205713</v>
       </c>
       <c r="C216" t="n">
-        <v>0.5115589970868325</v>
+        <v>0.2645200316024076</v>
       </c>
       <c r="D216" t="n">
-        <v>0.4114782013360573</v>
+        <v>-0.2080105014395562</v>
       </c>
       <c r="E216" t="n">
-        <v>0.4815668087881392</v>
+        <v>0.3017315555677913</v>
       </c>
       <c r="F216" t="n">
-        <v>0.410191279105563</v>
+        <v>-0.3493082724922306</v>
       </c>
       <c r="G216" t="n">
         <v>2.001663093756192</v>
@@ -5841,19 +5841,19 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.3550358274620459</v>
+        <v>-1.377585306309448</v>
       </c>
       <c r="C217" t="n">
-        <v>0.7317580553485201</v>
+        <v>1.830723561361999</v>
       </c>
       <c r="D217" t="n">
-        <v>0.4426684444754861</v>
+        <v>-0.02729145861227524</v>
       </c>
       <c r="E217" t="n">
-        <v>0.4827034973952568</v>
+        <v>0.3108684152473591</v>
       </c>
       <c r="F217" t="n">
-        <v>0.4559956168515474</v>
+        <v>-0.0362508375237905</v>
       </c>
       <c r="G217" t="n">
         <v>2.468161441532856</v>
@@ -5866,19 +5866,19 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.1779409329907097</v>
+        <v>-3.634574371021774</v>
       </c>
       <c r="C218" t="n">
-        <v>0.3880760033303961</v>
+        <v>-0.6137739184869415</v>
       </c>
       <c r="D218" t="n">
-        <v>0.3490290499232579</v>
+        <v>-0.5698464389872923</v>
       </c>
       <c r="E218" t="n">
-        <v>0.4668088778224345</v>
+        <v>0.1831052725646437</v>
       </c>
       <c r="F218" t="n">
-        <v>0.3372265473069909</v>
+        <v>-0.8479979797137639</v>
       </c>
       <c r="G218" t="n">
         <v>1.719081411373789</v>
@@ -5891,19 +5891,19 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.2361145999896068</v>
+        <v>-2.893179026663169</v>
       </c>
       <c r="C219" t="n">
-        <v>0.5018991103299165</v>
+        <v>0.1958124319641756</v>
       </c>
       <c r="D219" t="n">
-        <v>0.3831814890115057</v>
+        <v>-0.3719641693732126</v>
       </c>
       <c r="E219" t="n">
-        <v>0.4582629696004738</v>
+        <v>0.1144120845010132</v>
       </c>
       <c r="F219" t="n">
-        <v>0.5138836760132525</v>
+        <v>0.3593948198147103</v>
       </c>
       <c r="G219" t="n">
         <v>2.093341844944755</v>
@@ -5916,19 +5916,19 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.4182169638066665</v>
+        <v>-0.5723721788977614</v>
       </c>
       <c r="C220" t="n">
-        <v>0.7992003819160949</v>
+        <v>2.310418664325629</v>
       </c>
       <c r="D220" t="n">
-        <v>0.6758760648418746</v>
+        <v>1.323934235404981</v>
       </c>
       <c r="E220" t="n">
-        <v>0.6255221851617148</v>
+        <v>1.458864710425384</v>
       </c>
       <c r="F220" t="n">
-        <v>0.4001020783515729</v>
+        <v>-0.4182646086026177</v>
       </c>
       <c r="G220" t="n">
         <v>2.918917674077924</v>
@@ -5941,19 +5941,19 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.5688988326557041</v>
+        <v>1.347995606169807</v>
       </c>
       <c r="C221" t="n">
-        <v>0.9508253203478138</v>
+        <v>3.388877017626667</v>
       </c>
       <c r="D221" t="n">
-        <v>0.4893176035464733</v>
+        <v>0.2429979180469656</v>
       </c>
       <c r="E221" t="n">
-        <v>0.5399677975801482</v>
+        <v>0.7711667521548982</v>
       </c>
       <c r="F221" t="n">
-        <v>0.3086791843266006</v>
+        <v>-1.043109723918329</v>
       </c>
       <c r="G221" t="n">
         <v>2.857688738456741</v>
@@ -5966,19 +5966,19 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.6192192838779915</v>
+        <v>1.989305500953223</v>
       </c>
       <c r="C222" t="n">
-        <v>0.4906597672668175</v>
+        <v>0.115870678731585</v>
       </c>
       <c r="D222" t="n">
-        <v>0.6283238568180597</v>
+        <v>1.048412512795384</v>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>4.468968995683205</v>
       </c>
       <c r="F222" t="n">
-        <v>0.2969084132078498</v>
+        <v>-1.123559034952408</v>
       </c>
       <c r="G222" t="n">
         <v>3.035111321170719</v>
@@ -5991,19 +5991,19 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.4248179261674954</v>
+        <v>-0.4882460954810556</v>
       </c>
       <c r="C223" t="n">
-        <v>0.8082516259482172</v>
+        <v>2.374797188301778</v>
       </c>
       <c r="D223" t="n">
-        <v>0.5989022301140617</v>
+        <v>0.8779409908967105</v>
       </c>
       <c r="E223" t="n">
-        <v>0.5867831827342153</v>
+        <v>1.147475270001562</v>
       </c>
       <c r="F223" t="n">
-        <v>0.3653320574293619</v>
+        <v>-0.655906153036052</v>
       </c>
       <c r="G223" t="n">
         <v>2.784087022393352</v>
@@ -6016,19 +6016,19 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.6245990521195686</v>
+        <v>2.057868053974148</v>
       </c>
       <c r="C224" t="n">
-        <v>0.9272890782070158</v>
+        <v>3.221471462810959</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4256417908896859</v>
+        <v>-0.1259454038483644</v>
       </c>
       <c r="E224" t="n">
-        <v>0.5797237447425392</v>
+        <v>1.090730534510535</v>
       </c>
       <c r="F224" t="n">
-        <v>0.3213662500470058</v>
+        <v>-0.9563978436214826</v>
       </c>
       <c r="G224" t="n">
         <v>2.878619916005815</v>
@@ -6041,19 +6041,19 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.2512154326087934</v>
+        <v>-2.700726194009252</v>
       </c>
       <c r="C225" t="n">
-        <v>0.5399745325352203</v>
+        <v>0.4666303960635669</v>
       </c>
       <c r="D225" t="n">
-        <v>0.4627884183456831</v>
+        <v>0.08928545947322115</v>
       </c>
       <c r="E225" t="n">
-        <v>0.5102773844495231</v>
+        <v>0.5325111195530996</v>
       </c>
       <c r="F225" t="n">
-        <v>0.4945223921991618</v>
+        <v>0.2270668756329048</v>
       </c>
       <c r="G225" t="n">
         <v>2.258778160138382</v>
@@ -6066,19 +6066,19 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.5716251258835774</v>
+        <v>1.382740899199727</v>
       </c>
       <c r="C226" t="n">
-        <v>0.7631301894487509</v>
+        <v>2.053863240304131</v>
       </c>
       <c r="D226" t="n">
-        <v>0.5784025780778975</v>
+        <v>0.7591641837488152</v>
       </c>
       <c r="E226" t="n">
-        <v>0.9557272924072273</v>
+        <v>4.113098870499632</v>
       </c>
       <c r="F226" t="n">
-        <v>0.2558588985768082</v>
+        <v>-1.404118833204703</v>
       </c>
       <c r="G226" t="n">
         <v>3.124744084394261</v>
@@ -6091,19 +6091,19 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.5221085043788396</v>
+        <v>0.751675426695204</v>
       </c>
       <c r="C227" t="n">
-        <v>0.7553621744720782</v>
+        <v>1.998611902847312</v>
       </c>
       <c r="D227" t="n">
-        <v>0.407072192905268</v>
+        <v>-0.2335393061603699</v>
       </c>
       <c r="E227" t="n">
-        <v>0.5467060663945901</v>
+        <v>0.8253298855365894</v>
       </c>
       <c r="F227" t="n">
-        <v>0</v>
+        <v>-3.152829423596941</v>
       </c>
       <c r="G227" t="n">
         <v>2.231248938150776</v>
@@ -6116,19 +6116,19 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.5408296386864688</v>
+        <v>0.9902672592687232</v>
       </c>
       <c r="C228" t="n">
-        <v>0.9395089289547327</v>
+        <v>3.308387244945979</v>
       </c>
       <c r="D228" t="n">
-        <v>0.4987083101161232</v>
+        <v>0.2974085071261394</v>
       </c>
       <c r="E228" t="n">
-        <v>0.5100398145084318</v>
+        <v>0.5306014996253184</v>
       </c>
       <c r="F228" t="n">
-        <v>0.2726721214950831</v>
+        <v>-1.289206038928812</v>
       </c>
       <c r="G228" t="n">
         <v>2.76175881376084</v>
@@ -6141,19 +6141,19 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.3646860607290272</v>
+        <v>-1.254597735038583</v>
       </c>
       <c r="C229" t="n">
-        <v>0.6261505446070396</v>
+        <v>1.079572046917901</v>
       </c>
       <c r="D229" t="n">
-        <v>0.4696965368577231</v>
+        <v>0.129311712543852</v>
       </c>
       <c r="E229" t="n">
-        <v>0.552381269604404</v>
+        <v>0.8709479510792628</v>
       </c>
       <c r="F229" t="n">
-        <v>0.3827890185058271</v>
+        <v>-0.5365936222611427</v>
       </c>
       <c r="G229" t="n">
         <v>2.395703430304021</v>
@@ -6166,19 +6166,19 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.2941176784090271</v>
+        <v>-2.15395775152092</v>
       </c>
       <c r="C230" t="n">
-        <v>0.6129973684613884</v>
+        <v>0.986017827978479</v>
       </c>
       <c r="D230" t="n">
-        <v>0.490711863121258</v>
+        <v>0.2510763820294841</v>
       </c>
       <c r="E230" t="n">
-        <v>0.4855938665327031</v>
+        <v>0.3341016007175349</v>
       </c>
       <c r="F230" t="n">
-        <v>0.3397056083934357</v>
+        <v>-0.8310544205871934</v>
       </c>
       <c r="G230" t="n">
         <v>2.223126384917812</v>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.3133673978823705</v>
+        <v>-1.908629355805097</v>
       </c>
       <c r="C231" t="n">
-        <v>0.3870000273540503</v>
+        <v>-0.6214269819713759</v>
       </c>
       <c r="D231" t="n">
-        <v>0.3946022389423063</v>
+        <v>-0.3057913285063547</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6462142951592343</v>
+        <v>1.625190742319843</v>
       </c>
       <c r="F231" t="n">
-        <v>0.3699383224177243</v>
+        <v>-0.6244238617727518</v>
       </c>
       <c r="G231" t="n">
         <v>2.111122281755686</v>
@@ -6216,19 +6216,19 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.649379010409445</v>
+        <v>2.373676677657147</v>
       </c>
       <c r="C232" t="n">
-        <v>0.889267526655467</v>
+        <v>2.951036662966345</v>
       </c>
       <c r="D232" t="n">
-        <v>0.5879062992908778</v>
+        <v>0.8142295897230301</v>
       </c>
       <c r="E232" t="n">
-        <v>0.7337509993188622</v>
+        <v>2.328822834442656</v>
       </c>
       <c r="F232" t="n">
-        <v>0.302029449336873</v>
+        <v>-1.088558453919593</v>
       </c>
       <c r="G232" t="n">
         <v>3.162333285011525</v>
@@ -6241,19 +6241,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.2788733721751365</v>
+        <v>-2.348239086235433</v>
       </c>
       <c r="C233" t="n">
-        <v>0.4918840494978706</v>
+        <v>0.1245785958627225</v>
       </c>
       <c r="D233" t="n">
-        <v>0.4234772177116315</v>
+        <v>-0.1384871333603442</v>
       </c>
       <c r="E233" t="n">
-        <v>0.5930481878495744</v>
+        <v>1.197834244546017</v>
       </c>
       <c r="F233" t="n">
-        <v>0.3102738424467273</v>
+        <v>-1.032210765319538</v>
       </c>
       <c r="G233" t="n">
         <v>2.09755666968094</v>
@@ -6266,19 +6266,19 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.4142555485967008</v>
+        <v>-0.6228585062216963</v>
       </c>
       <c r="C234" t="n">
-        <v>0.7896911826970081</v>
+        <v>2.242782855618303</v>
       </c>
       <c r="D234" t="n">
-        <v>0.3292291024079723</v>
+        <v>-0.6845690959091115</v>
       </c>
       <c r="E234" t="n">
-        <v>0.5159588919543439</v>
+        <v>0.5781798598878798</v>
       </c>
       <c r="F234" t="n">
-        <v>0.8776809367945191</v>
+        <v>2.84582826505566</v>
       </c>
       <c r="G234" t="n">
         <v>2.926815662450544</v>
@@ -6291,19 +6291,19 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.4038542082182854</v>
+        <v>-0.755418575570471</v>
       </c>
       <c r="C235" t="n">
-        <v>0.7667095077809323</v>
+        <v>2.079321755205378</v>
       </c>
       <c r="D235" t="n">
-        <v>0.3981621350645452</v>
+        <v>-0.2851649737549776</v>
       </c>
       <c r="E235" t="n">
-        <v>0.4946684742248205</v>
+        <v>0.4070445479863124</v>
       </c>
       <c r="F235" t="n">
-        <v>0.6978335280245669</v>
+        <v>1.616630960916539</v>
       </c>
       <c r="G235" t="n">
         <v>2.76122785331315</v>
@@ -6316,19 +6316,19 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.4149598379345008</v>
+        <v>-0.6138826781011105</v>
       </c>
       <c r="C236" t="n">
-        <v>0.8229620343245406</v>
+        <v>2.479427488290719</v>
       </c>
       <c r="D236" t="n">
-        <v>0.53995855022922</v>
+        <v>0.536416067160533</v>
       </c>
       <c r="E236" t="n">
-        <v>0.4793895173920875</v>
+        <v>0.2842301872575205</v>
       </c>
       <c r="F236" t="n">
-        <v>0.5606721641398377</v>
+        <v>0.6791785957572891</v>
       </c>
       <c r="G236" t="n">
         <v>2.817942104020186</v>
@@ -6341,19 +6341,19 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.4143646465443926</v>
+        <v>-0.6214681054670167</v>
       </c>
       <c r="C237" t="n">
-        <v>0.7778475415219213</v>
+        <v>2.158542928526597</v>
       </c>
       <c r="D237" t="n">
-        <v>0.3592896198391997</v>
+        <v>-0.5103957843135772</v>
       </c>
       <c r="E237" t="n">
-        <v>0.5417945584480232</v>
+        <v>0.7858505077704507</v>
       </c>
       <c r="F237" t="n">
-        <v>0.9597483543529494</v>
+        <v>3.406731806065343</v>
       </c>
       <c r="G237" t="n">
         <v>3.053044720706486</v>

--- a/results/01_pollution_assessment/artifacts/SumRel_01_updated_data.xlsx
+++ b/results/01_pollution_assessment/artifacts/SumRel_01_updated_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -544,16 +544,16 @@
         <v>0.1461630171032758</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2830717709267092</v>
+        <v>-0.2830717709267113</v>
       </c>
       <c r="D5" t="n">
         <v>2.763479807123514</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.159931038013033</v>
+        <v>-1.159931038013035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4481559725105925</v>
+        <v>0.4481559725105921</v>
       </c>
       <c r="G5" t="n">
         <v>2.660090922031275</v>
@@ -566,22 +566,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2.61842307096378</v>
+        <v>-2.618423070963779</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.166129328688029</v>
+        <v>-2.166129328688025</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.182851566076757</v>
+        <v>-1.182851566076756</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.21295224057067</v>
+        <v>-2.212952240570672</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2280902140263398</v>
+        <v>-0.2280902140263392</v>
       </c>
       <c r="G6" t="n">
-        <v>1.267377728946281</v>
+        <v>1.267377728946282</v>
       </c>
     </row>
     <row r="7">
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.94899418220281</v>
+        <v>-1.948994182202809</v>
       </c>
       <c r="C7" t="n">
         <v>-1.925284433762951</v>
       </c>
       <c r="D7" t="n">
-        <v>2.27731399542493</v>
+        <v>2.277313995424928</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8832640027353664</v>
+        <v>-0.8832640027353673</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1098273345114712</v>
+        <v>-0.1098273345114725</v>
       </c>
       <c r="G7" t="n">
         <v>2.133680624276793</v>
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.975472939029722</v>
+        <v>3.97547293902972</v>
       </c>
       <c r="C8" t="n">
-        <v>1.160291485359084</v>
+        <v>1.160291485359082</v>
       </c>
       <c r="D8" t="n">
         <v>2.931685290551719</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8363597358625144</v>
+        <v>-0.8363597358625162</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3156354404163368</v>
+        <v>0.3156354404163359</v>
       </c>
       <c r="G8" t="n">
         <v>3.213382159378861</v>
@@ -641,19 +641,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.158486857018305</v>
+        <v>-1.158486857018304</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.517311159518486</v>
+        <v>-1.517311159518487</v>
       </c>
       <c r="D9" t="n">
-        <v>2.689290658553455</v>
+        <v>2.689290658553454</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.289131891287967</v>
+        <v>-1.289131891287969</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2011033877524098</v>
+        <v>0.2011033877524087</v>
       </c>
       <c r="G9" t="n">
         <v>2.319169845368289</v>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.01182994612998662</v>
+        <v>-0.01182994612998619</v>
       </c>
       <c r="C10" t="n">
-        <v>-2.684591911729092</v>
+        <v>-2.684591911729093</v>
       </c>
       <c r="D10" t="n">
-        <v>1.72542878264095</v>
+        <v>1.725428782640946</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8106820869196382</v>
+        <v>0.8106820869196393</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7232573657160433</v>
+        <v>0.7232573657160435</v>
       </c>
       <c r="G10" t="n">
         <v>2.416306192148566</v>
@@ -691,22 +691,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1685092747940378</v>
+        <v>-0.168509274794038</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2339992025810342</v>
+        <v>-0.233999202581033</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.414281141650042</v>
+        <v>-0.4142811416500403</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.259369393840901</v>
+        <v>-2.259369393840903</v>
       </c>
       <c r="F11" t="n">
         <v>-0.4446788403161421</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8264396881881</v>
+        <v>1.826439688188101</v>
       </c>
     </row>
     <row r="12">
@@ -716,22 +716,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.8481886362914927</v>
+        <v>-0.8481886362914923</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.704637286806151</v>
+        <v>-1.704637286806149</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.721009913415572</v>
+        <v>-1.721009913415571</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8219106478881908</v>
+        <v>-0.8219106478881912</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02202355758647872</v>
+        <v>0.02202355758647974</v>
       </c>
       <c r="G12" t="n">
-        <v>1.587931943698385</v>
+        <v>1.587931943698386</v>
       </c>
     </row>
     <row r="13">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.7164653447894558</v>
+        <v>-0.7164653447894552</v>
       </c>
       <c r="C13" t="n">
         <v>-1.944336984631359</v>
       </c>
       <c r="D13" t="n">
-        <v>1.980082126228146</v>
+        <v>1.980082126228144</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6499989825683068</v>
+        <v>-0.6499989825683078</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3765148355833932</v>
+        <v>0.3765148355833927</v>
       </c>
       <c r="G13" t="n">
         <v>2.276591213569075</v>
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3562999044695216</v>
+        <v>0.3562999044695218</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.659126151170106</v>
+        <v>-1.659126151170107</v>
       </c>
       <c r="D14" t="n">
-        <v>2.170404167423368</v>
+        <v>2.170404167423365</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2646348156958178</v>
+        <v>-0.2646348156958182</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0150657937917144</v>
+        <v>0.01506579379171362</v>
       </c>
       <c r="G14" t="n">
-        <v>2.428769770649007</v>
+        <v>2.428769770649006</v>
       </c>
     </row>
     <row r="15">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7552322148557221</v>
+        <v>0.7552322148557223</v>
       </c>
       <c r="C15" t="n">
         <v>-1.614456959361735</v>
       </c>
       <c r="D15" t="n">
-        <v>1.872176383011477</v>
+        <v>1.872176383011475</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9181584723730878</v>
+        <v>0.9181584723730882</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04037724894114841</v>
+        <v>-0.04037724894114933</v>
       </c>
       <c r="G15" t="n">
         <v>2.553916868025238</v>
@@ -819,16 +819,16 @@
         <v>3.660881940237104</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.199794878257832</v>
+        <v>-1.199794878257831</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6150695869593756</v>
+        <v>-0.6150695869593791</v>
       </c>
       <c r="E16" t="n">
-        <v>3.247123106123325</v>
+        <v>3.247123106123329</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.30216719642931</v>
+        <v>-1.302167196429312</v>
       </c>
       <c r="G16" t="n">
         <v>2.516058244911793</v>
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-2.3649278791398</v>
+        <v>-2.364927879139799</v>
       </c>
       <c r="C17" t="n">
         <v>-3.031381304667946</v>
       </c>
       <c r="D17" t="n">
-        <v>1.782195423600141</v>
+        <v>1.782195423600139</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6723566193204957</v>
+        <v>-0.6723566193204962</v>
       </c>
       <c r="F17" t="n">
-        <v>0.298223176955328</v>
+        <v>0.2982231769553275</v>
       </c>
       <c r="G17" t="n">
         <v>1.946022617128232</v>
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8368269871156375</v>
+        <v>0.8368269871156374</v>
       </c>
       <c r="C18" t="n">
         <v>-1.076897913852441</v>
       </c>
       <c r="D18" t="n">
-        <v>2.331876477399435</v>
+        <v>2.331876477399433</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3182199128360695</v>
+        <v>-0.3182199128360703</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05340069262867814</v>
+        <v>0.05340069262867714</v>
       </c>
       <c r="G18" t="n">
         <v>2.575143254829423</v>
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.949847872202055</v>
+        <v>1.949847872202053</v>
       </c>
       <c r="C19" t="n">
-        <v>1.226906681163135</v>
+        <v>1.226906681163136</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0820872779230888</v>
+        <v>-0.08208727792308602</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.569168821793931</v>
+        <v>-3.569168821793935</v>
       </c>
       <c r="F19" t="n">
         <v>-1.483859035078137</v>
       </c>
       <c r="G19" t="n">
-        <v>1.940391299795311</v>
+        <v>1.940391299795312</v>
       </c>
     </row>
     <row r="20">
@@ -916,22 +916,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7465135631616248</v>
+        <v>0.7465135631616244</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.4013403221579306</v>
+        <v>-0.4013403221579288</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.228808898461442</v>
+        <v>-1.22880889846144</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.185963437294383</v>
+        <v>-1.185963437294384</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1599334242983557</v>
+        <v>0.1599334242983567</v>
       </c>
       <c r="G20" t="n">
-        <v>1.956132481892578</v>
+        <v>1.95613248189258</v>
       </c>
     </row>
     <row r="21">
@@ -941,19 +941,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.253632497881782</v>
+        <v>-2.253632497881781</v>
       </c>
       <c r="C21" t="n">
         <v>-2.069920739796283</v>
       </c>
       <c r="D21" t="n">
-        <v>2.240589840363225</v>
+        <v>2.240589840363223</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.122935549455663</v>
+        <v>-1.122935549455664</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5151875717321431</v>
+        <v>0.5151875717321424</v>
       </c>
       <c r="G21" t="n">
         <v>2.1447348528261</v>
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.812069921391803</v>
+        <v>1.812069921391802</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3089824857697</v>
+        <v>1.308982485769698</v>
       </c>
       <c r="D22" t="n">
-        <v>2.14217953067516</v>
+        <v>2.142179530675161</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.707103258251648</v>
+        <v>-2.707103258251652</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2458269768227078</v>
+        <v>-0.2458269768227087</v>
       </c>
       <c r="G22" t="n">
         <v>2.613392401706197</v>
@@ -991,19 +991,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-2.031664809092879</v>
+        <v>-2.031664809092878</v>
       </c>
       <c r="C23" t="n">
         <v>-2.339730116487223</v>
       </c>
       <c r="D23" t="n">
-        <v>2.049351828762988</v>
+        <v>2.049351828762986</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9593342209431666</v>
+        <v>-0.9593342209431678</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3890834931741244</v>
+        <v>0.3890834931741241</v>
       </c>
       <c r="G23" t="n">
         <v>2.093114728459417</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.750516170830915</v>
+        <v>1.750516170830914</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3855112466161313</v>
+        <v>0.3855112466161319</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8920854058379685</v>
+        <v>-0.8920854058379664</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.644561760504088</v>
+        <v>-1.64456176050409</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.263110520300714</v>
+        <v>-0.2631105203007135</v>
       </c>
       <c r="G24" t="n">
-        <v>2.084703800191285</v>
+        <v>2.084703800191287</v>
       </c>
     </row>
     <row r="25">
@@ -1041,22 +1041,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.297408573733281</v>
+        <v>1.29740857373328</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.5531380335439952</v>
+        <v>-0.5531380335439938</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7098264489323145</v>
+        <v>-0.7098264489323138</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.252159608114467</v>
+        <v>-1.252159608114468</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6091386422503443</v>
+        <v>-0.6091386422503441</v>
       </c>
       <c r="G25" t="n">
-        <v>1.946827249585245</v>
+        <v>1.946827249585246</v>
       </c>
     </row>
     <row r="26">
@@ -1066,22 +1066,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1267166616629151</v>
+        <v>-0.1267166616629155</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1262227552824805</v>
+        <v>-0.1262227552824786</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6530638644716826</v>
+        <v>-0.6530638644716803</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.879120418322136</v>
+        <v>-2.879120418322139</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.487085405320118</v>
+        <v>-0.4870854053201178</v>
       </c>
       <c r="G26" t="n">
-        <v>1.720354307325032</v>
+        <v>1.720354307325034</v>
       </c>
     </row>
     <row r="27">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2563066744296122</v>
+        <v>0.2563066744296121</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.286603496790511</v>
+        <v>-0.2866034967905129</v>
       </c>
       <c r="D27" t="n">
-        <v>2.760509079714799</v>
+        <v>2.760509079714798</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.465575326243233</v>
+        <v>-1.465575326243235</v>
       </c>
       <c r="F27" t="n">
-        <v>0.191087196148281</v>
+        <v>0.1910871961482802</v>
       </c>
       <c r="G27" t="n">
         <v>2.592087358193917</v>
@@ -1119,19 +1119,19 @@
         <v>2.890769349844495</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.4176783503458927</v>
+        <v>-0.4176783503458913</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.440996099631296</v>
+        <v>-1.440996099631298</v>
       </c>
       <c r="E28" t="n">
         <v>1.528924025574536</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5607045290296652</v>
+        <v>-0.5607045290296654</v>
       </c>
       <c r="G28" t="n">
-        <v>2.317775570522614</v>
+        <v>2.317775570522615</v>
       </c>
     </row>
     <row r="29">
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2963143150595054</v>
+        <v>0.2963143150595057</v>
       </c>
       <c r="C29" t="n">
-        <v>-3.374030983295713</v>
+        <v>-3.374030983295709</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.592151797078886</v>
+        <v>-2.592151797078889</v>
       </c>
       <c r="E29" t="n">
-        <v>1.396823502055015</v>
+        <v>1.396823502055017</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.187861406564276</v>
+        <v>-0.1878614065642749</v>
       </c>
       <c r="G29" t="n">
         <v>1.53799541057551</v>
@@ -1169,16 +1169,16 @@
         <v>2.114576865878735</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4561645542585586</v>
+        <v>-0.4561645542585609</v>
       </c>
       <c r="D30" t="n">
-        <v>1.841000626125448</v>
+        <v>1.841000626125446</v>
       </c>
       <c r="E30" t="n">
-        <v>1.661775072365689</v>
+        <v>1.66177507236569</v>
       </c>
       <c r="F30" t="n">
-        <v>0.478674549516585</v>
+        <v>0.4786745495165846</v>
       </c>
       <c r="G30" t="n">
         <v>2.98650154228345</v>
@@ -1191,22 +1191,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.05587728398447637</v>
+        <v>0.05587728398447642</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.154686338107861</v>
+        <v>-1.154686338107859</v>
       </c>
       <c r="D31" t="n">
         <v>-1.208586529855833</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.528443406890065</v>
+        <v>-0.5284434068900659</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.633238882931122</v>
+        <v>-0.6332388829311222</v>
       </c>
       <c r="G31" t="n">
-        <v>1.765264470594877</v>
+        <v>1.765264470594878</v>
       </c>
     </row>
     <row r="32">
@@ -1216,22 +1216,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.981908648169002</v>
+        <v>2.981908648169001</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.519456137488236</v>
+        <v>-1.519456137488234</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.586383492277014</v>
+        <v>-1.586383492277017</v>
       </c>
       <c r="E32" t="n">
-        <v>2.20004623168318</v>
+        <v>2.200046231683181</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7697715287667245</v>
+        <v>-0.7697715287667248</v>
       </c>
       <c r="G32" t="n">
-        <v>2.197833998920958</v>
+        <v>2.197833998920959</v>
       </c>
     </row>
     <row r="33">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5272604864964361</v>
+        <v>-0.5272604864964356</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.757565527648523</v>
+        <v>-1.75756552764852</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.293187217031307</v>
+        <v>-1.293187217031306</v>
       </c>
       <c r="E33" t="n">
         <v>-1.08021719865085</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2864756987871691</v>
+        <v>0.2864756987871703</v>
       </c>
       <c r="G33" t="n">
-        <v>1.686067623874442</v>
+        <v>1.686067623874443</v>
       </c>
     </row>
     <row r="34">
@@ -1266,22 +1266,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.2843845156874721</v>
+        <v>0.2843845156874716</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1902703507386197</v>
+        <v>0.1902703507386209</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3452403717077387</v>
+        <v>-0.3452403717077367</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.118111757274341</v>
+        <v>-3.118111757274344</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8229604609119283</v>
+        <v>-0.8229604609119288</v>
       </c>
       <c r="G34" t="n">
-        <v>1.77136061975014</v>
+        <v>1.771360619750141</v>
       </c>
     </row>
     <row r="35">
@@ -1291,22 +1291,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.008968663813961</v>
+        <v>3.00896866381396</v>
       </c>
       <c r="C35" t="n">
-        <v>1.72734782158501</v>
+        <v>1.727347821585009</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1071423841781833</v>
+        <v>-0.1071423841781808</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.979194873782933</v>
+        <v>-1.979194873782935</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3323228525645893</v>
+        <v>-0.3323228525645894</v>
       </c>
       <c r="G35" t="n">
-        <v>2.455818527721652</v>
+        <v>2.455818527721654</v>
       </c>
     </row>
     <row r="36">
@@ -1319,19 +1319,19 @@
         <v>1.096144918039989</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.012537915989258</v>
+        <v>-1.012537915989257</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.566229961667883</v>
+        <v>-1.566229961667882</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.2111682135202834</v>
+        <v>-0.2111682135202839</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6083797869825953</v>
+        <v>0.6083797869825972</v>
       </c>
       <c r="G36" t="n">
-        <v>2.026284898920165</v>
+        <v>2.026284898920166</v>
       </c>
     </row>
     <row r="37">
@@ -1341,22 +1341,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.390154119132507</v>
+        <v>1.390154119132506</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3359104167086873</v>
+        <v>0.3359104167086889</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.6986618072380764</v>
+        <v>-0.6986618072380745</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.747224801904364</v>
+        <v>-2.747224801904367</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.128089700601403</v>
+        <v>-1.128089700601404</v>
       </c>
       <c r="G37" t="n">
-        <v>1.819100764139649</v>
+        <v>1.81910076413965</v>
       </c>
     </row>
     <row r="38">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4614431773001467</v>
+        <v>0.4614431773001468</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.272841961854766</v>
+        <v>-1.272841961854767</v>
       </c>
       <c r="D38" t="n">
-        <v>2.329091938623054</v>
+        <v>2.329091938623052</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.02000065937321023</v>
+        <v>-0.02000065937321058</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.06100077834916965</v>
+        <v>-0.06100077834917084</v>
       </c>
       <c r="G38" t="n">
         <v>2.538021683189385</v>
@@ -1391,22 +1391,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.496490641299062</v>
+        <v>3.49649064129906</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3630888933851129</v>
+        <v>0.3630888933851146</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.684343026396639</v>
+        <v>-1.684343026396637</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.235971834270616</v>
+        <v>-1.235971834270617</v>
       </c>
       <c r="F39" t="n">
-        <v>0.05663323021793536</v>
+        <v>0.05663323021793675</v>
       </c>
       <c r="G39" t="n">
-        <v>2.179427979287093</v>
+        <v>2.179427979287095</v>
       </c>
     </row>
     <row r="40">
@@ -1419,16 +1419,16 @@
         <v>1.004051977027507</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01682419404342771</v>
+        <v>0.01682419404342659</v>
       </c>
       <c r="D40" t="n">
-        <v>1.764210717020153</v>
+        <v>1.764210717020154</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.597679228265277</v>
+        <v>-1.597679228265279</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6018438449320197</v>
+        <v>0.60184384493202</v>
       </c>
       <c r="G40" t="n">
         <v>2.56513296321162</v>
@@ -1441,19 +1441,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.02584519600344023</v>
+        <v>0.02584519600344052</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.492514202663214</v>
+        <v>-1.492514202663216</v>
       </c>
       <c r="D41" t="n">
-        <v>2.640973257360858</v>
+        <v>2.640973257360855</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1702998710440349</v>
+        <v>0.1702998710440346</v>
       </c>
       <c r="F41" t="n">
-        <v>0.43835146177413</v>
+        <v>0.4383514617741294</v>
       </c>
       <c r="G41" t="n">
         <v>2.623521679116926</v>
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.831779336136942</v>
+        <v>3.831779336136941</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.2533712924685882</v>
+        <v>-0.253371292468588</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.209108675880971</v>
+        <v>-0.2091086758809709</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5989791318749325</v>
+        <v>0.5989791318749326</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1327326221235222</v>
+        <v>-0.1327326221235216</v>
       </c>
       <c r="G42" t="n">
         <v>2.574249921944149</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6.555506950144018</v>
+        <v>6.555506950144017</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5305752111939868</v>
+        <v>0.5305752111939875</v>
       </c>
       <c r="D43" t="n">
         <v>-1.263601978316839</v>
@@ -1503,10 +1503,10 @@
         <v>1.22162492489978</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2526557449325313</v>
+        <v>0.2526557449325331</v>
       </c>
       <c r="G43" t="n">
-        <v>2.850039865917742</v>
+        <v>2.850039865917743</v>
       </c>
     </row>
     <row r="44">
@@ -1516,22 +1516,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.557871964241698</v>
+        <v>3.557871964241697</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7957803428894118</v>
+        <v>0.7957803428894116</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.02208469318061384</v>
+        <v>-0.02208469318061201</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.670088070269003</v>
+        <v>-1.670088070269005</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.5990870643821545</v>
+        <v>-0.5990870643821543</v>
       </c>
       <c r="G44" t="n">
-        <v>2.382019409392692</v>
+        <v>2.382019409392693</v>
       </c>
     </row>
     <row r="45">
@@ -1541,19 +1541,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.893366224598804</v>
+        <v>2.893366224598803</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8199709332536217</v>
+        <v>0.8199709332536196</v>
       </c>
       <c r="D45" t="n">
-        <v>1.177464176677081</v>
+        <v>1.177464176677082</v>
       </c>
       <c r="E45" t="n">
-        <v>1.185782260096363</v>
+        <v>1.185782260096365</v>
       </c>
       <c r="F45" t="n">
-        <v>3.681838434817529</v>
+        <v>3.681838434817533</v>
       </c>
       <c r="G45" t="n">
         <v>3.521954334390625</v>
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.337393455759457</v>
+        <v>1.337393455759456</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5331758392759078</v>
+        <v>0.5331758392759087</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6024635876501555</v>
+        <v>-0.6024635876501536</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.451075413770698</v>
+        <v>-2.451075413770702</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.6400317145522038</v>
+        <v>-0.6400317145522035</v>
       </c>
       <c r="G46" t="n">
-        <v>1.967550286873326</v>
+        <v>1.967550286873327</v>
       </c>
     </row>
     <row r="47">
@@ -1591,22 +1591,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.8696228508612583</v>
+        <v>-0.8696228508612581</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.6780040357184001</v>
+        <v>-0.6780040357183982</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.8316796114408801</v>
+        <v>-0.831679611440878</v>
       </c>
       <c r="E47" t="n">
-        <v>-2.11581238940162</v>
+        <v>-2.115812389401623</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4202137105699785</v>
+        <v>0.4202137105699799</v>
       </c>
       <c r="G47" t="n">
-        <v>1.781367992902675</v>
+        <v>1.781367992902676</v>
       </c>
     </row>
     <row r="48">
@@ -1616,22 +1616,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.917489125100054</v>
+        <v>2.917489125100053</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3013469030487012</v>
+        <v>0.301346903048699</v>
       </c>
       <c r="D48" t="n">
-        <v>2.642621409451311</v>
+        <v>2.64262140945131</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.619292308046149</v>
+        <v>-0.6192923080461501</v>
       </c>
       <c r="F48" t="n">
         <v>0.661193444829144</v>
       </c>
       <c r="G48" t="n">
-        <v>3.037279593619371</v>
+        <v>3.037279593619372</v>
       </c>
     </row>
     <row r="49">
@@ -1644,19 +1644,19 @@
         <v>-0.4022551669291249</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.554329369729555</v>
+        <v>-1.554329369729554</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.9984175910096292</v>
+        <v>-0.9984175910096287</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.521855557076872</v>
+        <v>-1.521855557076874</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.536947676587389</v>
+        <v>-0.5369476765873886</v>
       </c>
       <c r="G49" t="n">
-        <v>1.599903870452274</v>
+        <v>1.599903870452275</v>
       </c>
     </row>
     <row r="50">
@@ -1669,16 +1669,16 @@
         <v>1.701127217951179</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.5255717405315506</v>
+        <v>-0.5255717405315481</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7490546763134789</v>
+        <v>-0.7490546763134792</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.883228847554964</v>
+        <v>-1.883228847554966</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.986107704915156</v>
+        <v>-1.986107704915158</v>
       </c>
       <c r="G50" t="n">
         <v>1.6956326448348</v>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.354622465982963</v>
+        <v>2.354622465982962</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2169522388396917</v>
+        <v>-0.21695223883969</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.1462368872799416</v>
+        <v>-0.1462368872799426</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.850664987457779</v>
+        <v>-1.850664987457781</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.559989688843802</v>
+        <v>-2.559989688843805</v>
       </c>
       <c r="G51" t="n">
         <v>1.814424290990326</v>
@@ -1716,22 +1716,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.755914530699477</v>
+        <v>1.755914530699476</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.3932650110784013</v>
+        <v>-0.3932650110783986</v>
       </c>
       <c r="D52" t="n">
         <v>-1.285858004246176</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.801379598214613</v>
+        <v>-1.801379598214616</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.990840503368205</v>
+        <v>-1.990840503368206</v>
       </c>
       <c r="G52" t="n">
-        <v>1.635376515132371</v>
+        <v>1.635376515132372</v>
       </c>
     </row>
     <row r="53">
@@ -1741,22 +1741,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.831748300360889</v>
+        <v>2.831748300360887</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5698189879606708</v>
+        <v>0.5698189879606722</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.549240827464957</v>
+        <v>-1.549240827464954</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.368068382791717</v>
+        <v>-1.368068382791719</v>
       </c>
       <c r="F53" t="n">
-        <v>0.08171329404120221</v>
+        <v>0.08171329404120359</v>
       </c>
       <c r="G53" t="n">
-        <v>2.166886998732811</v>
+        <v>2.166886998732812</v>
       </c>
     </row>
     <row r="54">
@@ -1766,22 +1766,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2442386661857714</v>
+        <v>0.2442386661857713</v>
       </c>
       <c r="C54" t="n">
-        <v>-1.489400948004193</v>
+        <v>-1.48940094800419</v>
       </c>
       <c r="D54" t="n">
         <v>-1.452284749538686</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.5588161764787654</v>
+        <v>-0.5588161764787657</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1511661431674419</v>
+        <v>-0.1511661431674412</v>
       </c>
       <c r="G54" t="n">
-        <v>1.757680422973135</v>
+        <v>1.757680422973136</v>
       </c>
     </row>
     <row r="55">
@@ -1791,22 +1791,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3.859064533468148</v>
+        <v>3.859064533468147</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5949047331578832</v>
+        <v>0.5949047331578841</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.249725436149384</v>
+        <v>-1.249725436149383</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.164560056284858</v>
+        <v>-1.16456005628486</v>
       </c>
       <c r="F55" t="n">
         <v>-1.016166214201748</v>
       </c>
       <c r="G55" t="n">
-        <v>2.167399578748308</v>
+        <v>2.16739957874831</v>
       </c>
     </row>
     <row r="56">
@@ -1816,22 +1816,22 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.029942607617384</v>
+        <v>3.029942607617383</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5056992805458262</v>
+        <v>0.505699280545828</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.841305546190881</v>
+        <v>-1.841305546190878</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.359147195369583</v>
+        <v>-1.359147195369584</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2041376924456348</v>
+        <v>0.2041376924456366</v>
       </c>
       <c r="G56" t="n">
-        <v>2.142038247198994</v>
+        <v>2.142038247198995</v>
       </c>
     </row>
     <row r="57">
@@ -1841,22 +1841,22 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.7333748808754794</v>
+        <v>-0.7333748808754791</v>
       </c>
       <c r="C57" t="n">
-        <v>-1.29581634812179</v>
+        <v>-1.295816348121789</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7028897843651414</v>
+        <v>-0.7028897843651398</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.752716859612337</v>
+        <v>-1.752716859612338</v>
       </c>
       <c r="F57" t="n">
-        <v>1.114846676565727</v>
+        <v>1.114846676565729</v>
       </c>
       <c r="G57" t="n">
-        <v>1.874231056252467</v>
+        <v>1.874231056252468</v>
       </c>
     </row>
     <row r="58">
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.236425197476465</v>
+        <v>1.236425197476464</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5229166707300932</v>
+        <v>0.522916670730094</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.9519113489681915</v>
+        <v>-0.9519113489681899</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.050607832484112</v>
+        <v>-1.050607832484113</v>
       </c>
       <c r="F58" t="n">
-        <v>0.005734034642913454</v>
+        <v>0.005734034642914089</v>
       </c>
       <c r="G58" t="n">
         <v>2.166586058617908</v>
@@ -1891,22 +1891,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.439541641446721</v>
+        <v>-1.43954164144672</v>
       </c>
       <c r="C59" t="n">
-        <v>-2.461612245429088</v>
+        <v>-2.461612245429085</v>
       </c>
       <c r="D59" t="n">
         <v>-1.206520528247183</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5504189769382474</v>
+        <v>-0.5504189769382472</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2620814423873599</v>
+        <v>0.262081442387361</v>
       </c>
       <c r="G59" t="n">
-        <v>1.592799680919376</v>
+        <v>1.592799680919377</v>
       </c>
     </row>
     <row r="60">
@@ -1916,22 +1916,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4.253570297804814</v>
+        <v>4.253570297804812</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4821206401543292</v>
+        <v>0.4821206401543305</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.101857824483052</v>
+        <v>-1.101857824483051</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.8592076220340685</v>
+        <v>-0.8592076220340693</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.06090283215241446</v>
+        <v>-0.06090283215241264</v>
       </c>
       <c r="G60" t="n">
-        <v>2.385773459994635</v>
+        <v>2.385773459994636</v>
       </c>
     </row>
     <row r="61">
@@ -1947,16 +1947,16 @@
         <v>-3.283531393661418</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1777485130759779</v>
+        <v>0.1777485130759719</v>
       </c>
       <c r="E61" t="n">
-        <v>4.292117288815221</v>
+        <v>4.292117288815225</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.378067637022015</v>
+        <v>-1.37806763702202</v>
       </c>
       <c r="G61" t="n">
-        <v>2.326577164822367</v>
+        <v>2.326577164822365</v>
       </c>
     </row>
     <row r="62">
@@ -1966,22 +1966,22 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6.721331834074801</v>
+        <v>6.721331834074799</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2378281737638503</v>
+        <v>-0.2378281737638491</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.482955547530763</v>
+        <v>-1.482955547530764</v>
       </c>
       <c r="E62" t="n">
-        <v>1.608521071413265</v>
+        <v>1.608521071413266</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2688249326222985</v>
+        <v>0.2688249326223004</v>
       </c>
       <c r="G62" t="n">
-        <v>2.767658466815638</v>
+        <v>2.767658466815639</v>
       </c>
     </row>
     <row r="63">
@@ -1994,16 +1994,16 @@
         <v>1.084890527059936</v>
       </c>
       <c r="C63" t="n">
-        <v>-2.648009856997918</v>
+        <v>-2.648009856997915</v>
       </c>
       <c r="D63" t="n">
-        <v>-1.104312921431662</v>
+        <v>-1.104312921431664</v>
       </c>
       <c r="E63" t="n">
         <v>1.172734572661247</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7043113833963557</v>
+        <v>-0.7043113833963559</v>
       </c>
       <c r="G63" t="n">
         <v>1.855289598793966</v>
@@ -2016,22 +2016,22 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1.751073100130719</v>
+        <v>1.751073100130718</v>
       </c>
       <c r="C64" t="n">
-        <v>-1.077547471185917</v>
+        <v>-1.077547471185916</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8186403210752722</v>
+        <v>-0.8186403210752726</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4451878713022363</v>
+        <v>-0.4451878713022375</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.8410704702600007</v>
+        <v>-0.8410704702600009</v>
       </c>
       <c r="G64" t="n">
-        <v>1.95637328929545</v>
+        <v>1.956373289295451</v>
       </c>
     </row>
     <row r="65">
@@ -2041,22 +2041,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5.165385367077522</v>
+        <v>5.165385367077521</v>
       </c>
       <c r="C65" t="n">
-        <v>-1.21244588903694</v>
+        <v>-1.212445889036938</v>
       </c>
       <c r="D65" t="n">
-        <v>-1.698425369095952</v>
+        <v>-1.698425369095953</v>
       </c>
       <c r="E65" t="n">
-        <v>1.741456655909494</v>
+        <v>1.741456655909495</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1323380202061264</v>
+        <v>0.1323380202061279</v>
       </c>
       <c r="G65" t="n">
-        <v>2.467925848234416</v>
+        <v>2.467925848234417</v>
       </c>
     </row>
     <row r="66">
@@ -2069,10 +2069,10 @@
         <v>3.927630929673222</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.8339453898192339</v>
+        <v>-0.8339453898192326</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8000528662636212</v>
+        <v>-0.8000528662636227</v>
       </c>
       <c r="E66" t="n">
         <v>1.169320434116975</v>
@@ -2091,16 +2091,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4.391681541309022</v>
+        <v>4.391681541309021</v>
       </c>
       <c r="C67" t="n">
-        <v>0.588705010907279</v>
+        <v>0.5887050109072769</v>
       </c>
       <c r="D67" t="n">
         <v>2.44515658057355</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.2749326915845541</v>
+        <v>-0.2749326915845549</v>
       </c>
       <c r="F67" t="n">
         <v>0.5420714604346089</v>
@@ -2119,16 +2119,16 @@
         <v>1.625018578307704</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4208195679317051</v>
+        <v>0.4208195679317033</v>
       </c>
       <c r="D68" t="n">
-        <v>2.96181698670493</v>
+        <v>2.961816986704928</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.369553483197379</v>
+        <v>-1.369553483197382</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8188432413649119</v>
+        <v>-0.8188432413649146</v>
       </c>
       <c r="G68" t="n">
         <v>2.697866645085115</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.439829056709893</v>
+        <v>1.439829056709892</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5391272967615832</v>
+        <v>-0.5391272967615851</v>
       </c>
       <c r="D69" t="n">
-        <v>2.519851425934307</v>
+        <v>2.519851425934306</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.2292652497648993</v>
+        <v>-0.2292652497649001</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5884704727570466</v>
+        <v>0.5884704727570462</v>
       </c>
       <c r="G69" t="n">
         <v>2.81986200162722</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3.882269467735987</v>
+        <v>3.882269467735984</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3859021438073764</v>
+        <v>0.385902143807374</v>
       </c>
       <c r="D70" t="n">
         <v>2.446547528586752</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.2538932574431716</v>
+        <v>-0.2538932574431721</v>
       </c>
       <c r="F70" t="n">
-        <v>0.6313690995957126</v>
+        <v>0.6313690995957127</v>
       </c>
       <c r="G70" t="n">
         <v>3.132123317376894</v>
@@ -2191,22 +2191,22 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2.259695112876489</v>
+        <v>2.259695112876488</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4124096069512407</v>
+        <v>-0.4124096069512422</v>
       </c>
       <c r="D71" t="n">
-        <v>2.001300295158102</v>
+        <v>2.001300295158101</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1016510303501927</v>
+        <v>0.1016510303501929</v>
       </c>
       <c r="F71" t="n">
         <v>1.119488047643306</v>
       </c>
       <c r="G71" t="n">
-        <v>2.931375062218854</v>
+        <v>2.931375062218855</v>
       </c>
     </row>
     <row r="72">
@@ -2219,19 +2219,19 @@
         <v>2.93171650680845</v>
       </c>
       <c r="C72" t="n">
-        <v>-1.246861032558254</v>
+        <v>-1.246861032558255</v>
       </c>
       <c r="D72" t="n">
         <v>1.015875801478323</v>
       </c>
       <c r="E72" t="n">
-        <v>1.113760588626013</v>
+        <v>1.113760588626016</v>
       </c>
       <c r="F72" t="n">
-        <v>3.441225940226508</v>
+        <v>3.441225940226512</v>
       </c>
       <c r="G72" t="n">
-        <v>3.162325813413912</v>
+        <v>3.162325813413913</v>
       </c>
     </row>
     <row r="73">
@@ -2241,22 +2241,22 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>5.600905185773277</v>
+        <v>5.600905185773275</v>
       </c>
       <c r="C73" t="n">
         <v>1.324891464506641</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.54604777660728</v>
+        <v>-1.546047776607276</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.3795126897460858</v>
+        <v>-0.3795126897460843</v>
       </c>
       <c r="F73" t="n">
-        <v>3.354816259848985</v>
+        <v>3.354816259848991</v>
       </c>
       <c r="G73" t="n">
-        <v>3.09275938411877</v>
+        <v>3.092759384118771</v>
       </c>
     </row>
     <row r="74">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4.641127841209785</v>
+        <v>4.641127841209784</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6403242024800895</v>
+        <v>0.6403242024800866</v>
       </c>
       <c r="D74" t="n">
-        <v>2.747678329341149</v>
+        <v>2.747678329341148</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.4857227734505894</v>
+        <v>-0.4857227734505903</v>
       </c>
       <c r="F74" t="n">
-        <v>0.413036395460917</v>
+        <v>0.4130363954609165</v>
       </c>
       <c r="G74" t="n">
         <v>3.218623461786999</v>
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.422931739155248</v>
+        <v>2.422931739155247</v>
       </c>
       <c r="C75" t="n">
-        <v>0.694603504653542</v>
+        <v>0.694603504653539</v>
       </c>
       <c r="D75" t="n">
-        <v>2.867646459747699</v>
+        <v>2.8676464597477</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9756382137286365</v>
+        <v>-0.9756382137286383</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4008740656604979</v>
+        <v>0.4008740656604975</v>
       </c>
       <c r="G75" t="n">
-        <v>3.010180697508016</v>
+        <v>3.010180697508017</v>
       </c>
     </row>
     <row r="76">
@@ -2316,19 +2316,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2.54754624141797</v>
+        <v>2.547546241417968</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.1420697621067095</v>
+        <v>-0.1420697621067109</v>
       </c>
       <c r="D76" t="n">
-        <v>3.201937143472751</v>
+        <v>3.201937143472749</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.9066829971401626</v>
+        <v>-0.9066829971401648</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.38265272173316</v>
+        <v>-1.382652721733163</v>
       </c>
       <c r="G76" t="n">
         <v>2.70764789314648</v>
@@ -2341,19 +2341,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.612800923759805</v>
+        <v>1.612800923759804</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.3983365856625974</v>
+        <v>-0.3983365856625989</v>
       </c>
       <c r="D77" t="n">
-        <v>2.190284421048478</v>
+        <v>2.190284421048477</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.4804905232448999</v>
+        <v>-0.4804905232449004</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8733700831459458</v>
+        <v>0.8733700831459461</v>
       </c>
       <c r="G77" t="n">
         <v>2.80677906407145</v>
@@ -2369,16 +2369,16 @@
         <v>2.74901437268143</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.1084537780728595</v>
+        <v>-0.1084537780728612</v>
       </c>
       <c r="D78" t="n">
-        <v>2.258560850647712</v>
+        <v>2.258560850647711</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.10915958426013</v>
+        <v>-0.1091595842601304</v>
       </c>
       <c r="F78" t="n">
-        <v>0.7387695177326324</v>
+        <v>0.7387695177326323</v>
       </c>
       <c r="G78" t="n">
         <v>2.974974154604542</v>
@@ -2394,19 +2394,19 @@
         <v>-0.4734431126533395</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6465911402704233</v>
+        <v>-0.6465911402704219</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.5377542214199683</v>
+        <v>-0.5377542214199664</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.960698538998704</v>
+        <v>-1.960698538998706</v>
       </c>
       <c r="F79" t="n">
-        <v>0.675456641873503</v>
+        <v>0.6754566418735045</v>
       </c>
       <c r="G79" t="n">
-        <v>1.924241807834034</v>
+        <v>1.924241807834035</v>
       </c>
     </row>
     <row r="80">
@@ -2419,16 +2419,16 @@
         <v>1.306237217147264</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.389894957891074</v>
+        <v>-1.389894957891076</v>
       </c>
       <c r="D80" t="n">
-        <v>2.234811351149597</v>
+        <v>2.234811351149595</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2682474220609176</v>
+        <v>0.2682474220609177</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6142898632900973</v>
+        <v>0.6142898632900974</v>
       </c>
       <c r="G80" t="n">
         <v>2.706243498091828</v>
@@ -2444,19 +2444,19 @@
         <v>3.67803512406718</v>
       </c>
       <c r="C81" t="n">
-        <v>0.5909833209329661</v>
+        <v>0.5909833209329634</v>
       </c>
       <c r="D81" t="n">
-        <v>2.946025923939023</v>
+        <v>2.946025923939022</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.733676393169858</v>
+        <v>-0.73367639316986</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.4858923464044823</v>
+        <v>-0.485892346404484</v>
       </c>
       <c r="G81" t="n">
-        <v>3.007977987695615</v>
+        <v>3.007977987695614</v>
       </c>
     </row>
     <row r="82">
@@ -2466,19 +2466,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2.102291927982409</v>
+        <v>2.102291927982408</v>
       </c>
       <c r="C82" t="n">
-        <v>0.5240442890198951</v>
+        <v>0.5240442890198962</v>
       </c>
       <c r="D82" t="n">
-        <v>0.1278549153132864</v>
+        <v>0.1278549153132857</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.898611718858809</v>
+        <v>-1.898611718858813</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.679523865859168</v>
+        <v>-2.679523865859172</v>
       </c>
       <c r="G82" t="n">
         <v>1.922656049092005</v>
@@ -2494,19 +2494,19 @@
         <v>1.375731789244887</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.2841528374220448</v>
+        <v>-0.2841528374220431</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.9911566270194123</v>
+        <v>-0.9911566270194104</v>
       </c>
       <c r="E83" t="n">
-        <v>-2.123036001117732</v>
+        <v>-2.123036001117734</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.6009409013509414</v>
+        <v>-0.6009409013509408</v>
       </c>
       <c r="G83" t="n">
-        <v>1.83509232946154</v>
+        <v>1.835092329461541</v>
       </c>
     </row>
     <row r="84">
@@ -2516,19 +2516,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3.650971145561097</v>
+        <v>3.650971145561096</v>
       </c>
       <c r="C84" t="n">
-        <v>-1.069193164904969</v>
+        <v>-1.069193164904971</v>
       </c>
       <c r="D84" t="n">
-        <v>1.86524277841623</v>
+        <v>1.865242778416228</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9761304867284574</v>
+        <v>0.9761304867284583</v>
       </c>
       <c r="F84" t="n">
-        <v>0.6387877130265049</v>
+        <v>0.6387877130265055</v>
       </c>
       <c r="G84" t="n">
         <v>2.963178281022482</v>
@@ -2541,19 +2541,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2.993905594326431</v>
+        <v>2.99390559432643</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.5754280415407723</v>
+        <v>-0.5754280415407742</v>
       </c>
       <c r="D85" t="n">
-        <v>2.276108632192367</v>
+        <v>2.276108632192365</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2384530455286678</v>
+        <v>0.2384530455286676</v>
       </c>
       <c r="F85" t="n">
-        <v>0.6836269438271769</v>
+        <v>0.683626943827177</v>
       </c>
       <c r="G85" t="n">
         <v>2.966741635078163</v>
@@ -2566,19 +2566,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5.994649004624828</v>
+        <v>5.994649004624826</v>
       </c>
       <c r="C86" t="n">
-        <v>0.09379496059533921</v>
+        <v>0.09379496059533642</v>
       </c>
       <c r="D86" t="n">
-        <v>2.216906959638711</v>
+        <v>2.216906959638709</v>
       </c>
       <c r="E86" t="n">
-        <v>1.297515288832765</v>
+        <v>1.297515288832766</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9021676857652036</v>
+        <v>0.9021676857652045</v>
       </c>
       <c r="G86" t="n">
         <v>3.449796541904556</v>
@@ -2591,22 +2591,22 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.0716826007252645</v>
+        <v>-0.07168260072526415</v>
       </c>
       <c r="C87" t="n">
         <v>-2.259233990916757</v>
       </c>
       <c r="D87" t="n">
-        <v>2.082519693034055</v>
+        <v>2.082519693034051</v>
       </c>
       <c r="E87" t="n">
-        <v>0.400440579422697</v>
+        <v>0.4004405794226971</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.6111783377618998</v>
+        <v>-0.6111783377619016</v>
       </c>
       <c r="G87" t="n">
-        <v>2.286760865150849</v>
+        <v>2.286760865150848</v>
       </c>
     </row>
     <row r="88">
@@ -2619,16 +2619,16 @@
         <v>1.455689547548723</v>
       </c>
       <c r="C88" t="n">
-        <v>-1.762811633415942</v>
+        <v>-1.762811633415943</v>
       </c>
       <c r="D88" t="n">
-        <v>1.671309493066756</v>
+        <v>1.671309493066753</v>
       </c>
       <c r="E88" t="n">
-        <v>1.020791049551393</v>
+        <v>1.020791049551394</v>
       </c>
       <c r="F88" t="n">
-        <v>0.3393065010980859</v>
+        <v>0.3393065010980857</v>
       </c>
       <c r="G88" t="n">
         <v>2.621673805581241</v>
@@ -2641,22 +2641,22 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.6300563840674588</v>
+        <v>-0.6300563840674583</v>
       </c>
       <c r="C89" t="n">
-        <v>-1.061309204420766</v>
+        <v>-1.061309204420764</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.6069763381490443</v>
+        <v>-0.6069763381490427</v>
       </c>
       <c r="E89" t="n">
-        <v>-1.308009574396477</v>
+        <v>-1.308009574396479</v>
       </c>
       <c r="F89" t="n">
-        <v>1.177133058657776</v>
+        <v>1.177133058657778</v>
       </c>
       <c r="G89" t="n">
-        <v>1.996299924242431</v>
+        <v>1.996299924242432</v>
       </c>
     </row>
     <row r="90">
@@ -2666,22 +2666,22 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3.102842087588441</v>
+        <v>3.102842087588439</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5962109768908158</v>
+        <v>0.5962109768908169</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.161948046679061</v>
+        <v>-1.161948046679059</v>
       </c>
       <c r="E90" t="n">
         <v>-1.280750594691914</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1852093443319505</v>
+        <v>0.1852093443319517</v>
       </c>
       <c r="G90" t="n">
-        <v>2.284717445377044</v>
+        <v>2.284717445377045</v>
       </c>
     </row>
     <row r="91">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1.357077591889135</v>
+        <v>1.357077591889134</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3377884854966019</v>
+        <v>0.3377884854965997</v>
       </c>
       <c r="D91" t="n">
         <v>2.924915352577265</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.887001556146362</v>
+        <v>-1.887001556146365</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.1005942475604853</v>
+        <v>-0.1005942475604864</v>
       </c>
       <c r="G91" t="n">
         <v>2.699515062297849</v>
@@ -2716,22 +2716,22 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3.362997082671668</v>
+        <v>3.362997082671666</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6114393606530381</v>
+        <v>0.6114393606530388</v>
       </c>
       <c r="D92" t="n">
-        <v>-1.30109193151684</v>
+        <v>-1.301091931516839</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.8730571517962926</v>
+        <v>-0.8730571517962928</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3788151064100657</v>
+        <v>0.3788151064100666</v>
       </c>
       <c r="G92" t="n">
-        <v>2.362303663218555</v>
+        <v>2.362303663218557</v>
       </c>
     </row>
     <row r="93">
@@ -2741,22 +2741,22 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4.314021542726616</v>
+        <v>4.314021542726615</v>
       </c>
       <c r="C93" t="n">
-        <v>1.667025264466083</v>
+        <v>1.667025264466085</v>
       </c>
       <c r="D93" t="n">
-        <v>-1.697165519117817</v>
+        <v>-1.697165519117813</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.368536115273023</v>
+        <v>-1.368536115273024</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7650340129331171</v>
+        <v>0.765034012933119</v>
       </c>
       <c r="G93" t="n">
-        <v>2.511844681103095</v>
+        <v>2.511844681103097</v>
       </c>
     </row>
     <row r="94">
@@ -2769,19 +2769,19 @@
         <v>-1.479897126734461</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.53235087981043</v>
+        <v>-1.532350879810428</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.9948873764699908</v>
+        <v>-0.9948873764699895</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.353137802142319</v>
+        <v>-1.353137802142321</v>
       </c>
       <c r="F94" t="n">
-        <v>0.28106403645769</v>
+        <v>0.2810640364576912</v>
       </c>
       <c r="G94" t="n">
-        <v>1.65972121560007</v>
+        <v>1.659721215600071</v>
       </c>
     </row>
     <row r="95">
@@ -2791,22 +2791,22 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.4712671734293135</v>
+        <v>0.4712671734293133</v>
       </c>
       <c r="C95" t="n">
-        <v>-1.357928779475431</v>
+        <v>-1.357928779475429</v>
       </c>
       <c r="D95" t="n">
         <v>-1.038370805348676</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.8362323636200973</v>
+        <v>-0.8362323636200977</v>
       </c>
       <c r="F95" t="n">
-        <v>0.02433001605627384</v>
+        <v>0.0243300160562748</v>
       </c>
       <c r="G95" t="n">
-        <v>1.856580591721243</v>
+        <v>1.856580591721244</v>
       </c>
     </row>
     <row r="96">
@@ -2816,19 +2816,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3.419836466439655</v>
+        <v>3.419836466439654</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.7046764791470588</v>
+        <v>-0.7046764791470572</v>
       </c>
       <c r="D96" t="n">
-        <v>-1.233668887015886</v>
+        <v>-1.233668887015885</v>
       </c>
       <c r="E96" t="n">
-        <v>0.5823711694053896</v>
+        <v>0.5823711694053906</v>
       </c>
       <c r="F96" t="n">
-        <v>0.316308908648707</v>
+        <v>0.3163089086487083</v>
       </c>
       <c r="G96" t="n">
         <v>2.365281800563952</v>
@@ -2844,19 +2844,19 @@
         <v>2.496300783960359</v>
       </c>
       <c r="C97" t="n">
-        <v>-1.772332189042571</v>
+        <v>-1.772332189042569</v>
       </c>
       <c r="D97" t="n">
-        <v>-1.681330466262061</v>
+        <v>-1.681330466262063</v>
       </c>
       <c r="E97" t="n">
-        <v>0.8913062809110552</v>
+        <v>0.8913062809110561</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.6274446345226417</v>
+        <v>-0.6274446345226411</v>
       </c>
       <c r="G97" t="n">
-        <v>1.96579890939884</v>
+        <v>1.965798909398841</v>
       </c>
     </row>
     <row r="98">
@@ -2866,22 +2866,22 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2.07460541267196</v>
+        <v>2.074605412671959</v>
       </c>
       <c r="C98" t="n">
-        <v>-1.049913595301275</v>
+        <v>-1.049913595301274</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.620220973066474</v>
+        <v>-1.620220973066473</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.2745125618607719</v>
+        <v>-0.2745125618607721</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3577400192920832</v>
+        <v>0.357740019292085</v>
       </c>
       <c r="G98" t="n">
-        <v>2.04393451113358</v>
+        <v>2.043934511133581</v>
       </c>
     </row>
     <row r="99">
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1.999527390187418</v>
+        <v>1.999527390187417</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.156679533706541</v>
+        <v>-1.15667953370654</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.6777949870155584</v>
+        <v>-0.6777949870155594</v>
       </c>
       <c r="E99" t="n">
-        <v>0.3974150841908107</v>
+        <v>0.3974150841908109</v>
       </c>
       <c r="F99" t="n">
         <v>-0.6287489291991131</v>
@@ -2916,19 +2916,19 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.580632863388202</v>
+        <v>1.580632863388201</v>
       </c>
       <c r="C100" t="n">
-        <v>-2.150490192749234</v>
+        <v>-2.150490192749232</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.9298410963006669</v>
+        <v>-0.9298410963006685</v>
       </c>
       <c r="E100" t="n">
-        <v>0.5158132170675322</v>
+        <v>0.5158132170675328</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.5038878653218247</v>
+        <v>-0.5038878653218243</v>
       </c>
       <c r="G100" t="n">
         <v>1.941847447874568</v>
@@ -2944,19 +2944,19 @@
         <v>1.618941185585461</v>
       </c>
       <c r="C101" t="n">
-        <v>-1.54081422181885</v>
+        <v>-1.540814221818849</v>
       </c>
       <c r="D101" t="n">
-        <v>-1.654842583243645</v>
+        <v>-1.654842583243644</v>
       </c>
       <c r="E101" t="n">
-        <v>0.5091560069959498</v>
+        <v>0.509156006995952</v>
       </c>
       <c r="F101" t="n">
-        <v>2.490543804887305</v>
+        <v>2.490543804887309</v>
       </c>
       <c r="G101" t="n">
-        <v>2.342738156704757</v>
+        <v>2.342738156704758</v>
       </c>
     </row>
     <row r="102">
@@ -2966,22 +2966,22 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8985095536166571</v>
+        <v>0.8985095536166569</v>
       </c>
       <c r="C102" t="n">
-        <v>-2.014381739605798</v>
+        <v>-2.014381739605796</v>
       </c>
       <c r="D102" t="n">
-        <v>-2.103920126488463</v>
+        <v>-2.103920126488462</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.6024043892282173</v>
+        <v>-0.6024043892282159</v>
       </c>
       <c r="F102" t="n">
-        <v>2.259100056813676</v>
+        <v>2.25910005681368</v>
       </c>
       <c r="G102" t="n">
-        <v>1.969973419804847</v>
+        <v>1.969973419804848</v>
       </c>
     </row>
     <row r="103">
@@ -2991,22 +2991,22 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7690516142844713</v>
+        <v>0.7690516142844709</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.7793796419223545</v>
+        <v>-0.7793796419223523</v>
       </c>
       <c r="D103" t="n">
-        <v>-1.232270711403085</v>
+        <v>-1.232270711403084</v>
       </c>
       <c r="E103" t="n">
-        <v>-1.544345589737193</v>
+        <v>-1.544345589737194</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.6564639066398494</v>
+        <v>-0.6564639066398493</v>
       </c>
       <c r="G103" t="n">
-        <v>1.740118668200615</v>
+        <v>1.740118668200616</v>
       </c>
     </row>
     <row r="104">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-2.696758330834611</v>
+        <v>-2.69675833083461</v>
       </c>
       <c r="C104" t="n">
-        <v>-2.15624905610703</v>
+        <v>-2.156249056107028</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.5146928646770766</v>
+        <v>-0.5146928646770758</v>
       </c>
       <c r="E104" t="n">
-        <v>-1.958080545394549</v>
+        <v>-1.95808054539455</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2549825368686213</v>
+        <v>0.2549825368686224</v>
       </c>
       <c r="G104" t="n">
-        <v>1.480325127657849</v>
+        <v>1.48032512765785</v>
       </c>
     </row>
     <row r="105">
@@ -3041,22 +3041,22 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3.55318567121627</v>
+        <v>3.553185671216268</v>
       </c>
       <c r="C105" t="n">
-        <v>1.002939503884801</v>
+        <v>1.002939503884802</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.126254408870247</v>
+        <v>-1.126254408870244</v>
       </c>
       <c r="E105" t="n">
-        <v>-1.424677001963086</v>
+        <v>-1.424677001963087</v>
       </c>
       <c r="F105" t="n">
-        <v>0.06312144951122764</v>
+        <v>0.06312144951122879</v>
       </c>
       <c r="G105" t="n">
-        <v>2.347629236282947</v>
+        <v>2.347629236282949</v>
       </c>
     </row>
     <row r="106">
@@ -3066,22 +3066,22 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3.628259546920428</v>
+        <v>3.628259546920427</v>
       </c>
       <c r="C106" t="n">
-        <v>0.9121714838650443</v>
+        <v>0.912171483865045</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.7933724643384455</v>
+        <v>-0.7933724643384436</v>
       </c>
       <c r="E106" t="n">
         <v>-1.353976378872652</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2092706182527805</v>
+        <v>0.2092706182527813</v>
       </c>
       <c r="G106" t="n">
-        <v>2.428389608256134</v>
+        <v>2.428389608256135</v>
       </c>
     </row>
     <row r="107">
@@ -3094,16 +3094,16 @@
         <v>-1.360558816998082</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.910537857825419</v>
+        <v>-0.9105378578254169</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.9456069335605172</v>
+        <v>-0.9456069335605157</v>
       </c>
       <c r="E107" t="n">
-        <v>-1.576440884683023</v>
+        <v>-1.576440884683025</v>
       </c>
       <c r="F107" t="n">
-        <v>0.02075406377236158</v>
+        <v>0.02075406377236224</v>
       </c>
       <c r="G107" t="n">
         <v>1.699146526632239</v>
@@ -3116,22 +3116,22 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3.216623186227426</v>
+        <v>3.216623186227425</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.4311546262664994</v>
+        <v>-0.431154626266498</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.572597589535271</v>
+        <v>-1.57259758953527</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1721000406428136</v>
+        <v>0.172100040642814</v>
       </c>
       <c r="F108" t="n">
-        <v>0.8438185853079608</v>
+        <v>0.8438185853079632</v>
       </c>
       <c r="G108" t="n">
-        <v>2.355437518210778</v>
+        <v>2.355437518210779</v>
       </c>
     </row>
     <row r="109">
@@ -3141,22 +3141,22 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1.419031303557776</v>
+        <v>1.419031303557775</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.8835396072265423</v>
+        <v>-0.8835396072265405</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.284493238932921</v>
+        <v>-1.28449323893292</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.727969133042968</v>
+        <v>-0.7279691330429683</v>
       </c>
       <c r="F109" t="n">
-        <v>0.5883443989180057</v>
+        <v>0.5883443989180075</v>
       </c>
       <c r="G109" t="n">
-        <v>2.0511564272528</v>
+        <v>2.051156427252802</v>
       </c>
     </row>
     <row r="110">
@@ -3169,13 +3169,13 @@
         <v>1.539199842727658</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.9701855777780007</v>
+        <v>-0.9701855777780021</v>
       </c>
       <c r="D110" t="n">
-        <v>2.261944630732623</v>
+        <v>2.261944630732621</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.1806512213699573</v>
+        <v>-0.1806512213699578</v>
       </c>
       <c r="F110" t="n">
         <v>0.6067564661714181</v>
@@ -3194,16 +3194,16 @@
         <v>0.3320269878203992</v>
       </c>
       <c r="C111" t="n">
-        <v>-1.724787621091628</v>
+        <v>-1.724787621091629</v>
       </c>
       <c r="D111" t="n">
-        <v>2.447053049583766</v>
+        <v>2.447053049583763</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.2093669085122475</v>
+        <v>-0.2093669085122483</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.6728193002905415</v>
+        <v>-0.6728193002905434</v>
       </c>
       <c r="G111" t="n">
         <v>2.371609573871898</v>
@@ -3216,22 +3216,22 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2.980226863603674</v>
+        <v>2.980226863603672</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8733838460084996</v>
+        <v>0.8733838460085012</v>
       </c>
       <c r="D112" t="n">
-        <v>-1.777464340316397</v>
+        <v>-1.777464340316394</v>
       </c>
       <c r="E112" t="n">
-        <v>-1.503915652549578</v>
+        <v>-1.503915652549579</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2511448081360659</v>
+        <v>0.2511448081360677</v>
       </c>
       <c r="G112" t="n">
-        <v>2.189717478082502</v>
+        <v>2.189717478082504</v>
       </c>
     </row>
     <row r="113">
@@ -3241,22 +3241,22 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2.963231493334849</v>
+        <v>2.963231493334848</v>
       </c>
       <c r="C113" t="n">
-        <v>0.7798740514161859</v>
+        <v>0.7798740514161868</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.8212092614068203</v>
+        <v>-0.8212092614068179</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.153274073312916</v>
+        <v>-1.153274073312917</v>
       </c>
       <c r="F113" t="n">
-        <v>0.675246484669455</v>
+        <v>0.6752464846694569</v>
       </c>
       <c r="G113" t="n">
-        <v>2.445950551269787</v>
+        <v>2.445950551269788</v>
       </c>
     </row>
     <row r="114">
@@ -3266,22 +3266,22 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-2.264450097716577</v>
+        <v>-2.264450097716575</v>
       </c>
       <c r="C114" t="n">
         <v>-2.489352228448325</v>
       </c>
       <c r="D114" t="n">
-        <v>2.098624495594011</v>
+        <v>2.098624495594008</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.10938263130116</v>
+        <v>-0.1093826313011605</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.03895816992636211</v>
+        <v>-0.03895816992636347</v>
       </c>
       <c r="G114" t="n">
-        <v>2.105429015772428</v>
+        <v>2.105429015772427</v>
       </c>
     </row>
     <row r="115">
@@ -3291,22 +3291,22 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.8125296561302462</v>
+        <v>-0.8125296561302459</v>
       </c>
       <c r="C115" t="n">
-        <v>-1.472079099865078</v>
+        <v>-1.472079099865075</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.26212284092699</v>
+        <v>-1.262122840926988</v>
       </c>
       <c r="E115" t="n">
         <v>-1.110089546590431</v>
       </c>
       <c r="F115" t="n">
-        <v>0.3357388722078157</v>
+        <v>0.335738872207817</v>
       </c>
       <c r="G115" t="n">
-        <v>1.712674570899483</v>
+        <v>1.712674570899484</v>
       </c>
     </row>
     <row r="116">
@@ -3316,22 +3316,22 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.1716471532704986</v>
+        <v>0.171647153270499</v>
       </c>
       <c r="C116" t="n">
-        <v>-1.55113774161119</v>
+        <v>-1.551137741611191</v>
       </c>
       <c r="D116" t="n">
-        <v>2.462421000713577</v>
+        <v>2.462421000713574</v>
       </c>
       <c r="E116" t="n">
-        <v>0.4665958781700509</v>
+        <v>0.466595878170051</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.2209402022920736</v>
+        <v>-0.2209402022920749</v>
       </c>
       <c r="G116" t="n">
-        <v>2.53630204743449</v>
+        <v>2.536302047434489</v>
       </c>
     </row>
     <row r="117">
@@ -3341,22 +3341,22 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2.97371023896531</v>
+        <v>2.973710238965309</v>
       </c>
       <c r="C117" t="n">
-        <v>-2.349064598510147</v>
+        <v>-2.349064598510145</v>
       </c>
       <c r="D117" t="n">
-        <v>-2.351082737354753</v>
+        <v>-2.351082737354752</v>
       </c>
       <c r="E117" t="n">
-        <v>1.535461665498797</v>
+        <v>1.535461665498801</v>
       </c>
       <c r="F117" t="n">
-        <v>3.302504865988261</v>
+        <v>3.302504865988268</v>
       </c>
       <c r="G117" t="n">
-        <v>2.461721010099457</v>
+        <v>2.461721010099459</v>
       </c>
     </row>
     <row r="118">
@@ -3369,19 +3369,19 @@
         <v>0.8957563220736062</v>
       </c>
       <c r="C118" t="n">
-        <v>-1.976206269847286</v>
+        <v>-1.976206269847287</v>
       </c>
       <c r="D118" t="n">
-        <v>2.111274559084756</v>
+        <v>2.111274559084752</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9105602947064138</v>
+        <v>0.9105602947064145</v>
       </c>
       <c r="F118" t="n">
-        <v>0.04755766728354271</v>
+        <v>0.04755766728354175</v>
       </c>
       <c r="G118" t="n">
-        <v>2.567269894938152</v>
+        <v>2.567269894938151</v>
       </c>
     </row>
     <row r="119">
@@ -3391,22 +3391,22 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-0.7489969610075358</v>
+        <v>-0.7489969610075353</v>
       </c>
       <c r="C119" t="n">
         <v>-2.963415679810057</v>
       </c>
       <c r="D119" t="n">
-        <v>1.977978767617577</v>
+        <v>1.977978767617572</v>
       </c>
       <c r="E119" t="n">
-        <v>1.030358584314974</v>
+        <v>1.030358584314975</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.5547603924229295</v>
+        <v>-0.5547603924229313</v>
       </c>
       <c r="G119" t="n">
-        <v>2.203189639917697</v>
+        <v>2.203189639917696</v>
       </c>
     </row>
     <row r="120">
@@ -3416,22 +3416,22 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4.537863287148288</v>
+        <v>4.537863287148287</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.3470965291217281</v>
+        <v>-0.3470965291217272</v>
       </c>
       <c r="D120" t="n">
         <v>-1.030554795386875</v>
       </c>
       <c r="E120" t="n">
-        <v>1.355402209977573</v>
+        <v>1.355402209977574</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.7183532923190646</v>
+        <v>-0.7183532923190642</v>
       </c>
       <c r="G120" t="n">
-        <v>2.483122943432949</v>
+        <v>2.48312294343295</v>
       </c>
     </row>
     <row r="121">
@@ -3441,22 +3441,22 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.1095685099940603</v>
+        <v>0.1095685099940605</v>
       </c>
       <c r="C121" t="n">
-        <v>-2.987962334392148</v>
+        <v>-2.987962334392145</v>
       </c>
       <c r="D121" t="n">
-        <v>-2.325141000201505</v>
+        <v>-2.325141000201506</v>
       </c>
       <c r="E121" t="n">
-        <v>0.3020051722514078</v>
+        <v>0.3020051722514085</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.6520054892059023</v>
+        <v>-0.6520054892059015</v>
       </c>
       <c r="G121" t="n">
-        <v>1.41959144276309</v>
+        <v>1.419591442763091</v>
       </c>
     </row>
     <row r="122">
@@ -3466,16 +3466,16 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>4.234344600914814</v>
+        <v>4.234344600914811</v>
       </c>
       <c r="C122" t="n">
-        <v>0.03521772307458364</v>
+        <v>0.03521772307458383</v>
       </c>
       <c r="D122" t="n">
         <v>-0.6104984980629383</v>
       </c>
       <c r="E122" t="n">
-        <v>0.9729631694070708</v>
+        <v>0.9729631694070713</v>
       </c>
       <c r="F122" t="n">
         <v>-0.5369440477986557</v>
@@ -3494,19 +3494,19 @@
         <v>1.50832628214832</v>
       </c>
       <c r="C123" t="n">
-        <v>-2.227205801614457</v>
+        <v>-2.227205801614454</v>
       </c>
       <c r="D123" t="n">
-        <v>-1.349372266011108</v>
+        <v>-1.34937226601111</v>
       </c>
       <c r="E123" t="n">
-        <v>0.8439177330835586</v>
+        <v>0.8439177330835591</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.5811836255615815</v>
+        <v>-0.5811836255615813</v>
       </c>
       <c r="G123" t="n">
-        <v>1.882490492086886</v>
+        <v>1.882490492086887</v>
       </c>
     </row>
     <row r="124">
@@ -3516,22 +3516,22 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2.386608600933051</v>
+        <v>2.38660860093305</v>
       </c>
       <c r="C124" t="n">
-        <v>-1.24093159544928</v>
+        <v>-1.240931595449278</v>
       </c>
       <c r="D124" t="n">
-        <v>-1.058117413721145</v>
+        <v>-1.058117413721146</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.1573995152551072</v>
+        <v>-0.1573995152551076</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.3397256353204008</v>
+        <v>-0.3397256353204003</v>
       </c>
       <c r="G124" t="n">
-        <v>2.051094598265961</v>
+        <v>2.051094598265962</v>
       </c>
     </row>
     <row r="125">
@@ -3544,19 +3544,19 @@
         <v>1.494055001250989</v>
       </c>
       <c r="C125" t="n">
-        <v>-1.936790041658746</v>
+        <v>-1.936790041658744</v>
       </c>
       <c r="D125" t="n">
-        <v>-1.977392743005802</v>
+        <v>-1.977392743005803</v>
       </c>
       <c r="E125" t="n">
-        <v>1.038588448218466</v>
+        <v>1.038588448218468</v>
       </c>
       <c r="F125" t="n">
-        <v>0.7358190626987998</v>
+        <v>0.735819062698802</v>
       </c>
       <c r="G125" t="n">
-        <v>2.030724447306778</v>
+        <v>2.030724447306779</v>
       </c>
     </row>
     <row r="126">
@@ -3569,16 +3569,16 @@
         <v>2.342495426879799</v>
       </c>
       <c r="C126" t="n">
-        <v>-2.498028696597507</v>
+        <v>-2.498028696597506</v>
       </c>
       <c r="D126" t="n">
-        <v>-1.306008079135043</v>
+        <v>-1.306008079135045</v>
       </c>
       <c r="E126" t="n">
-        <v>1.527722179071396</v>
+        <v>1.527722179071397</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.5107666564447587</v>
+        <v>-0.5107666564447582</v>
       </c>
       <c r="G126" t="n">
         <v>2.012724679396036</v>
@@ -3594,16 +3594,16 @@
         <v>1.032975630603418</v>
       </c>
       <c r="C127" t="n">
-        <v>-2.908700277339375</v>
+        <v>-2.908700277339374</v>
       </c>
       <c r="D127" t="n">
-        <v>1.65638967226272</v>
+        <v>1.656389672262715</v>
       </c>
       <c r="E127" t="n">
-        <v>1.636271245077607</v>
+        <v>1.636271245077609</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.176215346785682</v>
+        <v>-0.1762153467856826</v>
       </c>
       <c r="G127" t="n">
         <v>2.425967768448829</v>
@@ -3616,22 +3616,22 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2.266442758183566</v>
+        <v>2.266442758183565</v>
       </c>
       <c r="C128" t="n">
-        <v>-2.024981386432087</v>
+        <v>-2.024981386432084</v>
       </c>
       <c r="D128" t="n">
-        <v>-1.839037290403609</v>
+        <v>-1.839037290403611</v>
       </c>
       <c r="E128" t="n">
-        <v>1.384432759523746</v>
+        <v>1.384432759523747</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.5460113970483075</v>
+        <v>-0.5460113970483069</v>
       </c>
       <c r="G128" t="n">
-        <v>1.958286583401054</v>
+        <v>1.958286583401055</v>
       </c>
     </row>
     <row r="129">
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>6.842172179612913</v>
+        <v>6.84217217961291</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.7695964628965734</v>
+        <v>-0.7695964628965719</v>
       </c>
       <c r="D129" t="n">
-        <v>-1.806888049298418</v>
+        <v>-1.806888049298419</v>
       </c>
       <c r="E129" t="n">
-        <v>2.219377802842296</v>
+        <v>2.219377802842298</v>
       </c>
       <c r="F129" t="n">
         <v>-1.005038480131347</v>
@@ -3669,19 +3669,19 @@
         <v>1.909023305041172</v>
       </c>
       <c r="C130" t="n">
-        <v>-1.363011598568051</v>
+        <v>-1.36301159856805</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.8475377465410968</v>
+        <v>-0.8475377465410977</v>
       </c>
       <c r="E130" t="n">
-        <v>0.8012954533772055</v>
+        <v>0.8012954533772059</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.7210715540432888</v>
+        <v>-0.7210715540432889</v>
       </c>
       <c r="G130" t="n">
-        <v>2.096273428956862</v>
+        <v>2.096273428956863</v>
       </c>
     </row>
     <row r="131">
@@ -3691,22 +3691,22 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1.828638938318954</v>
+        <v>1.828638938318953</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.4263038113098841</v>
+        <v>-0.4263038113098824</v>
       </c>
       <c r="D131" t="n">
-        <v>-1.195595935613467</v>
+        <v>-1.195595935613465</v>
       </c>
       <c r="E131" t="n">
-        <v>-1.192476054964748</v>
+        <v>-1.192476054964749</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.2218709043944195</v>
+        <v>-0.2218709043944186</v>
       </c>
       <c r="G131" t="n">
-        <v>1.98659095328797</v>
+        <v>1.986590953287971</v>
       </c>
     </row>
     <row r="132">
@@ -3719,19 +3719,19 @@
         <v>2.097144506609979</v>
       </c>
       <c r="C132" t="n">
-        <v>-2.016794480502424</v>
+        <v>-2.016794480502421</v>
       </c>
       <c r="D132" t="n">
-        <v>-2.171853412966033</v>
+        <v>-2.171853412966034</v>
       </c>
       <c r="E132" t="n">
-        <v>1.140372710368378</v>
+        <v>1.140372710368379</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.6004829770661529</v>
+        <v>-0.6004829770661522</v>
       </c>
       <c r="G132" t="n">
-        <v>1.850380323804276</v>
+        <v>1.850380323804277</v>
       </c>
     </row>
     <row r="133">
@@ -3744,16 +3744,16 @@
         <v>-2.659880920205858</v>
       </c>
       <c r="C133" t="n">
-        <v>0.5817263597017146</v>
+        <v>0.5817263597017139</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2261077391060719</v>
+        <v>0.2261077391060712</v>
       </c>
       <c r="E133" t="n">
-        <v>0.6372310545687212</v>
+        <v>0.637231054568722</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.3016328255649398</v>
+        <v>-0.3016328255649409</v>
       </c>
       <c r="G133" t="n">
         <v>2.237451327282891</v>
@@ -3766,19 +3766,19 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-1.55324796683983</v>
+        <v>-1.553247966839829</v>
       </c>
       <c r="C134" t="n">
-        <v>1.159945263963395</v>
+        <v>1.159945263963394</v>
       </c>
       <c r="D134" t="n">
-        <v>0.0661018916304101</v>
+        <v>0.06610189163041018</v>
       </c>
       <c r="E134" t="n">
         <v>0.436775633386527</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.5128194317398215</v>
+        <v>-0.5128194317398225</v>
       </c>
       <c r="G134" t="n">
         <v>2.322124876224269</v>
@@ -3791,22 +3791,22 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.05102240646716513</v>
+        <v>0.05102240646716471</v>
       </c>
       <c r="C135" t="n">
-        <v>2.644770402642359</v>
+        <v>2.644770402642358</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.3367399296441296</v>
+        <v>-0.3367399296441287</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1628477315154365</v>
+        <v>0.1628477315154367</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.7292843217125511</v>
+        <v>-0.7292843217125522</v>
       </c>
       <c r="G135" t="n">
-        <v>2.521485384160801</v>
+        <v>2.521485384160802</v>
       </c>
     </row>
     <row r="136">
@@ -3816,19 +3816,19 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-0.4114118853150632</v>
+        <v>-0.4114118853150635</v>
       </c>
       <c r="C136" t="n">
-        <v>2.297080782692796</v>
+        <v>2.297080782692795</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.3209299233824855</v>
+        <v>-0.3209299233824852</v>
       </c>
       <c r="E136" t="n">
-        <v>0.1226021542103289</v>
+        <v>0.1226021542103288</v>
       </c>
       <c r="F136" t="n">
-        <v>-1.194091358866186</v>
+        <v>-1.194091358866187</v>
       </c>
       <c r="G136" t="n">
         <v>2.366031854330265</v>
@@ -3844,19 +3844,19 @@
         <v>1.574155328554725</v>
       </c>
       <c r="C137" t="n">
-        <v>3.738640352011697</v>
+        <v>3.738640352011694</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.3357418814520001</v>
+        <v>-0.3357418814519992</v>
       </c>
       <c r="E137" t="n">
-        <v>0.4245549055398301</v>
+        <v>0.4245549055398308</v>
       </c>
       <c r="F137" t="n">
-        <v>-1.062452382198005</v>
+        <v>-1.062452382198006</v>
       </c>
       <c r="G137" t="n">
-        <v>2.778773550497863</v>
+        <v>2.778773550497865</v>
       </c>
     </row>
     <row r="138">
@@ -3866,22 +3866,22 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-2.86691774796456</v>
+        <v>-2.866917747964559</v>
       </c>
       <c r="C138" t="n">
-        <v>0.5942638348690173</v>
+        <v>0.5942638348690169</v>
       </c>
       <c r="D138" t="n">
-        <v>0.07705447803092877</v>
+        <v>0.07705447803092948</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.004694666039584187</v>
+        <v>-0.004694666039584003</v>
       </c>
       <c r="F138" t="n">
-        <v>0.4228692413244797</v>
+        <v>0.4228692413244799</v>
       </c>
       <c r="G138" t="n">
-        <v>2.223387786056885</v>
+        <v>2.223387786056886</v>
       </c>
     </row>
     <row r="139">
@@ -3894,19 +3894,19 @@
         <v>-1.624655840193646</v>
       </c>
       <c r="C139" t="n">
-        <v>1.818686323504345</v>
+        <v>1.818686323504344</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.09510515480824508</v>
+        <v>-0.09510515480824371</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.1421802995513126</v>
+        <v>-0.142180299551313</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.3862921824597976</v>
+        <v>-0.3862921824597982</v>
       </c>
       <c r="G139" t="n">
-        <v>2.327800757639896</v>
+        <v>2.327800757639897</v>
       </c>
     </row>
     <row r="140">
@@ -3916,22 +3916,22 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.09022932653583574</v>
+        <v>0.09022932653583529</v>
       </c>
       <c r="C140" t="n">
-        <v>2.828166794916441</v>
+        <v>2.828166794916438</v>
       </c>
       <c r="D140" t="n">
-        <v>0.1195295161581694</v>
+        <v>0.1195295161581706</v>
       </c>
       <c r="E140" t="n">
-        <v>0.5119995260044338</v>
+        <v>0.511999526004435</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2212047974901072</v>
+        <v>0.2212047974901067</v>
       </c>
       <c r="G140" t="n">
-        <v>2.811599330696371</v>
+        <v>2.811599330696372</v>
       </c>
     </row>
     <row r="141">
@@ -3941,22 +3941,22 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3856285630281259</v>
+        <v>0.3856285630281253</v>
       </c>
       <c r="C141" t="n">
-        <v>2.89246897692229</v>
+        <v>2.892468976922289</v>
       </c>
       <c r="D141" t="n">
         <v>0.5350162300503305</v>
       </c>
       <c r="E141" t="n">
-        <v>0.4148264374011926</v>
+        <v>0.4148264374011923</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.200596191800883</v>
+        <v>-1.200596191800885</v>
       </c>
       <c r="G141" t="n">
-        <v>2.695410281693217</v>
+        <v>2.695410281693218</v>
       </c>
     </row>
     <row r="142">
@@ -3969,19 +3969,19 @@
         <v>-1.992975354535908</v>
       </c>
       <c r="C142" t="n">
-        <v>1.019001490209825</v>
+        <v>1.019001490209824</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.08630783099461956</v>
+        <v>-0.08630783099462019</v>
       </c>
       <c r="E142" t="n">
-        <v>0.2690099107124406</v>
+        <v>0.2690099107124407</v>
       </c>
       <c r="F142" t="n">
-        <v>-1.086205036776972</v>
+        <v>-1.086205036776974</v>
       </c>
       <c r="G142" t="n">
-        <v>2.136736479757284</v>
+        <v>2.136736479757285</v>
       </c>
     </row>
     <row r="143">
@@ -3994,19 +3994,19 @@
         <v>-0.4556813296037188</v>
       </c>
       <c r="C143" t="n">
-        <v>2.281399646184818</v>
+        <v>2.281399646184817</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.3409016791991754</v>
+        <v>-0.340901679199173</v>
       </c>
       <c r="E143" t="n">
-        <v>0.6713802523539808</v>
+        <v>0.6713802523539828</v>
       </c>
       <c r="F143" t="n">
-        <v>2.426258453264439</v>
+        <v>2.426258453264441</v>
       </c>
       <c r="G143" t="n">
-        <v>2.954882287793785</v>
+        <v>2.954882287793787</v>
       </c>
     </row>
     <row r="144">
@@ -4016,22 +4016,22 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-1.861428435646548</v>
+        <v>-1.861428435646547</v>
       </c>
       <c r="C144" t="n">
-        <v>0.6979453299958206</v>
+        <v>0.6979453299958208</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.6057022915659784</v>
+        <v>-0.6057022915659795</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9159042099526967</v>
+        <v>0.9159042099526975</v>
       </c>
       <c r="F144" t="n">
-        <v>-1.775440584254941</v>
+        <v>-1.775440584254943</v>
       </c>
       <c r="G144" t="n">
-        <v>1.991911662371239</v>
+        <v>1.99191166237124</v>
       </c>
     </row>
     <row r="145">
@@ -4041,22 +4041,22 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1.28112292462921</v>
+        <v>1.281122924629209</v>
       </c>
       <c r="C145" t="n">
-        <v>3.513996231819244</v>
+        <v>3.513996231819243</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.434357927027624</v>
+        <v>-0.434357927027622</v>
       </c>
       <c r="E145" t="n">
-        <v>0.4116549744018875</v>
+        <v>0.4116549744018881</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.2501102329732696</v>
+        <v>-0.25011023297327</v>
       </c>
       <c r="G145" t="n">
-        <v>2.824428254541614</v>
+        <v>2.824428254541615</v>
       </c>
     </row>
     <row r="146">
@@ -4066,22 +4066,22 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-0.8032310309116535</v>
+        <v>-0.8032310309116534</v>
       </c>
       <c r="C146" t="n">
-        <v>2.088387627045643</v>
+        <v>2.088387627045642</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.7218320420275312</v>
+        <v>-0.7218320420275279</v>
       </c>
       <c r="E146" t="n">
-        <v>0.7084664352816403</v>
+        <v>0.7084664352816434</v>
       </c>
       <c r="F146" t="n">
-        <v>3.471640522215216</v>
+        <v>3.47164052221522</v>
       </c>
       <c r="G146" t="n">
-        <v>2.992297397362443</v>
+        <v>2.992297397362445</v>
       </c>
     </row>
     <row r="147">
@@ -4091,19 +4091,19 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-4.141317086697408</v>
+        <v>-4.141317086697407</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.1844323770344575</v>
+        <v>-0.1844323770344572</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.4803394424950003</v>
+        <v>-0.4803394424949992</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.01186528899884616</v>
+        <v>-0.011865288998846</v>
       </c>
       <c r="F147" t="n">
-        <v>0.05674552872975166</v>
+        <v>0.05674552872975196</v>
       </c>
       <c r="G147" t="n">
         <v>1.863250632167729</v>
@@ -4116,22 +4116,22 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-0.0009168402738896204</v>
+        <v>-0.0009168402738898804</v>
       </c>
       <c r="C148" t="n">
-        <v>2.572324085095787</v>
+        <v>2.572324085095786</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.2482837194917268</v>
+        <v>-0.2482837194917239</v>
       </c>
       <c r="E148" t="n">
-        <v>0.6709174410343501</v>
+        <v>0.6709174410343522</v>
       </c>
       <c r="F148" t="n">
-        <v>2.460365518868009</v>
+        <v>2.460365518868012</v>
       </c>
       <c r="G148" t="n">
-        <v>3.052385339417484</v>
+        <v>3.052385339417486</v>
       </c>
     </row>
     <row r="149">
@@ -4141,22 +4141,22 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-4.513345977991692</v>
+        <v>-4.51334597799169</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.2278467920222016</v>
+        <v>-0.2278467920222026</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3631259557317028</v>
+        <v>0.3631259557317053</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.5045693462221438</v>
+        <v>-0.504569346222143</v>
       </c>
       <c r="F149" t="n">
-        <v>1.491828202025415</v>
+        <v>1.491828202025417</v>
       </c>
       <c r="G149" t="n">
-        <v>2.122204256854241</v>
+        <v>2.122204256854243</v>
       </c>
     </row>
     <row r="150">
@@ -4166,19 +4166,19 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-3.242025698135956</v>
+        <v>-3.242025698135955</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.7304111800598454</v>
+        <v>-0.7304111800598452</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.03693724919662139</v>
+        <v>-0.0369372491966227</v>
       </c>
       <c r="E150" t="n">
-        <v>0.9648845432904982</v>
+        <v>0.9648845432904991</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.060693496632741</v>
+        <v>-0.06069349663274136</v>
       </c>
       <c r="G150" t="n">
         <v>2.037910447379761</v>
@@ -4191,19 +4191,19 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-1.151176389202471</v>
+        <v>-1.15117638920247</v>
       </c>
       <c r="C151" t="n">
-        <v>0.2497670883415908</v>
+        <v>0.2497670883415904</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.4138642296663495</v>
+        <v>-0.4138642296663517</v>
       </c>
       <c r="E151" t="n">
-        <v>2.345119257307775</v>
+        <v>2.345119257307778</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.6927317260028962</v>
+        <v>-0.6927317260028975</v>
       </c>
       <c r="G151" t="n">
         <v>2.353958206813392</v>
@@ -4216,19 +4216,19 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-2.439700839201843</v>
+        <v>-2.439700839201842</v>
       </c>
       <c r="C152" t="n">
-        <v>0.1425519674914449</v>
+        <v>0.1425519674914446</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.03201976511787162</v>
+        <v>-0.03201976511787239</v>
       </c>
       <c r="E152" t="n">
-        <v>0.8628174876049537</v>
+        <v>0.8628174876049548</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.04651621837521624</v>
+        <v>-0.04651621837521674</v>
       </c>
       <c r="G152" t="n">
         <v>2.213823646660722</v>
@@ -4241,19 +4241,19 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-2.578897144950596</v>
+        <v>-2.578897144950594</v>
       </c>
       <c r="C153" t="n">
-        <v>0.8414405896299196</v>
+        <v>0.8414405896299194</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.1511940825355887</v>
+        <v>-0.1511940825355881</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.1924244229482608</v>
+        <v>-0.1924244229482611</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.2811972299589065</v>
+        <v>-0.2811972299589072</v>
       </c>
       <c r="G153" t="n">
         <v>2.114976731832695</v>
@@ -4266,19 +4266,19 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-3.43626133609625</v>
+        <v>-3.436261336096248</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.2446775521077678</v>
+        <v>-0.2446775521077686</v>
       </c>
       <c r="D154" t="n">
-        <v>0.6387228815394025</v>
+        <v>0.6387228815394022</v>
       </c>
       <c r="E154" t="n">
-        <v>0.551844211236988</v>
+        <v>0.5518442112369888</v>
       </c>
       <c r="F154" t="n">
-        <v>0.406046713764525</v>
+        <v>0.4060467137645249</v>
       </c>
       <c r="G154" t="n">
         <v>2.224478036930559</v>
@@ -4291,22 +4291,22 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-2.760373686353978</v>
+        <v>-2.760373686353977</v>
       </c>
       <c r="C155" t="n">
-        <v>0.9528045877563314</v>
+        <v>0.9528045877563307</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.5934382489122353</v>
+        <v>-0.5934382489122326</v>
       </c>
       <c r="E155" t="n">
-        <v>0.2779495342621806</v>
+        <v>0.2779495342621819</v>
       </c>
       <c r="F155" t="n">
-        <v>1.50995125235221</v>
+        <v>1.509951252352212</v>
       </c>
       <c r="G155" t="n">
-        <v>2.360653385828175</v>
+        <v>2.360653385828176</v>
       </c>
     </row>
     <row r="156">
@@ -4316,22 +4316,22 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-1.411231724688604</v>
+        <v>-1.411231724688603</v>
       </c>
       <c r="C156" t="n">
-        <v>0.9483297598528198</v>
+        <v>0.9483297598528191</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.5574692344484831</v>
+        <v>-0.5574692344484811</v>
       </c>
       <c r="E156" t="n">
-        <v>0.3062228976495382</v>
+        <v>0.30622289764954</v>
       </c>
       <c r="F156" t="n">
-        <v>0.4875842149707524</v>
+        <v>0.4875842149707536</v>
       </c>
       <c r="G156" t="n">
-        <v>2.326024631400954</v>
+        <v>2.326024631400955</v>
       </c>
     </row>
     <row r="157">
@@ -4341,22 +4341,22 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-2.581173744467304</v>
+        <v>-2.581173744467303</v>
       </c>
       <c r="C157" t="n">
         <v>1.25213874847473</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.5216023525975783</v>
+        <v>-0.521602352597576</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.07736697576897676</v>
+        <v>-0.07736697576897671</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.02387642351555256</v>
+        <v>-0.02387642351555248</v>
       </c>
       <c r="G157" t="n">
-        <v>2.160574503947267</v>
+        <v>2.160574503947268</v>
       </c>
     </row>
     <row r="158">
@@ -4369,16 +4369,16 @@
         <v>-1.373047849338763</v>
       </c>
       <c r="C158" t="n">
-        <v>1.395703867641043</v>
+        <v>1.395703867641041</v>
       </c>
       <c r="D158" t="n">
-        <v>0.2457503571397776</v>
+        <v>0.2457503571397784</v>
       </c>
       <c r="E158" t="n">
-        <v>0.2759666513892742</v>
+        <v>0.275966651389274</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.4042775050966564</v>
+        <v>-0.4042775050966572</v>
       </c>
       <c r="G158" t="n">
         <v>2.396291383950244</v>
@@ -4394,19 +4394,19 @@
         <v>-1.106447438167609</v>
       </c>
       <c r="C159" t="n">
-        <v>1.159301123999511</v>
+        <v>1.15930112399951</v>
       </c>
       <c r="D159" t="n">
-        <v>0.1506203614877049</v>
+        <v>0.1506203614877053</v>
       </c>
       <c r="E159" t="n">
-        <v>0.5551811156139007</v>
+        <v>0.5551811156139014</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.1776683158246657</v>
+        <v>-0.1776683158246658</v>
       </c>
       <c r="G159" t="n">
-        <v>2.435446972553423</v>
+        <v>2.435446972553424</v>
       </c>
     </row>
     <row r="160">
@@ -4416,19 +4416,19 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-3.195690729618029</v>
+        <v>-3.195690729618028</v>
       </c>
       <c r="C160" t="n">
-        <v>0.4825169087612939</v>
+        <v>0.482516908761293</v>
       </c>
       <c r="D160" t="n">
-        <v>0.3744859909660251</v>
+        <v>0.3744859909660261</v>
       </c>
       <c r="E160" t="n">
-        <v>0.0555784626785556</v>
+        <v>0.05557846267855571</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3289721812868349</v>
+        <v>0.3289721812868353</v>
       </c>
       <c r="G160" t="n">
         <v>2.226973269905113</v>
@@ -4441,19 +4441,19 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-3.510178099878564</v>
+        <v>-3.510178099878563</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.06305290565901274</v>
+        <v>-0.06305290565901372</v>
       </c>
       <c r="D161" t="n">
-        <v>0.1992687207339622</v>
+        <v>0.1992687207339627</v>
       </c>
       <c r="E161" t="n">
-        <v>0.3010141847338035</v>
+        <v>0.3010141847338039</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.02448702938226801</v>
+        <v>-0.02448702938226815</v>
       </c>
       <c r="G161" t="n">
         <v>2.074170629105309</v>
@@ -4466,19 +4466,19 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-2.802382558568401</v>
+        <v>-2.8023825585684</v>
       </c>
       <c r="C162" t="n">
-        <v>0.5202305328356266</v>
+        <v>0.5202305328356256</v>
       </c>
       <c r="D162" t="n">
-        <v>0.3364094618074827</v>
+        <v>0.3364094618074828</v>
       </c>
       <c r="E162" t="n">
-        <v>0.4188136406937694</v>
+        <v>0.41881364069377</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.2525268163382256</v>
+        <v>-0.2525268163382263</v>
       </c>
       <c r="G162" t="n">
         <v>2.216673110272878</v>
@@ -4497,16 +4497,16 @@
         <v>1.631616508994628</v>
       </c>
       <c r="D163" t="n">
-        <v>-1.068978085685103</v>
+        <v>-1.0689780856851</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.2755671803498808</v>
+        <v>-0.275567180349881</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.7522664682617017</v>
+        <v>-0.7522664682617023</v>
       </c>
       <c r="G163" t="n">
-        <v>2.034841982253901</v>
+        <v>2.034841982253903</v>
       </c>
     </row>
     <row r="164">
@@ -4516,22 +4516,22 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-3.758612310991614</v>
+        <v>-3.758612310991612</v>
       </c>
       <c r="C164" t="n">
-        <v>0.09935429824762962</v>
+        <v>0.09935429824762949</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.4743599055680986</v>
+        <v>-0.4743599055680971</v>
       </c>
       <c r="E164" t="n">
-        <v>0.03575774137811578</v>
+        <v>0.03575774137811642</v>
       </c>
       <c r="F164" t="n">
-        <v>0.2080320203356396</v>
+        <v>0.2080320203356401</v>
       </c>
       <c r="G164" t="n">
-        <v>1.962270156315282</v>
+        <v>1.962270156315283</v>
       </c>
     </row>
     <row r="165">
@@ -4541,22 +4541,22 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-3.074779840474537</v>
+        <v>-3.074779840474536</v>
       </c>
       <c r="C165" t="n">
         <v>0.6453997802115087</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.8434162717686631</v>
+        <v>-0.8434162717686613</v>
       </c>
       <c r="E165" t="n">
-        <v>0.3639135508736945</v>
+        <v>0.3639135508736957</v>
       </c>
       <c r="F165" t="n">
-        <v>1.094157600689859</v>
+        <v>1.09415760068986</v>
       </c>
       <c r="G165" t="n">
-        <v>2.19947907359759</v>
+        <v>2.199479073597591</v>
       </c>
     </row>
     <row r="166">
@@ -4566,22 +4566,22 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-4.68886119658462</v>
+        <v>-4.688861196584618</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.8075047608284311</v>
+        <v>-0.8075047608284306</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.6543597642288085</v>
+        <v>-0.654359764228807</v>
       </c>
       <c r="E166" t="n">
-        <v>0.2707578771571686</v>
+        <v>0.2707578771571704</v>
       </c>
       <c r="F166" t="n">
-        <v>1.712434519322673</v>
+        <v>1.712434519322675</v>
       </c>
       <c r="G166" t="n">
-        <v>1.980061994995101</v>
+        <v>1.980061994995102</v>
       </c>
     </row>
     <row r="167">
@@ -4591,22 +4591,22 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-4.185837621709718</v>
+        <v>-4.185837621709716</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.8235847569029561</v>
+        <v>-0.8235847569029555</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.6836513076621652</v>
+        <v>-0.683651307662165</v>
       </c>
       <c r="E167" t="n">
-        <v>0.3289455898705217</v>
+        <v>0.3289455898705219</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.1359963094813013</v>
+        <v>-0.1359963094813015</v>
       </c>
       <c r="G167" t="n">
-        <v>1.749005322801854</v>
+        <v>1.749005322801855</v>
       </c>
     </row>
     <row r="168">
@@ -4616,22 +4616,22 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-3.190250970880944</v>
+        <v>-3.190250970880943</v>
       </c>
       <c r="C168" t="n">
-        <v>0.7317719760849947</v>
+        <v>0.7317719760849941</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.6438057482755478</v>
+        <v>-0.6438057482755455</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.1315481080118148</v>
+        <v>-0.1315481080118147</v>
       </c>
       <c r="F168" t="n">
-        <v>0.5081568813577235</v>
+        <v>0.5081568813577246</v>
       </c>
       <c r="G168" t="n">
-        <v>2.089634443137524</v>
+        <v>2.089634443137526</v>
       </c>
     </row>
     <row r="169">
@@ -4641,22 +4641,22 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-4.810413324261017</v>
+        <v>-4.810413324261015</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.4820904001367389</v>
+        <v>-0.4820904001367383</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.6211647391765079</v>
+        <v>-0.6211647391765061</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.1735720320163709</v>
+        <v>-0.1735720320163703</v>
       </c>
       <c r="F169" t="n">
-        <v>0.850042454471434</v>
+        <v>0.850042454471435</v>
       </c>
       <c r="G169" t="n">
-        <v>1.840548077590976</v>
+        <v>1.840548077590977</v>
       </c>
     </row>
     <row r="170">
@@ -4666,22 +4666,22 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-0.469918918221544</v>
+        <v>-0.4699189182215443</v>
       </c>
       <c r="C170" t="n">
-        <v>2.404075708339076</v>
+        <v>2.404075708339075</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.470213259509207</v>
+        <v>-0.4702132595092057</v>
       </c>
       <c r="E170" t="n">
-        <v>0.4385462480233608</v>
+        <v>0.4385462480233604</v>
       </c>
       <c r="F170" t="n">
-        <v>-1.17165851049401</v>
+        <v>-1.171658510494012</v>
       </c>
       <c r="G170" t="n">
-        <v>2.393307037852836</v>
+        <v>2.393307037852837</v>
       </c>
     </row>
     <row r="171">
@@ -4691,22 +4691,22 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.5639311574533636</v>
+        <v>0.5639311574533632</v>
       </c>
       <c r="C171" t="n">
-        <v>3.144907615587742</v>
+        <v>3.144907615587739</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.4650455086744995</v>
+        <v>-0.4650455086744957</v>
       </c>
       <c r="E171" t="n">
-        <v>0.697344672657509</v>
+        <v>0.6973446726575118</v>
       </c>
       <c r="F171" t="n">
-        <v>3.07319366785422</v>
+        <v>3.073193667854224</v>
       </c>
       <c r="G171" t="n">
-        <v>3.232749633922047</v>
+        <v>3.232749633922049</v>
       </c>
     </row>
     <row r="172">
@@ -4716,22 +4716,22 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-3.520703057690538</v>
+        <v>-3.520703057690537</v>
       </c>
       <c r="C172" t="n">
-        <v>0.3135571086324083</v>
+        <v>0.3135571086324089</v>
       </c>
       <c r="D172" t="n">
-        <v>-1.230057082428342</v>
+        <v>-1.23005708242834</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.5572789064304755</v>
+        <v>-0.5572789064304754</v>
       </c>
       <c r="F172" t="n">
-        <v>0.2570025709125904</v>
+        <v>0.2570025709125911</v>
       </c>
       <c r="G172" t="n">
-        <v>1.814015012552385</v>
+        <v>1.814015012552386</v>
       </c>
     </row>
     <row r="173">
@@ -4747,16 +4747,16 @@
         <v>0.6879196415360052</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.9984289821318733</v>
+        <v>-0.9984289821318713</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.07511486816851831</v>
+        <v>-0.07511486816851791</v>
       </c>
       <c r="F173" t="n">
-        <v>0.4552761016617888</v>
+        <v>0.4552761016617894</v>
       </c>
       <c r="G173" t="n">
-        <v>2.035944702964898</v>
+        <v>2.035944702964899</v>
       </c>
     </row>
     <row r="174">
@@ -4772,16 +4772,16 @@
         <v>1.721196139976914</v>
       </c>
       <c r="D174" t="n">
-        <v>-1.245441852743973</v>
+        <v>-1.245441852743968</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.2187613768492899</v>
+        <v>-0.2187613768492871</v>
       </c>
       <c r="F174" t="n">
-        <v>3.342005881826272</v>
+        <v>3.342005881826277</v>
       </c>
       <c r="G174" t="n">
-        <v>2.58173120276074</v>
+        <v>2.581731202760742</v>
       </c>
     </row>
     <row r="175">
@@ -4791,19 +4791,19 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-3.54708639464208</v>
+        <v>-3.547086394642079</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.3679391199235528</v>
+        <v>-0.3679391199235527</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.5645995936718938</v>
+        <v>-0.5645995936718937</v>
       </c>
       <c r="E175" t="n">
-        <v>0.7910971372700197</v>
+        <v>0.7910971372700207</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.02931360735713913</v>
+        <v>-0.02931360735713957</v>
       </c>
       <c r="G175" t="n">
         <v>1.956837125037536</v>
@@ -4816,22 +4816,22 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-4.108049826135982</v>
+        <v>-4.108049826135981</v>
       </c>
       <c r="C176" t="n">
-        <v>0.009180138479683136</v>
+        <v>0.009180138479683252</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.5500708506679908</v>
+        <v>-0.5500708506679891</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.1144720813057002</v>
+        <v>-0.1144720813056999</v>
       </c>
       <c r="F176" t="n">
-        <v>0.4203976788765076</v>
+        <v>0.4203976788765081</v>
       </c>
       <c r="G176" t="n">
-        <v>1.921488818329889</v>
+        <v>1.92148881832989</v>
       </c>
     </row>
     <row r="177">
@@ -4841,22 +4841,22 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-5.902345788846264</v>
+        <v>-5.902345788846261</v>
       </c>
       <c r="C177" t="n">
-        <v>-1.52049748079914</v>
+        <v>-1.520497480799139</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.3232936172527501</v>
+        <v>-0.3232936172527495</v>
       </c>
       <c r="E177" t="n">
-        <v>0.0649993372270171</v>
+        <v>0.06499933722701789</v>
       </c>
       <c r="F177" t="n">
-        <v>0.9029263946437102</v>
+        <v>0.9029263946437107</v>
       </c>
       <c r="G177" t="n">
-        <v>1.697702529447634</v>
+        <v>1.697702529447635</v>
       </c>
     </row>
     <row r="178">
@@ -4866,19 +4866,19 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>-3.960616696665573</v>
+        <v>-3.960616696665571</v>
       </c>
       <c r="C178" t="n">
-        <v>0.03006659771482753</v>
+        <v>0.03006659771482772</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.4711193811620099</v>
+        <v>-0.4711193811620091</v>
       </c>
       <c r="E178" t="n">
-        <v>0.01136404650554766</v>
+        <v>0.0113640465055475</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.2681371305397149</v>
+        <v>-0.2681371305397157</v>
       </c>
       <c r="G178" t="n">
         <v>1.864533266905906</v>
@@ -4891,19 +4891,19 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>-2.936918600390152</v>
+        <v>-2.936918600390151</v>
       </c>
       <c r="C179" t="n">
-        <v>0.1665916799276767</v>
+        <v>0.1665916799276758</v>
       </c>
       <c r="D179" t="n">
-        <v>0.2316925153583238</v>
+        <v>0.2316925153583246</v>
       </c>
       <c r="E179" t="n">
-        <v>0.04650945874169456</v>
+        <v>0.0465094587416947</v>
       </c>
       <c r="F179" t="n">
-        <v>0.1891153940625758</v>
+        <v>0.1891153940625761</v>
       </c>
       <c r="G179" t="n">
         <v>2.156624834714633</v>
@@ -4916,19 +4916,19 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-2.983722098231791</v>
+        <v>-2.98372209823179</v>
       </c>
       <c r="C180" t="n">
-        <v>0.3699778028954989</v>
+        <v>0.3699778028954983</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.1606453834415504</v>
+        <v>-0.1606453834415492</v>
       </c>
       <c r="E180" t="n">
-        <v>0.2947857833110621</v>
+        <v>0.2947857833110632</v>
       </c>
       <c r="F180" t="n">
-        <v>1.231274817110714</v>
+        <v>1.231274817110715</v>
       </c>
       <c r="G180" t="n">
         <v>2.297202467234839</v>
@@ -4941,22 +4941,22 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-2.524291739508804</v>
+        <v>-2.524291739508803</v>
       </c>
       <c r="C181" t="n">
-        <v>0.9536585525384379</v>
+        <v>0.953658552538437</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.03807721227876779</v>
+        <v>-0.03807721227876688</v>
       </c>
       <c r="E181" t="n">
-        <v>0.08817596612237134</v>
+        <v>0.08817596612237175</v>
       </c>
       <c r="F181" t="n">
         <v>0.5216125667239547</v>
       </c>
       <c r="G181" t="n">
-        <v>2.306931397631996</v>
+        <v>2.306931397631997</v>
       </c>
     </row>
     <row r="182">
@@ -4966,19 +4966,19 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-2.013017868520377</v>
+        <v>-2.013017868520376</v>
       </c>
       <c r="C182" t="n">
-        <v>1.013142727929477</v>
+        <v>1.013142727929476</v>
       </c>
       <c r="D182" t="n">
-        <v>0.07368187339158484</v>
+        <v>0.07368187339158443</v>
       </c>
       <c r="E182" t="n">
-        <v>0.5288516589971349</v>
+        <v>0.5288516589971347</v>
       </c>
       <c r="F182" t="n">
-        <v>-0.7056868162947558</v>
+        <v>-0.7056868162947572</v>
       </c>
       <c r="G182" t="n">
         <v>2.249953539859346</v>
@@ -4991,19 +4991,19 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>-2.324733581296837</v>
+        <v>-2.324733581296836</v>
       </c>
       <c r="C183" t="n">
-        <v>0.9722756047535895</v>
+        <v>0.9722756047535885</v>
       </c>
       <c r="D183" t="n">
-        <v>0.0725763802093511</v>
+        <v>0.07257638020935145</v>
       </c>
       <c r="E183" t="n">
-        <v>0.3320104059494367</v>
+        <v>0.3320104059494368</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.1000156031009907</v>
+        <v>-0.1000156031009914</v>
       </c>
       <c r="G183" t="n">
         <v>2.283687347209508</v>
@@ -5019,16 +5019,16 @@
         <v>-2.187752253661311</v>
       </c>
       <c r="C184" t="n">
-        <v>0.7339863349705229</v>
+        <v>0.7339863349705223</v>
       </c>
       <c r="D184" t="n">
-        <v>0.1042823855986838</v>
+        <v>0.1042823855986836</v>
       </c>
       <c r="E184" t="n">
-        <v>0.456616141058968</v>
+        <v>0.4566161410589682</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.4476214874188126</v>
+        <v>-0.4476214874188136</v>
       </c>
       <c r="G184" t="n">
         <v>2.231048248706692</v>
@@ -5044,19 +5044,19 @@
         <v>-1.330882486634583</v>
       </c>
       <c r="C185" t="n">
-        <v>1.257954690354242</v>
+        <v>1.257954690354241</v>
       </c>
       <c r="D185" t="n">
-        <v>0.07673594645472889</v>
+        <v>0.07673594645472878</v>
       </c>
       <c r="E185" t="n">
-        <v>0.6046416302846215</v>
+        <v>0.6046416302846217</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.6588779620603112</v>
+        <v>-0.6588779620603125</v>
       </c>
       <c r="G185" t="n">
-        <v>2.354701135242428</v>
+        <v>2.354701135242429</v>
       </c>
     </row>
     <row r="186">
@@ -5066,19 +5066,19 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-0.8218360378718387</v>
+        <v>-0.8218360378718385</v>
       </c>
       <c r="C186" t="n">
-        <v>1.875976569729429</v>
+        <v>1.875976569729428</v>
       </c>
       <c r="D186" t="n">
-        <v>0.2959118269430437</v>
+        <v>0.2959118269430438</v>
       </c>
       <c r="E186" t="n">
-        <v>0.5342310612743216</v>
+        <v>0.5342310612743217</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.6395430371529254</v>
+        <v>-0.6395430371529269</v>
       </c>
       <c r="G186" t="n">
         <v>2.513430666320724</v>
@@ -5091,19 +5091,19 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-2.00387448101298</v>
+        <v>-2.003874481012979</v>
       </c>
       <c r="C187" t="n">
-        <v>1.145913294481564</v>
+        <v>1.145913294481563</v>
       </c>
       <c r="D187" t="n">
         <v>0.2123490308111696</v>
       </c>
       <c r="E187" t="n">
-        <v>0.4117629353417954</v>
+        <v>0.4117629353417953</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.3350270227443484</v>
+        <v>-0.3350270227443495</v>
       </c>
       <c r="G187" t="n">
         <v>2.332935920758041</v>
@@ -5119,16 +5119,16 @@
         <v>-2.455206264957245</v>
       </c>
       <c r="C188" t="n">
-        <v>0.1755632645769141</v>
+        <v>0.1755632645769131</v>
       </c>
       <c r="D188" t="n">
-        <v>0.2197974878143911</v>
+        <v>0.2197974878143908</v>
       </c>
       <c r="E188" t="n">
-        <v>0.8897147236621819</v>
+        <v>0.8897147236621835</v>
       </c>
       <c r="F188" t="n">
-        <v>1.238337014231035</v>
+        <v>1.238337014231036</v>
       </c>
       <c r="G188" t="n">
         <v>2.452046058937082</v>
@@ -5141,22 +5141,22 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-2.340303423626747</v>
+        <v>-2.340303423626746</v>
       </c>
       <c r="C189" t="n">
-        <v>1.153587063923145</v>
+        <v>1.153587063923144</v>
       </c>
       <c r="D189" t="n">
-        <v>0.3118922555744778</v>
+        <v>0.3118922555744776</v>
       </c>
       <c r="E189" t="n">
-        <v>0.4364205492945742</v>
+        <v>0.4364205492945743</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.5830855910769702</v>
+        <v>-0.5830855910769717</v>
       </c>
       <c r="G189" t="n">
-        <v>2.291570420175599</v>
+        <v>2.2915704201756</v>
       </c>
     </row>
     <row r="190">
@@ -5169,19 +5169,19 @@
         <v>-0.5171609633397494</v>
       </c>
       <c r="C190" t="n">
-        <v>1.6943120196512</v>
+        <v>1.694312019651198</v>
       </c>
       <c r="D190" t="n">
         <v>1.000870237260326</v>
       </c>
       <c r="E190" t="n">
-        <v>0.6522929198930111</v>
+        <v>0.652292919893011</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.5340608389236194</v>
+        <v>-0.5340608389236209</v>
       </c>
       <c r="G190" t="n">
-        <v>2.66358572557284</v>
+        <v>2.663585725572841</v>
       </c>
     </row>
     <row r="191">
@@ -5191,19 +5191,19 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>-2.940155623136333</v>
+        <v>-2.940155623136332</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.1080974265040334</v>
+        <v>-0.1080974265040329</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.2214655288718388</v>
+        <v>-0.2214655288718398</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3859934558355891</v>
+        <v>0.3859934558355894</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.6050807259304319</v>
+        <v>-0.6050807259304329</v>
       </c>
       <c r="G191" t="n">
         <v>1.965573784935676</v>
@@ -5216,22 +5216,22 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-4.105839313524629</v>
+        <v>-4.105839313524627</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.8686905438922697</v>
+        <v>-0.8686905438922694</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.1911591883863978</v>
+        <v>-0.1911591883863987</v>
       </c>
       <c r="E192" t="n">
-        <v>0.2947578242478518</v>
+        <v>0.2947578242478527</v>
       </c>
       <c r="F192" t="n">
         <v>0.2623200431468876</v>
       </c>
       <c r="G192" t="n">
-        <v>1.887965471466098</v>
+        <v>1.887965471466099</v>
       </c>
     </row>
     <row r="193">
@@ -5241,22 +5241,22 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-4.756711921702698</v>
+        <v>-4.756711921702694</v>
       </c>
       <c r="C193" t="n">
-        <v>-1.17736905892881</v>
+        <v>-1.177369058928809</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2255743639278613</v>
+        <v>-0.2255743639278622</v>
       </c>
       <c r="E193" t="n">
-        <v>0.01017673150811147</v>
+        <v>0.0101767315081114</v>
       </c>
       <c r="F193" t="n">
-        <v>-0.2133494205605597</v>
+        <v>-0.21334942056056</v>
       </c>
       <c r="G193" t="n">
-        <v>1.68255615038818</v>
+        <v>1.682556150388181</v>
       </c>
     </row>
     <row r="194">
@@ -5266,19 +5266,19 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>-4.983158489062824</v>
+        <v>-4.983158489062821</v>
       </c>
       <c r="C194" t="n">
         <v>-1.489073936010241</v>
       </c>
       <c r="D194" t="n">
-        <v>0.1429728031931556</v>
+        <v>0.1429728031931542</v>
       </c>
       <c r="E194" t="n">
-        <v>0.3327282763969321</v>
+        <v>0.3327282763969324</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.1782187716001077</v>
+        <v>-0.1782187716001085</v>
       </c>
       <c r="G194" t="n">
         <v>1.729839265233774</v>
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>-5.053988926513258</v>
+        <v>-5.053988926513257</v>
       </c>
       <c r="C195" t="n">
         <v>-1.463747012355636</v>
       </c>
       <c r="D195" t="n">
-        <v>0.1699012675676762</v>
+        <v>0.169901267567674</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1906505373581875</v>
+        <v>0.1906505373581873</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.5846043798639832</v>
+        <v>-0.5846043798639847</v>
       </c>
       <c r="G195" t="n">
         <v>1.655355032934677</v>
@@ -5319,16 +5319,16 @@
         <v>-2.486303803133826</v>
       </c>
       <c r="C196" t="n">
-        <v>0.9974300436367265</v>
+        <v>0.9974300436367262</v>
       </c>
       <c r="D196" t="n">
-        <v>0.08484399723816416</v>
+        <v>0.08484399723816391</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.1826213398967675</v>
+        <v>-0.1826213398967681</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.7872752502013224</v>
+        <v>-0.7872752502013239</v>
       </c>
       <c r="G196" t="n">
         <v>2.112084856300919</v>
@@ -5341,22 +5341,22 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-1.604782727595732</v>
+        <v>-1.604782727595731</v>
       </c>
       <c r="C197" t="n">
-        <v>1.891855834533084</v>
+        <v>1.891855834533083</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.3887998443300119</v>
+        <v>-0.388799844330011</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.4644985259845586</v>
+        <v>-0.4644985259845594</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.7265285935515164</v>
+        <v>-0.7265285935515176</v>
       </c>
       <c r="G197" t="n">
-        <v>2.199079042961261</v>
+        <v>2.199079042961262</v>
       </c>
     </row>
     <row r="198">
@@ -5366,19 +5366,19 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>-2.809650654383938</v>
+        <v>-2.809650654383936</v>
       </c>
       <c r="C198" t="n">
-        <v>0.1363566327375006</v>
+        <v>0.1363566327375003</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.1830625996734525</v>
+        <v>-0.1830625996734528</v>
       </c>
       <c r="E198" t="n">
-        <v>0.4546077021090476</v>
+        <v>0.4546077021090479</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.3131136432768201</v>
+        <v>-0.3131136432768206</v>
       </c>
       <c r="G198" t="n">
         <v>2.068065267196406</v>
@@ -5391,22 +5391,22 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>-2.690555846556655</v>
+        <v>-2.690555846556654</v>
       </c>
       <c r="C199" t="n">
-        <v>0.7548653019835587</v>
+        <v>0.7548653019835583</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.3023446639026404</v>
+        <v>-0.3023446639026393</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1421800071269152</v>
+        <v>0.1421800071269163</v>
       </c>
       <c r="F199" t="n">
-        <v>0.769345116326919</v>
+        <v>0.7693451163269198</v>
       </c>
       <c r="G199" t="n">
-        <v>2.263291402362695</v>
+        <v>2.263291402362696</v>
       </c>
     </row>
     <row r="200">
@@ -5419,19 +5419,19 @@
         <v>-2.63200340774512</v>
       </c>
       <c r="C200" t="n">
-        <v>0.9154427833611247</v>
+        <v>0.9154427833611242</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.3384751131370404</v>
+        <v>-0.3384751131370389</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.1165489718296747</v>
+        <v>-0.1165489718296746</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3475570768303943</v>
+        <v>0.3475570768303948</v>
       </c>
       <c r="G200" t="n">
-        <v>2.190325534865725</v>
+        <v>2.190325534865726</v>
       </c>
     </row>
     <row r="201">
@@ -5441,22 +5441,22 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-2.427139790704279</v>
+        <v>-2.427139790704278</v>
       </c>
       <c r="C201" t="n">
         <v>1.133731828355369</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.1736878050238442</v>
+        <v>-0.1736878050238431</v>
       </c>
       <c r="E201" t="n">
         <v>-0.1317246647795638</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.01083940968724928</v>
+        <v>-0.01083940968724953</v>
       </c>
       <c r="G201" t="n">
-        <v>2.211204947752738</v>
+        <v>2.211204947752739</v>
       </c>
     </row>
     <row r="202">
@@ -5466,22 +5466,22 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>-0.492158973968328</v>
+        <v>-0.4921589739683283</v>
       </c>
       <c r="C202" t="n">
-        <v>2.533528760030684</v>
+        <v>2.533528760030682</v>
       </c>
       <c r="D202" t="n">
-        <v>0.06532341884622925</v>
+        <v>0.06532341884623011</v>
       </c>
       <c r="E202" t="n">
-        <v>0.1975350566441591</v>
+        <v>0.1975350566441587</v>
       </c>
       <c r="F202" t="n">
-        <v>-0.7423288107261099</v>
+        <v>-0.7423288107261113</v>
       </c>
       <c r="G202" t="n">
-        <v>2.535023427331285</v>
+        <v>2.535023427331286</v>
       </c>
     </row>
     <row r="203">
@@ -5494,19 +5494,19 @@
         <v>-1.094691571851184</v>
       </c>
       <c r="C203" t="n">
-        <v>2.256734289357667</v>
+        <v>2.256734289357665</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.01490333644465504</v>
+        <v>-0.01490333644465395</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1681639460635104</v>
+        <v>0.1681639460635105</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.1126670340673456</v>
+        <v>-0.1126670340673462</v>
       </c>
       <c r="G203" t="n">
-        <v>2.523457310390944</v>
+        <v>2.523457310390945</v>
       </c>
     </row>
     <row r="204">
@@ -5519,19 +5519,19 @@
         <v>-1.884481385449269</v>
       </c>
       <c r="C204" t="n">
-        <v>1.107286926342101</v>
+        <v>1.1072869263421</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.006178164676951891</v>
+        <v>-0.0061781646769517</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2318200203316245</v>
+        <v>0.2318200203316247</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.1304338789794753</v>
+        <v>-0.1304338789794757</v>
       </c>
       <c r="G204" t="n">
-        <v>2.306706400601063</v>
+        <v>2.306706400601064</v>
       </c>
     </row>
     <row r="205">
@@ -5544,19 +5544,19 @@
         <v>-1.905685478647686</v>
       </c>
       <c r="C205" t="n">
-        <v>1.025487315734785</v>
+        <v>1.025487315734784</v>
       </c>
       <c r="D205" t="n">
-        <v>0.172545156723566</v>
+        <v>0.1725451567235661</v>
       </c>
       <c r="E205" t="n">
-        <v>0.009979361821890246</v>
+        <v>0.00997936182189052</v>
       </c>
       <c r="F205" t="n">
         <v>0.2840115438054184</v>
       </c>
       <c r="G205" t="n">
-        <v>2.35742806758786</v>
+        <v>2.357428067587861</v>
       </c>
     </row>
     <row r="206">
@@ -5566,19 +5566,19 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-5.026561017200922</v>
+        <v>-5.026561017200919</v>
       </c>
       <c r="C206" t="n">
-        <v>-2.147196108988696</v>
+        <v>-2.147196108988695</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.0622102276949129</v>
+        <v>-0.0622102276949161</v>
       </c>
       <c r="E206" t="n">
-        <v>0.6183568982801889</v>
+        <v>0.6183568982801894</v>
       </c>
       <c r="F206" t="n">
-        <v>-1.108025431067092</v>
+        <v>-1.108025431067093</v>
       </c>
       <c r="G206" t="n">
         <v>1.497984556247476</v>
@@ -5597,16 +5597,16 @@
         <v>1.60572455480436</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.2824524602333997</v>
+        <v>-0.2824524602333993</v>
       </c>
       <c r="E207" t="n">
-        <v>0.1091544520300793</v>
+        <v>0.1091544520300794</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.5814012152830668</v>
+        <v>-0.5814012152830678</v>
       </c>
       <c r="G207" t="n">
-        <v>2.280966722486821</v>
+        <v>2.280966722486822</v>
       </c>
     </row>
     <row r="208">
@@ -5616,19 +5616,19 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-2.308302018755982</v>
+        <v>-2.30830201875598</v>
       </c>
       <c r="C208" t="n">
-        <v>1.003131569158714</v>
+        <v>1.003131569158713</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.0354731579512202</v>
+        <v>-0.03547315795122018</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3149888514582518</v>
+        <v>0.3149888514582516</v>
       </c>
       <c r="F208" t="n">
-        <v>-0.7686110148688693</v>
+        <v>-0.7686110148688708</v>
       </c>
       <c r="G208" t="n">
         <v>2.170724858175055</v>
@@ -5641,22 +5641,22 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-2.685456175718473</v>
+        <v>-2.685456175718471</v>
       </c>
       <c r="C209" t="n">
-        <v>0.3636594875885844</v>
+        <v>0.3636594875885845</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.3716301381617754</v>
+        <v>-0.3716301381617755</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3952472834481091</v>
+        <v>0.3952472834481093</v>
       </c>
       <c r="F209" t="n">
-        <v>-0.2171915829150729</v>
+        <v>-0.2171915829150734</v>
       </c>
       <c r="G209" t="n">
-        <v>2.083872627006261</v>
+        <v>2.083872627006262</v>
       </c>
     </row>
     <row r="210">
@@ -5666,22 +5666,22 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-2.924800481997058</v>
+        <v>-2.924800481997057</v>
       </c>
       <c r="C210" t="n">
-        <v>0.298824379653224</v>
+        <v>0.2988243796532243</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.2047355414983923</v>
+        <v>-0.2047355414983929</v>
       </c>
       <c r="E210" t="n">
-        <v>0.3002658069252208</v>
+        <v>0.3002658069252207</v>
       </c>
       <c r="F210" t="n">
-        <v>-0.962525031586438</v>
+        <v>-0.9625250315864396</v>
       </c>
       <c r="G210" t="n">
-        <v>1.963913055496472</v>
+        <v>1.963913055496473</v>
       </c>
     </row>
     <row r="211">
@@ -5694,16 +5694,16 @@
         <v>-3.98006376611318</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.9547041114529285</v>
+        <v>-0.9547041114529282</v>
       </c>
       <c r="D211" t="n">
-        <v>0.07028394015126727</v>
+        <v>0.07028394015126524</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3316121209436056</v>
+        <v>0.3316121209436059</v>
       </c>
       <c r="F211" t="n">
-        <v>-1.007269503210028</v>
+        <v>-1.00726950321003</v>
       </c>
       <c r="G211" t="n">
         <v>1.749691462066005</v>
@@ -5716,19 +5716,19 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-3.332509643481063</v>
+        <v>-3.332509643481061</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.6085943996875534</v>
+        <v>-0.6085943996875528</v>
       </c>
       <c r="D212" t="n">
-        <v>0.05227739231763506</v>
+        <v>0.05227739231763274</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5522479520124634</v>
+        <v>0.5522479520124639</v>
       </c>
       <c r="F212" t="n">
-        <v>-1.347985979776195</v>
+        <v>-1.347985979776197</v>
       </c>
       <c r="G212" t="n">
         <v>1.823652537543815</v>
@@ -5741,22 +5741,22 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>-2.905955682620839</v>
+        <v>-2.905955682620838</v>
       </c>
       <c r="C213" t="n">
-        <v>0.05195595063372497</v>
+        <v>0.05195595063372496</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.0561934943982489</v>
+        <v>-0.0561934943982502</v>
       </c>
       <c r="E213" t="n">
-        <v>0.599459299657599</v>
+        <v>0.5994592996575996</v>
       </c>
       <c r="F213" t="n">
-        <v>-1.092419831206434</v>
+        <v>-1.092419831206436</v>
       </c>
       <c r="G213" t="n">
-        <v>1.974536741320473</v>
+        <v>1.974536741320474</v>
       </c>
     </row>
     <row r="214">
@@ -5766,19 +5766,19 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-1.087059558354548</v>
+        <v>-1.087059558354547</v>
       </c>
       <c r="C214" t="n">
-        <v>1.642200669253487</v>
+        <v>1.642200669253486</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.01684311406886916</v>
+        <v>-0.01684311406886902</v>
       </c>
       <c r="E214" t="n">
-        <v>0.5938706305115669</v>
+        <v>0.5938706305115672</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.3651524675200444</v>
+        <v>-0.3651524675200453</v>
       </c>
       <c r="G214" t="n">
         <v>2.453340523812644</v>
@@ -5791,22 +5791,22 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-3.167019429454647</v>
+        <v>-3.167019429454646</v>
       </c>
       <c r="C215" t="n">
-        <v>0.1151098320646766</v>
+        <v>0.1151098320646765</v>
       </c>
       <c r="D215" t="n">
-        <v>0.05448763164076208</v>
+        <v>0.05448763164076097</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6135511696864331</v>
+        <v>0.6135511696864338</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.813456109039279</v>
+        <v>-0.8134561090392806</v>
       </c>
       <c r="G215" t="n">
-        <v>2.024602947540684</v>
+        <v>2.024602947540685</v>
       </c>
     </row>
     <row r="216">
@@ -5816,22 +5816,22 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-3.520805659205713</v>
+        <v>-3.520805659205712</v>
       </c>
       <c r="C216" t="n">
-        <v>0.2645200316024076</v>
+        <v>0.2645200316024074</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.2080105014395562</v>
+        <v>-0.2080105014395559</v>
       </c>
       <c r="E216" t="n">
-        <v>0.3017315555677913</v>
+        <v>0.3017315555677915</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.3493082724922306</v>
+        <v>-0.3493082724922315</v>
       </c>
       <c r="G216" t="n">
-        <v>2.001663093756192</v>
+        <v>2.001663093756193</v>
       </c>
     </row>
     <row r="217">
@@ -5841,22 +5841,22 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>-1.377585306309448</v>
+        <v>-1.377585306309447</v>
       </c>
       <c r="C217" t="n">
-        <v>1.830723561361999</v>
+        <v>1.830723561361998</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.02729145861227524</v>
+        <v>-0.02729145861227454</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3108684152473591</v>
+        <v>0.3108684152473596</v>
       </c>
       <c r="F217" t="n">
-        <v>-0.0362508375237905</v>
+        <v>-0.03625083752379112</v>
       </c>
       <c r="G217" t="n">
-        <v>2.468161441532856</v>
+        <v>2.468161441532857</v>
       </c>
     </row>
     <row r="218">
@@ -5866,22 +5866,22 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-3.634574371021774</v>
+        <v>-3.634574371021772</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.6137739184869415</v>
+        <v>-0.6137739184869405</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.5698464389872923</v>
+        <v>-0.5698464389872931</v>
       </c>
       <c r="E218" t="n">
-        <v>0.1831052725646437</v>
+        <v>0.1831052725646442</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.8479979797137639</v>
+        <v>-0.8479979797137651</v>
       </c>
       <c r="G218" t="n">
-        <v>1.719081411373789</v>
+        <v>1.71908141137379</v>
       </c>
     </row>
     <row r="219">
@@ -5891,22 +5891,22 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>-2.893179026663169</v>
+        <v>-2.893179026663168</v>
       </c>
       <c r="C219" t="n">
-        <v>0.1958124319641756</v>
+        <v>0.1958124319641759</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.3719641693732126</v>
+        <v>-0.3719641693732123</v>
       </c>
       <c r="E219" t="n">
-        <v>0.1144120845010132</v>
+        <v>0.1144120845010139</v>
       </c>
       <c r="F219" t="n">
-        <v>0.3593948198147103</v>
+        <v>0.3593948198147105</v>
       </c>
       <c r="G219" t="n">
-        <v>2.093341844944755</v>
+        <v>2.093341844944756</v>
       </c>
     </row>
     <row r="220">
@@ -5916,19 +5916,19 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>-0.5723721788977614</v>
+        <v>-0.572372178897761</v>
       </c>
       <c r="C220" t="n">
-        <v>2.310418664325629</v>
+        <v>2.310418664325626</v>
       </c>
       <c r="D220" t="n">
-        <v>1.323934235404981</v>
+        <v>1.32393423540498</v>
       </c>
       <c r="E220" t="n">
-        <v>1.458864710425384</v>
+        <v>1.458864710425385</v>
       </c>
       <c r="F220" t="n">
-        <v>-0.4182646086026177</v>
+        <v>-0.4182646086026196</v>
       </c>
       <c r="G220" t="n">
         <v>2.918917674077924</v>
@@ -5941,19 +5941,19 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>1.347995606169807</v>
+        <v>1.347995606169806</v>
       </c>
       <c r="C221" t="n">
-        <v>3.388877017626667</v>
+        <v>3.388877017626664</v>
       </c>
       <c r="D221" t="n">
-        <v>0.2429979180469656</v>
+        <v>0.242997918046966</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7711667521548982</v>
+        <v>0.7711667521548985</v>
       </c>
       <c r="F221" t="n">
-        <v>-1.043109723918329</v>
+        <v>-1.043109723918331</v>
       </c>
       <c r="G221" t="n">
         <v>2.857688738456741</v>
@@ -5966,22 +5966,22 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1.989305500953223</v>
+        <v>1.989305500953222</v>
       </c>
       <c r="C222" t="n">
-        <v>0.115870678731585</v>
+        <v>0.115870678731583</v>
       </c>
       <c r="D222" t="n">
-        <v>1.048412512795384</v>
+        <v>1.048412512795379</v>
       </c>
       <c r="E222" t="n">
-        <v>4.468968995683205</v>
+        <v>4.468968995683207</v>
       </c>
       <c r="F222" t="n">
-        <v>-1.123559034952408</v>
+        <v>-1.123559034952411</v>
       </c>
       <c r="G222" t="n">
-        <v>3.035111321170719</v>
+        <v>3.035111321170717</v>
       </c>
     </row>
     <row r="223">
@@ -5991,22 +5991,22 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>-0.4882460954810556</v>
+        <v>-0.4882460954810554</v>
       </c>
       <c r="C223" t="n">
-        <v>2.374797188301778</v>
+        <v>2.374797188301776</v>
       </c>
       <c r="D223" t="n">
-        <v>0.8779409908967105</v>
+        <v>0.8779409908967095</v>
       </c>
       <c r="E223" t="n">
         <v>1.147475270001562</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.655906153036052</v>
+        <v>-0.6559061530360539</v>
       </c>
       <c r="G223" t="n">
-        <v>2.784087022393352</v>
+        <v>2.784087022393351</v>
       </c>
     </row>
     <row r="224">
@@ -6016,22 +6016,22 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2.057868053974148</v>
+        <v>2.057868053974147</v>
       </c>
       <c r="C224" t="n">
-        <v>3.221471462810959</v>
+        <v>3.221471462810957</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.1259454038483644</v>
+        <v>-0.1259454038483643</v>
       </c>
       <c r="E224" t="n">
-        <v>1.090730534510535</v>
+        <v>1.090730534510536</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.9563978436214826</v>
+        <v>-0.9563978436214842</v>
       </c>
       <c r="G224" t="n">
-        <v>2.878619916005815</v>
+        <v>2.878619916005816</v>
       </c>
     </row>
     <row r="225">
@@ -6041,16 +6041,16 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>-2.700726194009252</v>
+        <v>-2.700726194009251</v>
       </c>
       <c r="C225" t="n">
-        <v>0.4666303960635669</v>
+        <v>0.4666303960635662</v>
       </c>
       <c r="D225" t="n">
-        <v>0.08928545947322115</v>
+        <v>0.08928545947322103</v>
       </c>
       <c r="E225" t="n">
-        <v>0.5325111195530996</v>
+        <v>0.5325111195531</v>
       </c>
       <c r="F225" t="n">
         <v>0.2270668756329048</v>
@@ -6069,16 +6069,16 @@
         <v>1.382740899199727</v>
       </c>
       <c r="C226" t="n">
-        <v>2.053863240304131</v>
+        <v>2.053863240304128</v>
       </c>
       <c r="D226" t="n">
-        <v>0.7591641837488152</v>
+        <v>0.7591641837488113</v>
       </c>
       <c r="E226" t="n">
-        <v>4.113098870499632</v>
+        <v>4.113098870499635</v>
       </c>
       <c r="F226" t="n">
-        <v>-1.404118833204703</v>
+        <v>-1.404118833204706</v>
       </c>
       <c r="G226" t="n">
         <v>3.124744084394261</v>
@@ -6091,19 +6091,19 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.751675426695204</v>
+        <v>0.7516754266952032</v>
       </c>
       <c r="C227" t="n">
         <v>1.998611902847312</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.2335393061603699</v>
+        <v>-0.2335393061603723</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8253298855365894</v>
+        <v>0.8253298855365897</v>
       </c>
       <c r="F227" t="n">
-        <v>-3.152829423596941</v>
+        <v>-3.152829423596946</v>
       </c>
       <c r="G227" t="n">
         <v>2.231248938150776</v>
@@ -6116,19 +6116,19 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9902672592687232</v>
+        <v>0.9902672592687222</v>
       </c>
       <c r="C228" t="n">
-        <v>3.308387244945979</v>
+        <v>3.308387244945977</v>
       </c>
       <c r="D228" t="n">
-        <v>0.2974085071261394</v>
+        <v>0.2974085071261397</v>
       </c>
       <c r="E228" t="n">
-        <v>0.5306014996253184</v>
+        <v>0.5306014996253183</v>
       </c>
       <c r="F228" t="n">
-        <v>-1.289206038928812</v>
+        <v>-1.289206038928814</v>
       </c>
       <c r="G228" t="n">
         <v>2.76175881376084</v>
@@ -6144,16 +6144,16 @@
         <v>-1.254597735038583</v>
       </c>
       <c r="C229" t="n">
-        <v>1.079572046917901</v>
+        <v>1.079572046917899</v>
       </c>
       <c r="D229" t="n">
-        <v>0.129311712543852</v>
+        <v>0.129311712543851</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8709479510792628</v>
+        <v>0.8709479510792636</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.5365936222611427</v>
+        <v>-0.5365936222611439</v>
       </c>
       <c r="G229" t="n">
         <v>2.395703430304021</v>
@@ -6166,22 +6166,22 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>-2.15395775152092</v>
+        <v>-2.153957751520919</v>
       </c>
       <c r="C230" t="n">
-        <v>0.986017827978479</v>
+        <v>0.9860178279784781</v>
       </c>
       <c r="D230" t="n">
-        <v>0.2510763820294841</v>
+        <v>0.2510763820294832</v>
       </c>
       <c r="E230" t="n">
-        <v>0.3341016007175349</v>
+        <v>0.334101600717535</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.8310544205871934</v>
+        <v>-0.8310544205871949</v>
       </c>
       <c r="G230" t="n">
-        <v>2.223126384917812</v>
+        <v>2.223126384917813</v>
       </c>
     </row>
     <row r="231">
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>-1.908629355805097</v>
+        <v>-1.908629355805096</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.6214269819713759</v>
+        <v>-0.6214269819713757</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.3057913285063547</v>
+        <v>-0.3057913285063572</v>
       </c>
       <c r="E231" t="n">
-        <v>1.625190742319843</v>
+        <v>1.625190742319844</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.6244238617727518</v>
+        <v>-0.6244238617727528</v>
       </c>
       <c r="G231" t="n">
         <v>2.111122281755686</v>
@@ -6219,19 +6219,19 @@
         <v>2.373676677657147</v>
       </c>
       <c r="C232" t="n">
-        <v>2.951036662966345</v>
+        <v>2.951036662966341</v>
       </c>
       <c r="D232" t="n">
-        <v>0.8142295897230301</v>
+        <v>0.8142295897230296</v>
       </c>
       <c r="E232" t="n">
-        <v>2.328822834442656</v>
+        <v>2.328822834442657</v>
       </c>
       <c r="F232" t="n">
-        <v>-1.088558453919593</v>
+        <v>-1.088558453919595</v>
       </c>
       <c r="G232" t="n">
-        <v>3.162333285011525</v>
+        <v>3.162333285011526</v>
       </c>
     </row>
     <row r="233">
@@ -6241,19 +6241,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>-2.348239086235433</v>
+        <v>-2.348239086235432</v>
       </c>
       <c r="C233" t="n">
-        <v>0.1245785958627225</v>
+        <v>0.1245785958627221</v>
       </c>
       <c r="D233" t="n">
-        <v>-0.1384871333603442</v>
+        <v>-0.1384871333603457</v>
       </c>
       <c r="E233" t="n">
-        <v>1.197834244546017</v>
+        <v>1.197834244546018</v>
       </c>
       <c r="F233" t="n">
-        <v>-1.032210765319538</v>
+        <v>-1.03221076531954</v>
       </c>
       <c r="G233" t="n">
         <v>2.09755666968094</v>
@@ -6266,22 +6266,22 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>-0.6228585062216963</v>
+        <v>-0.6228585062216961</v>
       </c>
       <c r="C234" t="n">
-        <v>2.242782855618303</v>
+        <v>2.242782855618302</v>
       </c>
       <c r="D234" t="n">
-        <v>-0.6845690959091115</v>
+        <v>-0.6845690959091084</v>
       </c>
       <c r="E234" t="n">
-        <v>0.5781798598878798</v>
+        <v>0.5781798598878823</v>
       </c>
       <c r="F234" t="n">
-        <v>2.84582826505566</v>
+        <v>2.845828265055662</v>
       </c>
       <c r="G234" t="n">
-        <v>2.926815662450544</v>
+        <v>2.926815662450545</v>
       </c>
     </row>
     <row r="235">
@@ -6291,22 +6291,22 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>-0.755418575570471</v>
+        <v>-0.7554185755704711</v>
       </c>
       <c r="C235" t="n">
-        <v>2.079321755205378</v>
+        <v>2.079321755205376</v>
       </c>
       <c r="D235" t="n">
-        <v>-0.2851649737549776</v>
+        <v>-0.2851649737549752</v>
       </c>
       <c r="E235" t="n">
-        <v>0.4070445479863124</v>
+        <v>0.4070445479863138</v>
       </c>
       <c r="F235" t="n">
-        <v>1.616630960916539</v>
+        <v>1.616630960916541</v>
       </c>
       <c r="G235" t="n">
-        <v>2.76122785331315</v>
+        <v>2.761227853313151</v>
       </c>
     </row>
     <row r="236">
@@ -6319,19 +6319,19 @@
         <v>-0.6138826781011105</v>
       </c>
       <c r="C236" t="n">
-        <v>2.479427488290719</v>
+        <v>2.479427488290717</v>
       </c>
       <c r="D236" t="n">
-        <v>0.536416067160533</v>
+        <v>0.5364160671605342</v>
       </c>
       <c r="E236" t="n">
-        <v>0.2842301872575205</v>
+        <v>0.2842301872575212</v>
       </c>
       <c r="F236" t="n">
-        <v>0.6791785957572891</v>
+        <v>0.6791785957572892</v>
       </c>
       <c r="G236" t="n">
-        <v>2.817942104020186</v>
+        <v>2.817942104020187</v>
       </c>
     </row>
     <row r="237">
@@ -6344,19 +6344,19 @@
         <v>-0.6214681054670167</v>
       </c>
       <c r="C237" t="n">
-        <v>2.158542928526597</v>
+        <v>2.158542928526594</v>
       </c>
       <c r="D237" t="n">
-        <v>-0.5103957843135772</v>
+        <v>-0.5103957843135741</v>
       </c>
       <c r="E237" t="n">
-        <v>0.7858505077704507</v>
+        <v>0.7858505077704538</v>
       </c>
       <c r="F237" t="n">
-        <v>3.406731806065343</v>
+        <v>3.406731806065347</v>
       </c>
       <c r="G237" t="n">
-        <v>3.053044720706486</v>
+        <v>3.053044720706488</v>
       </c>
     </row>
   </sheetData>
